--- a/Ventas Granel.xlsx
+++ b/Ventas Granel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hector/Desktop/Granel Movimientos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386BE4B5-52DA-D54F-8586-D31DB0581250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C940D61B-68E3-BC48-B2CA-1C09FD25727D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="100" yWindow="840" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Detalles movimientos" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="107">
   <si>
     <t>RESUMEN Y MOVIMIENTOS INDIVIDUALES: IGNACIO</t>
   </si>
@@ -353,6 +353,12 @@
   </si>
   <si>
     <t>Guía N° 2356889</t>
+  </si>
+  <si>
+    <t>Guía N° 2358078</t>
+  </si>
+  <si>
+    <t>Guía N° 2358522</t>
   </si>
 </sst>
 </file>
@@ -2375,7 +2381,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="6">
-        <f t="shared" ref="K26:K31" si="3">H26*I26</f>
+        <f t="shared" ref="K26:K29" si="3">H26*I26</f>
         <v>0</v>
       </c>
       <c r="L26" s="1" t="s">
@@ -2603,7 +2609,7 @@
         <v>104</v>
       </c>
       <c r="O30" s="12">
-        <v>3895122</v>
+        <v>3955528</v>
       </c>
       <c r="P30" s="29">
         <v>11656</v>
@@ -2626,23 +2632,39 @@
       </c>
     </row>
     <row r="31" spans="3:21">
-      <c r="C31" s="7"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="C31" s="7">
+        <v>46252</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="2"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="6"/>
-      <c r="L31" s="1"/>
+      <c r="L31" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="M31" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="N31" s="26"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="29"/>
+        <f t="shared" ref="M31" si="4">IF(F31="CJ", I31*200, "")</f>
+        <v/>
+      </c>
+      <c r="N31" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="O31" s="12">
+        <v>3889821</v>
+      </c>
+      <c r="P31" s="29">
+        <v>11462</v>
+      </c>
       <c r="R31" t="str">
         <f>IF(F31="CJ", COUNTIF(F$5:F31, "CJ"), "")</f>
         <v/>
@@ -2655,29 +2677,45 @@
         <f>IF(F31="Tripulacion", COUNTIF(F$5:F31, "Tripulacion"), "")</f>
         <v/>
       </c>
-      <c r="U31" t="str">
+      <c r="U31">
         <f>IF(F31="ENAP carga", COUNTIF(F$5:F31, "ENAP carga"), "")</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="3:21">
-      <c r="C32" s="7"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="C32" s="7">
+        <v>46253</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="G32" s="1"/>
       <c r="H32" s="2"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="6"/>
-      <c r="L32" s="1"/>
+      <c r="L32" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="M32" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="N32" s="26"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="29"/>
+      <c r="N32" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="O32" s="12">
+        <v>3830686</v>
+      </c>
+      <c r="P32" s="29">
+        <v>11288</v>
+      </c>
       <c r="R32" t="str">
         <f>IF(F32="CJ", COUNTIF(F$5:F32, "CJ"), "")</f>
         <v/>
@@ -2690,9 +2728,9 @@
         <f>IF(F32="Tripulacion", COUNTIF(F$5:F32, "Tripulacion"), "")</f>
         <v/>
       </c>
-      <c r="U32" t="str">
+      <c r="U32">
         <f>IF(F32="ENAP carga", COUNTIF(F$5:F32, "ENAP carga"), "")</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="3:21">
@@ -4284,7 +4322,7 @@
     </row>
     <row r="88" spans="13:21">
       <c r="M88" s="22" t="str">
-        <f t="shared" ref="M88:M151" si="4">IF(F88="CJ", I88*200, "")</f>
+        <f t="shared" ref="M88:M151" si="5">IF(F88="CJ", I88*200, "")</f>
         <v/>
       </c>
       <c r="R88" t="str">
@@ -4306,7 +4344,7 @@
     </row>
     <row r="89" spans="13:21">
       <c r="M89" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R89" t="str">
@@ -4328,7 +4366,7 @@
     </row>
     <row r="90" spans="13:21">
       <c r="M90" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R90" t="str">
@@ -4350,7 +4388,7 @@
     </row>
     <row r="91" spans="13:21">
       <c r="M91" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R91" t="str">
@@ -4372,7 +4410,7 @@
     </row>
     <row r="92" spans="13:21">
       <c r="M92" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R92" t="str">
@@ -4394,7 +4432,7 @@
     </row>
     <row r="93" spans="13:21">
       <c r="M93" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R93" t="str">
@@ -4416,7 +4454,7 @@
     </row>
     <row r="94" spans="13:21">
       <c r="M94" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R94" t="str">
@@ -4438,7 +4476,7 @@
     </row>
     <row r="95" spans="13:21">
       <c r="M95" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R95" t="str">
@@ -4460,7 +4498,7 @@
     </row>
     <row r="96" spans="13:21">
       <c r="M96" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R96" t="str">
@@ -4482,7 +4520,7 @@
     </row>
     <row r="97" spans="13:21">
       <c r="M97" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R97" t="str">
@@ -4504,7 +4542,7 @@
     </row>
     <row r="98" spans="13:21">
       <c r="M98" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R98" t="str">
@@ -4526,7 +4564,7 @@
     </row>
     <row r="99" spans="13:21">
       <c r="M99" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R99" t="str">
@@ -4548,7 +4586,7 @@
     </row>
     <row r="100" spans="13:21">
       <c r="M100" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R100" t="str">
@@ -4570,7 +4608,7 @@
     </row>
     <row r="101" spans="13:21">
       <c r="M101" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R101" t="str">
@@ -4592,7 +4630,7 @@
     </row>
     <row r="102" spans="13:21">
       <c r="M102" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R102" t="str">
@@ -4614,7 +4652,7 @@
     </row>
     <row r="103" spans="13:21">
       <c r="M103" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R103" t="str">
@@ -4636,7 +4674,7 @@
     </row>
     <row r="104" spans="13:21">
       <c r="M104" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R104" t="str">
@@ -4658,7 +4696,7 @@
     </row>
     <row r="105" spans="13:21">
       <c r="M105" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R105" t="str">
@@ -4680,7 +4718,7 @@
     </row>
     <row r="106" spans="13:21">
       <c r="M106" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R106" t="str">
@@ -4702,7 +4740,7 @@
     </row>
     <row r="107" spans="13:21">
       <c r="M107" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R107" t="str">
@@ -4724,7 +4762,7 @@
     </row>
     <row r="108" spans="13:21">
       <c r="M108" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R108" t="str">
@@ -4746,7 +4784,7 @@
     </row>
     <row r="109" spans="13:21">
       <c r="M109" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R109" t="str">
@@ -4768,7 +4806,7 @@
     </row>
     <row r="110" spans="13:21">
       <c r="M110" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R110" t="str">
@@ -4790,7 +4828,7 @@
     </row>
     <row r="111" spans="13:21">
       <c r="M111" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R111" t="str">
@@ -4812,7 +4850,7 @@
     </row>
     <row r="112" spans="13:21">
       <c r="M112" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R112" t="str">
@@ -4834,7 +4872,7 @@
     </row>
     <row r="113" spans="13:21">
       <c r="M113" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R113" t="str">
@@ -4856,7 +4894,7 @@
     </row>
     <row r="114" spans="13:21">
       <c r="M114" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R114" t="str">
@@ -4878,7 +4916,7 @@
     </row>
     <row r="115" spans="13:21">
       <c r="M115" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R115" t="str">
@@ -4900,7 +4938,7 @@
     </row>
     <row r="116" spans="13:21">
       <c r="M116" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R116" t="str">
@@ -4922,7 +4960,7 @@
     </row>
     <row r="117" spans="13:21">
       <c r="M117" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R117" t="str">
@@ -4944,7 +4982,7 @@
     </row>
     <row r="118" spans="13:21">
       <c r="M118" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R118" t="str">
@@ -4966,7 +5004,7 @@
     </row>
     <row r="119" spans="13:21">
       <c r="M119" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R119" t="str">
@@ -4988,7 +5026,7 @@
     </row>
     <row r="120" spans="13:21">
       <c r="M120" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R120" t="str">
@@ -5010,7 +5048,7 @@
     </row>
     <row r="121" spans="13:21">
       <c r="M121" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R121" t="str">
@@ -5032,7 +5070,7 @@
     </row>
     <row r="122" spans="13:21">
       <c r="M122" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R122" t="str">
@@ -5054,7 +5092,7 @@
     </row>
     <row r="123" spans="13:21">
       <c r="M123" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R123" t="str">
@@ -5076,7 +5114,7 @@
     </row>
     <row r="124" spans="13:21">
       <c r="M124" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R124" t="str">
@@ -5098,7 +5136,7 @@
     </row>
     <row r="125" spans="13:21">
       <c r="M125" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R125" t="str">
@@ -5120,7 +5158,7 @@
     </row>
     <row r="126" spans="13:21">
       <c r="M126" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R126" t="str">
@@ -5142,7 +5180,7 @@
     </row>
     <row r="127" spans="13:21">
       <c r="M127" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R127" t="str">
@@ -5164,7 +5202,7 @@
     </row>
     <row r="128" spans="13:21">
       <c r="M128" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R128" t="str">
@@ -5186,7 +5224,7 @@
     </row>
     <row r="129" spans="13:21">
       <c r="M129" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R129" t="str">
@@ -5208,7 +5246,7 @@
     </row>
     <row r="130" spans="13:21">
       <c r="M130" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R130" t="str">
@@ -5230,7 +5268,7 @@
     </row>
     <row r="131" spans="13:21">
       <c r="M131" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R131" t="str">
@@ -5252,7 +5290,7 @@
     </row>
     <row r="132" spans="13:21">
       <c r="M132" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R132" t="str">
@@ -5274,7 +5312,7 @@
     </row>
     <row r="133" spans="13:21">
       <c r="M133" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R133" t="str">
@@ -5296,7 +5334,7 @@
     </row>
     <row r="134" spans="13:21">
       <c r="M134" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R134" t="str">
@@ -5318,7 +5356,7 @@
     </row>
     <row r="135" spans="13:21">
       <c r="M135" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R135" t="str">
@@ -5340,7 +5378,7 @@
     </row>
     <row r="136" spans="13:21">
       <c r="M136" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R136" t="str">
@@ -5362,7 +5400,7 @@
     </row>
     <row r="137" spans="13:21">
       <c r="M137" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R137" t="str">
@@ -5384,7 +5422,7 @@
     </row>
     <row r="138" spans="13:21">
       <c r="M138" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R138" t="str">
@@ -5406,7 +5444,7 @@
     </row>
     <row r="139" spans="13:21">
       <c r="M139" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R139" t="str">
@@ -5428,7 +5466,7 @@
     </row>
     <row r="140" spans="13:21">
       <c r="M140" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R140" t="str">
@@ -5450,7 +5488,7 @@
     </row>
     <row r="141" spans="13:21">
       <c r="M141" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R141" t="str">
@@ -5472,7 +5510,7 @@
     </row>
     <row r="142" spans="13:21">
       <c r="M142" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R142" t="str">
@@ -5494,7 +5532,7 @@
     </row>
     <row r="143" spans="13:21">
       <c r="M143" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R143" t="str">
@@ -5516,7 +5554,7 @@
     </row>
     <row r="144" spans="13:21">
       <c r="M144" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R144" t="str">
@@ -5538,7 +5576,7 @@
     </row>
     <row r="145" spans="13:21">
       <c r="M145" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R145" t="str">
@@ -5560,7 +5598,7 @@
     </row>
     <row r="146" spans="13:21">
       <c r="M146" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R146" t="str">
@@ -5582,7 +5620,7 @@
     </row>
     <row r="147" spans="13:21">
       <c r="M147" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R147" t="str">
@@ -5604,7 +5642,7 @@
     </row>
     <row r="148" spans="13:21">
       <c r="M148" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R148" t="str">
@@ -5626,7 +5664,7 @@
     </row>
     <row r="149" spans="13:21">
       <c r="M149" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R149" t="str">
@@ -5648,7 +5686,7 @@
     </row>
     <row r="150" spans="13:21">
       <c r="M150" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R150" t="str">
@@ -5670,7 +5708,7 @@
     </row>
     <row r="151" spans="13:21">
       <c r="M151" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="R151" t="str">
@@ -5692,7 +5730,7 @@
     </row>
     <row r="152" spans="13:21">
       <c r="M152" s="22" t="str">
-        <f t="shared" ref="M152:M215" si="5">IF(F152="CJ", I152*200, "")</f>
+        <f t="shared" ref="M152:M215" si="6">IF(F152="CJ", I152*200, "")</f>
         <v/>
       </c>
       <c r="R152" t="str">
@@ -5714,7 +5752,7 @@
     </row>
     <row r="153" spans="13:21">
       <c r="M153" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R153" t="str">
@@ -5736,7 +5774,7 @@
     </row>
     <row r="154" spans="13:21">
       <c r="M154" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R154" t="str">
@@ -5758,7 +5796,7 @@
     </row>
     <row r="155" spans="13:21">
       <c r="M155" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R155" t="str">
@@ -5780,7 +5818,7 @@
     </row>
     <row r="156" spans="13:21">
       <c r="M156" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R156" t="str">
@@ -5802,7 +5840,7 @@
     </row>
     <row r="157" spans="13:21">
       <c r="M157" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R157" t="str">
@@ -5824,7 +5862,7 @@
     </row>
     <row r="158" spans="13:21">
       <c r="M158" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R158" t="str">
@@ -5846,7 +5884,7 @@
     </row>
     <row r="159" spans="13:21">
       <c r="M159" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R159" t="str">
@@ -5868,7 +5906,7 @@
     </row>
     <row r="160" spans="13:21">
       <c r="M160" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R160" t="str">
@@ -5890,7 +5928,7 @@
     </row>
     <row r="161" spans="13:21">
       <c r="M161" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R161" t="str">
@@ -5912,7 +5950,7 @@
     </row>
     <row r="162" spans="13:21">
       <c r="M162" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R162" t="str">
@@ -5934,7 +5972,7 @@
     </row>
     <row r="163" spans="13:21">
       <c r="M163" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R163" t="str">
@@ -5956,7 +5994,7 @@
     </row>
     <row r="164" spans="13:21">
       <c r="M164" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R164" t="str">
@@ -5978,7 +6016,7 @@
     </row>
     <row r="165" spans="13:21">
       <c r="M165" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R165" t="str">
@@ -6000,7 +6038,7 @@
     </row>
     <row r="166" spans="13:21">
       <c r="M166" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R166" t="str">
@@ -6022,7 +6060,7 @@
     </row>
     <row r="167" spans="13:21">
       <c r="M167" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R167" t="str">
@@ -6044,7 +6082,7 @@
     </row>
     <row r="168" spans="13:21">
       <c r="M168" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R168" t="str">
@@ -6066,7 +6104,7 @@
     </row>
     <row r="169" spans="13:21">
       <c r="M169" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R169" t="str">
@@ -6088,7 +6126,7 @@
     </row>
     <row r="170" spans="13:21">
       <c r="M170" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R170" t="str">
@@ -6110,7 +6148,7 @@
     </row>
     <row r="171" spans="13:21">
       <c r="M171" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R171" t="str">
@@ -6132,7 +6170,7 @@
     </row>
     <row r="172" spans="13:21">
       <c r="M172" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R172" t="str">
@@ -6154,7 +6192,7 @@
     </row>
     <row r="173" spans="13:21">
       <c r="M173" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R173" t="str">
@@ -6176,7 +6214,7 @@
     </row>
     <row r="174" spans="13:21">
       <c r="M174" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R174" t="str">
@@ -6198,7 +6236,7 @@
     </row>
     <row r="175" spans="13:21">
       <c r="M175" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R175" t="str">
@@ -6220,7 +6258,7 @@
     </row>
     <row r="176" spans="13:21">
       <c r="M176" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R176" t="str">
@@ -6242,7 +6280,7 @@
     </row>
     <row r="177" spans="13:21">
       <c r="M177" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R177" t="str">
@@ -6264,7 +6302,7 @@
     </row>
     <row r="178" spans="13:21">
       <c r="M178" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R178" t="str">
@@ -6286,7 +6324,7 @@
     </row>
     <row r="179" spans="13:21">
       <c r="M179" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R179" t="str">
@@ -6308,7 +6346,7 @@
     </row>
     <row r="180" spans="13:21">
       <c r="M180" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R180" t="str">
@@ -6330,7 +6368,7 @@
     </row>
     <row r="181" spans="13:21">
       <c r="M181" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R181" t="str">
@@ -6352,7 +6390,7 @@
     </row>
     <row r="182" spans="13:21">
       <c r="M182" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R182" t="str">
@@ -6374,7 +6412,7 @@
     </row>
     <row r="183" spans="13:21">
       <c r="M183" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R183" t="str">
@@ -6396,7 +6434,7 @@
     </row>
     <row r="184" spans="13:21">
       <c r="M184" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R184" t="str">
@@ -6418,7 +6456,7 @@
     </row>
     <row r="185" spans="13:21">
       <c r="M185" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R185" t="str">
@@ -6440,7 +6478,7 @@
     </row>
     <row r="186" spans="13:21">
       <c r="M186" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R186" t="str">
@@ -6462,7 +6500,7 @@
     </row>
     <row r="187" spans="13:21">
       <c r="M187" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R187" t="str">
@@ -6484,7 +6522,7 @@
     </row>
     <row r="188" spans="13:21">
       <c r="M188" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R188" t="str">
@@ -6506,7 +6544,7 @@
     </row>
     <row r="189" spans="13:21">
       <c r="M189" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R189" t="str">
@@ -6528,7 +6566,7 @@
     </row>
     <row r="190" spans="13:21">
       <c r="M190" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R190" t="str">
@@ -6550,7 +6588,7 @@
     </row>
     <row r="191" spans="13:21">
       <c r="M191" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R191" t="str">
@@ -6572,7 +6610,7 @@
     </row>
     <row r="192" spans="13:21">
       <c r="M192" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R192" t="str">
@@ -6594,7 +6632,7 @@
     </row>
     <row r="193" spans="13:21">
       <c r="M193" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R193" t="str">
@@ -6616,7 +6654,7 @@
     </row>
     <row r="194" spans="13:21">
       <c r="M194" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R194" t="str">
@@ -6638,7 +6676,7 @@
     </row>
     <row r="195" spans="13:21">
       <c r="M195" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R195" t="str">
@@ -6660,7 +6698,7 @@
     </row>
     <row r="196" spans="13:21">
       <c r="M196" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R196" t="str">
@@ -6682,7 +6720,7 @@
     </row>
     <row r="197" spans="13:21">
       <c r="M197" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R197" t="str">
@@ -6704,7 +6742,7 @@
     </row>
     <row r="198" spans="13:21">
       <c r="M198" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R198" t="str">
@@ -6726,7 +6764,7 @@
     </row>
     <row r="199" spans="13:21">
       <c r="M199" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R199" t="str">
@@ -6748,7 +6786,7 @@
     </row>
     <row r="200" spans="13:21">
       <c r="M200" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R200" t="str">
@@ -6770,7 +6808,7 @@
     </row>
     <row r="201" spans="13:21">
       <c r="M201" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R201" t="str">
@@ -6792,7 +6830,7 @@
     </row>
     <row r="202" spans="13:21">
       <c r="M202" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R202" t="str">
@@ -6814,7 +6852,7 @@
     </row>
     <row r="203" spans="13:21">
       <c r="M203" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R203" t="str">
@@ -6836,7 +6874,7 @@
     </row>
     <row r="204" spans="13:21">
       <c r="M204" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R204" t="str">
@@ -6858,7 +6896,7 @@
     </row>
     <row r="205" spans="13:21">
       <c r="M205" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R205" t="str">
@@ -6880,7 +6918,7 @@
     </row>
     <row r="206" spans="13:21">
       <c r="M206" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R206" t="str">
@@ -6902,7 +6940,7 @@
     </row>
     <row r="207" spans="13:21">
       <c r="M207" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R207" t="str">
@@ -6924,7 +6962,7 @@
     </row>
     <row r="208" spans="13:21">
       <c r="M208" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R208" t="str">
@@ -6946,7 +6984,7 @@
     </row>
     <row r="209" spans="13:21">
       <c r="M209" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R209" t="str">
@@ -6968,7 +7006,7 @@
     </row>
     <row r="210" spans="13:21">
       <c r="M210" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R210" t="str">
@@ -6990,7 +7028,7 @@
     </row>
     <row r="211" spans="13:21">
       <c r="M211" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R211" t="str">
@@ -7012,7 +7050,7 @@
     </row>
     <row r="212" spans="13:21">
       <c r="M212" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R212" t="str">
@@ -7034,7 +7072,7 @@
     </row>
     <row r="213" spans="13:21">
       <c r="M213" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R213" t="str">
@@ -7056,7 +7094,7 @@
     </row>
     <row r="214" spans="13:21">
       <c r="M214" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R214" t="str">
@@ -7078,7 +7116,7 @@
     </row>
     <row r="215" spans="13:21">
       <c r="M215" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R215" t="str">
@@ -7100,7 +7138,7 @@
     </row>
     <row r="216" spans="13:21">
       <c r="M216" s="22" t="str">
-        <f t="shared" ref="M216:M279" si="6">IF(F216="CJ", I216*200, "")</f>
+        <f t="shared" ref="M216:M279" si="7">IF(F216="CJ", I216*200, "")</f>
         <v/>
       </c>
       <c r="R216" t="str">
@@ -7122,7 +7160,7 @@
     </row>
     <row r="217" spans="13:21">
       <c r="M217" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R217" t="str">
@@ -7144,7 +7182,7 @@
     </row>
     <row r="218" spans="13:21">
       <c r="M218" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R218" t="str">
@@ -7166,7 +7204,7 @@
     </row>
     <row r="219" spans="13:21">
       <c r="M219" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R219" t="str">
@@ -7188,7 +7226,7 @@
     </row>
     <row r="220" spans="13:21">
       <c r="M220" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R220" t="str">
@@ -7210,7 +7248,7 @@
     </row>
     <row r="221" spans="13:21">
       <c r="M221" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R221" t="str">
@@ -7232,7 +7270,7 @@
     </row>
     <row r="222" spans="13:21">
       <c r="M222" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R222" t="str">
@@ -7254,7 +7292,7 @@
     </row>
     <row r="223" spans="13:21">
       <c r="M223" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R223" t="str">
@@ -7276,7 +7314,7 @@
     </row>
     <row r="224" spans="13:21">
       <c r="M224" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R224" t="str">
@@ -7298,7 +7336,7 @@
     </row>
     <row r="225" spans="13:21">
       <c r="M225" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R225" t="str">
@@ -7320,7 +7358,7 @@
     </row>
     <row r="226" spans="13:21">
       <c r="M226" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R226" t="str">
@@ -7342,7 +7380,7 @@
     </row>
     <row r="227" spans="13:21">
       <c r="M227" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R227" t="str">
@@ -7364,7 +7402,7 @@
     </row>
     <row r="228" spans="13:21">
       <c r="M228" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R228" t="str">
@@ -7386,7 +7424,7 @@
     </row>
     <row r="229" spans="13:21">
       <c r="M229" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R229" t="str">
@@ -7408,7 +7446,7 @@
     </row>
     <row r="230" spans="13:21">
       <c r="M230" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R230" t="str">
@@ -7430,7 +7468,7 @@
     </row>
     <row r="231" spans="13:21">
       <c r="M231" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R231" t="str">
@@ -7452,7 +7490,7 @@
     </row>
     <row r="232" spans="13:21">
       <c r="M232" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R232" t="str">
@@ -7474,7 +7512,7 @@
     </row>
     <row r="233" spans="13:21">
       <c r="M233" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R233" t="str">
@@ -7496,7 +7534,7 @@
     </row>
     <row r="234" spans="13:21">
       <c r="M234" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R234" t="str">
@@ -7518,7 +7556,7 @@
     </row>
     <row r="235" spans="13:21">
       <c r="M235" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R235" t="str">
@@ -7540,7 +7578,7 @@
     </row>
     <row r="236" spans="13:21">
       <c r="M236" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R236" t="str">
@@ -7562,7 +7600,7 @@
     </row>
     <row r="237" spans="13:21">
       <c r="M237" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R237" t="str">
@@ -7584,7 +7622,7 @@
     </row>
     <row r="238" spans="13:21">
       <c r="M238" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R238" t="str">
@@ -7606,7 +7644,7 @@
     </row>
     <row r="239" spans="13:21">
       <c r="M239" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R239" t="str">
@@ -7628,7 +7666,7 @@
     </row>
     <row r="240" spans="13:21">
       <c r="M240" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R240" t="str">
@@ -7650,7 +7688,7 @@
     </row>
     <row r="241" spans="13:21">
       <c r="M241" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R241" t="str">
@@ -7672,7 +7710,7 @@
     </row>
     <row r="242" spans="13:21">
       <c r="M242" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R242" t="str">
@@ -7694,7 +7732,7 @@
     </row>
     <row r="243" spans="13:21">
       <c r="M243" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R243" t="str">
@@ -7716,7 +7754,7 @@
     </row>
     <row r="244" spans="13:21">
       <c r="M244" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R244" t="str">
@@ -7738,7 +7776,7 @@
     </row>
     <row r="245" spans="13:21">
       <c r="M245" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R245" t="str">
@@ -7760,7 +7798,7 @@
     </row>
     <row r="246" spans="13:21">
       <c r="M246" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R246" t="str">
@@ -7782,7 +7820,7 @@
     </row>
     <row r="247" spans="13:21">
       <c r="M247" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R247" t="str">
@@ -7804,7 +7842,7 @@
     </row>
     <row r="248" spans="13:21">
       <c r="M248" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R248" t="str">
@@ -7826,7 +7864,7 @@
     </row>
     <row r="249" spans="13:21">
       <c r="M249" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R249" t="str">
@@ -7848,7 +7886,7 @@
     </row>
     <row r="250" spans="13:21">
       <c r="M250" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R250" t="str">
@@ -7870,7 +7908,7 @@
     </row>
     <row r="251" spans="13:21">
       <c r="M251" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R251" t="str">
@@ -7892,7 +7930,7 @@
     </row>
     <row r="252" spans="13:21">
       <c r="M252" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R252" t="str">
@@ -7914,7 +7952,7 @@
     </row>
     <row r="253" spans="13:21">
       <c r="M253" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R253" t="str">
@@ -7936,7 +7974,7 @@
     </row>
     <row r="254" spans="13:21">
       <c r="M254" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R254" t="str">
@@ -7958,7 +7996,7 @@
     </row>
     <row r="255" spans="13:21">
       <c r="M255" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R255" t="str">
@@ -7980,7 +8018,7 @@
     </row>
     <row r="256" spans="13:21">
       <c r="M256" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R256" t="str">
@@ -8002,7 +8040,7 @@
     </row>
     <row r="257" spans="13:21">
       <c r="M257" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R257" t="str">
@@ -8024,7 +8062,7 @@
     </row>
     <row r="258" spans="13:21">
       <c r="M258" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R258" t="str">
@@ -8046,7 +8084,7 @@
     </row>
     <row r="259" spans="13:21">
       <c r="M259" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R259" t="str">
@@ -8068,7 +8106,7 @@
     </row>
     <row r="260" spans="13:21">
       <c r="M260" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R260" t="str">
@@ -8090,7 +8128,7 @@
     </row>
     <row r="261" spans="13:21">
       <c r="M261" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R261" t="str">
@@ -8112,7 +8150,7 @@
     </row>
     <row r="262" spans="13:21">
       <c r="M262" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R262" t="str">
@@ -8134,7 +8172,7 @@
     </row>
     <row r="263" spans="13:21">
       <c r="M263" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R263" t="str">
@@ -8156,7 +8194,7 @@
     </row>
     <row r="264" spans="13:21">
       <c r="M264" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R264" t="str">
@@ -8178,7 +8216,7 @@
     </row>
     <row r="265" spans="13:21">
       <c r="M265" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R265" t="str">
@@ -8200,7 +8238,7 @@
     </row>
     <row r="266" spans="13:21">
       <c r="M266" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R266" t="str">
@@ -8222,7 +8260,7 @@
     </row>
     <row r="267" spans="13:21">
       <c r="M267" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R267" t="str">
@@ -8244,7 +8282,7 @@
     </row>
     <row r="268" spans="13:21">
       <c r="M268" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R268" t="str">
@@ -8266,7 +8304,7 @@
     </row>
     <row r="269" spans="13:21">
       <c r="M269" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R269" t="str">
@@ -8288,7 +8326,7 @@
     </row>
     <row r="270" spans="13:21">
       <c r="M270" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R270" t="str">
@@ -8310,7 +8348,7 @@
     </row>
     <row r="271" spans="13:21">
       <c r="M271" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R271" t="str">
@@ -8332,7 +8370,7 @@
     </row>
     <row r="272" spans="13:21">
       <c r="M272" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R272" t="str">
@@ -8354,7 +8392,7 @@
     </row>
     <row r="273" spans="13:21">
       <c r="M273" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R273" t="str">
@@ -8376,7 +8414,7 @@
     </row>
     <row r="274" spans="13:21">
       <c r="M274" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R274" t="str">
@@ -8398,7 +8436,7 @@
     </row>
     <row r="275" spans="13:21">
       <c r="M275" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R275" t="str">
@@ -8420,7 +8458,7 @@
     </row>
     <row r="276" spans="13:21">
       <c r="M276" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R276" t="str">
@@ -8442,7 +8480,7 @@
     </row>
     <row r="277" spans="13:21">
       <c r="M277" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R277" t="str">
@@ -8464,7 +8502,7 @@
     </row>
     <row r="278" spans="13:21">
       <c r="M278" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R278" t="str">
@@ -8486,7 +8524,7 @@
     </row>
     <row r="279" spans="13:21">
       <c r="M279" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R279" t="str">
@@ -8508,7 +8546,7 @@
     </row>
     <row r="280" spans="13:21">
       <c r="M280" s="22" t="str">
-        <f t="shared" ref="M280:M343" si="7">IF(F280="CJ", I280*200, "")</f>
+        <f t="shared" ref="M280:M343" si="8">IF(F280="CJ", I280*200, "")</f>
         <v/>
       </c>
       <c r="R280" t="str">
@@ -8530,7 +8568,7 @@
     </row>
     <row r="281" spans="13:21">
       <c r="M281" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R281" t="str">
@@ -8552,7 +8590,7 @@
     </row>
     <row r="282" spans="13:21">
       <c r="M282" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R282" t="str">
@@ -8574,7 +8612,7 @@
     </row>
     <row r="283" spans="13:21">
       <c r="M283" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R283" t="str">
@@ -8596,7 +8634,7 @@
     </row>
     <row r="284" spans="13:21">
       <c r="M284" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R284" t="str">
@@ -8618,7 +8656,7 @@
     </row>
     <row r="285" spans="13:21">
       <c r="M285" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R285" t="str">
@@ -8640,7 +8678,7 @@
     </row>
     <row r="286" spans="13:21">
       <c r="M286" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R286" t="str">
@@ -8662,7 +8700,7 @@
     </row>
     <row r="287" spans="13:21">
       <c r="M287" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R287" t="str">
@@ -8684,7 +8722,7 @@
     </row>
     <row r="288" spans="13:21">
       <c r="M288" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R288" t="str">
@@ -8706,7 +8744,7 @@
     </row>
     <row r="289" spans="13:21">
       <c r="M289" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R289" t="str">
@@ -8728,7 +8766,7 @@
     </row>
     <row r="290" spans="13:21">
       <c r="M290" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R290" t="str">
@@ -8750,7 +8788,7 @@
     </row>
     <row r="291" spans="13:21">
       <c r="M291" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R291" t="str">
@@ -8772,7 +8810,7 @@
     </row>
     <row r="292" spans="13:21">
       <c r="M292" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R292" t="str">
@@ -8794,7 +8832,7 @@
     </row>
     <row r="293" spans="13:21">
       <c r="M293" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R293" t="str">
@@ -8816,7 +8854,7 @@
     </row>
     <row r="294" spans="13:21">
       <c r="M294" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R294" t="str">
@@ -8838,7 +8876,7 @@
     </row>
     <row r="295" spans="13:21">
       <c r="M295" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R295" t="str">
@@ -8860,7 +8898,7 @@
     </row>
     <row r="296" spans="13:21">
       <c r="M296" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R296" t="str">
@@ -8882,7 +8920,7 @@
     </row>
     <row r="297" spans="13:21">
       <c r="M297" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R297" t="str">
@@ -8904,7 +8942,7 @@
     </row>
     <row r="298" spans="13:21">
       <c r="M298" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R298" t="str">
@@ -8926,7 +8964,7 @@
     </row>
     <row r="299" spans="13:21">
       <c r="M299" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R299" t="str">
@@ -8948,7 +8986,7 @@
     </row>
     <row r="300" spans="13:21">
       <c r="M300" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R300" t="str">
@@ -8970,7 +9008,7 @@
     </row>
     <row r="301" spans="13:21">
       <c r="M301" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R301" t="str">
@@ -8992,7 +9030,7 @@
     </row>
     <row r="302" spans="13:21">
       <c r="M302" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R302" t="str">
@@ -9014,7 +9052,7 @@
     </row>
     <row r="303" spans="13:21">
       <c r="M303" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R303" t="str">
@@ -9036,7 +9074,7 @@
     </row>
     <row r="304" spans="13:21">
       <c r="M304" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R304" t="str">
@@ -9058,7 +9096,7 @@
     </row>
     <row r="305" spans="13:21">
       <c r="M305" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R305" t="str">
@@ -9080,7 +9118,7 @@
     </row>
     <row r="306" spans="13:21">
       <c r="M306" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R306" t="str">
@@ -9102,7 +9140,7 @@
     </row>
     <row r="307" spans="13:21">
       <c r="M307" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R307" t="str">
@@ -9124,7 +9162,7 @@
     </row>
     <row r="308" spans="13:21">
       <c r="M308" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R308" t="str">
@@ -9146,7 +9184,7 @@
     </row>
     <row r="309" spans="13:21">
       <c r="M309" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R309" t="str">
@@ -9168,7 +9206,7 @@
     </row>
     <row r="310" spans="13:21">
       <c r="M310" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R310" t="str">
@@ -9190,7 +9228,7 @@
     </row>
     <row r="311" spans="13:21">
       <c r="M311" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R311" t="str">
@@ -9212,7 +9250,7 @@
     </row>
     <row r="312" spans="13:21">
       <c r="M312" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R312" t="str">
@@ -9234,7 +9272,7 @@
     </row>
     <row r="313" spans="13:21">
       <c r="M313" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R313" t="str">
@@ -9256,7 +9294,7 @@
     </row>
     <row r="314" spans="13:21">
       <c r="M314" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R314" t="str">
@@ -9278,7 +9316,7 @@
     </row>
     <row r="315" spans="13:21">
       <c r="M315" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R315" t="str">
@@ -9300,7 +9338,7 @@
     </row>
     <row r="316" spans="13:21">
       <c r="M316" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R316" t="str">
@@ -9322,7 +9360,7 @@
     </row>
     <row r="317" spans="13:21">
       <c r="M317" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R317" t="str">
@@ -9344,7 +9382,7 @@
     </row>
     <row r="318" spans="13:21">
       <c r="M318" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R318" t="str">
@@ -9366,7 +9404,7 @@
     </row>
     <row r="319" spans="13:21">
       <c r="M319" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R319" t="str">
@@ -9388,7 +9426,7 @@
     </row>
     <row r="320" spans="13:21">
       <c r="M320" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R320" t="str">
@@ -9410,7 +9448,7 @@
     </row>
     <row r="321" spans="13:21">
       <c r="M321" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R321" t="str">
@@ -9432,7 +9470,7 @@
     </row>
     <row r="322" spans="13:21">
       <c r="M322" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R322" t="str">
@@ -9454,7 +9492,7 @@
     </row>
     <row r="323" spans="13:21">
       <c r="M323" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R323" t="str">
@@ -9476,7 +9514,7 @@
     </row>
     <row r="324" spans="13:21">
       <c r="M324" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R324" t="str">
@@ -9498,7 +9536,7 @@
     </row>
     <row r="325" spans="13:21">
       <c r="M325" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R325" t="str">
@@ -9520,7 +9558,7 @@
     </row>
     <row r="326" spans="13:21">
       <c r="M326" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R326" t="str">
@@ -9542,7 +9580,7 @@
     </row>
     <row r="327" spans="13:21">
       <c r="M327" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R327" t="str">
@@ -9564,7 +9602,7 @@
     </row>
     <row r="328" spans="13:21">
       <c r="M328" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R328" t="str">
@@ -9586,7 +9624,7 @@
     </row>
     <row r="329" spans="13:21">
       <c r="M329" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R329" t="str">
@@ -9608,7 +9646,7 @@
     </row>
     <row r="330" spans="13:21">
       <c r="M330" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R330" t="str">
@@ -9630,7 +9668,7 @@
     </row>
     <row r="331" spans="13:21">
       <c r="M331" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R331" t="str">
@@ -9652,7 +9690,7 @@
     </row>
     <row r="332" spans="13:21">
       <c r="M332" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R332" t="str">
@@ -9674,7 +9712,7 @@
     </row>
     <row r="333" spans="13:21">
       <c r="M333" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R333" t="str">
@@ -9696,7 +9734,7 @@
     </row>
     <row r="334" spans="13:21">
       <c r="M334" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R334" t="str">
@@ -9718,7 +9756,7 @@
     </row>
     <row r="335" spans="13:21">
       <c r="M335" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R335" t="str">
@@ -9740,7 +9778,7 @@
     </row>
     <row r="336" spans="13:21">
       <c r="M336" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R336" t="str">
@@ -9762,7 +9800,7 @@
     </row>
     <row r="337" spans="13:21">
       <c r="M337" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R337" t="str">
@@ -9784,7 +9822,7 @@
     </row>
     <row r="338" spans="13:21">
       <c r="M338" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R338" t="str">
@@ -9806,7 +9844,7 @@
     </row>
     <row r="339" spans="13:21">
       <c r="M339" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R339" t="str">
@@ -9828,7 +9866,7 @@
     </row>
     <row r="340" spans="13:21">
       <c r="M340" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R340" t="str">
@@ -9850,7 +9888,7 @@
     </row>
     <row r="341" spans="13:21">
       <c r="M341" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R341" t="str">
@@ -9872,7 +9910,7 @@
     </row>
     <row r="342" spans="13:21">
       <c r="M342" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R342" t="str">
@@ -9894,7 +9932,7 @@
     </row>
     <row r="343" spans="13:21">
       <c r="M343" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R343" t="str">
@@ -9916,7 +9954,7 @@
     </row>
     <row r="344" spans="13:21">
       <c r="M344" s="22" t="str">
-        <f t="shared" ref="M344:M407" si="8">IF(F344="CJ", I344*200, "")</f>
+        <f t="shared" ref="M344:M407" si="9">IF(F344="CJ", I344*200, "")</f>
         <v/>
       </c>
       <c r="R344" t="str">
@@ -9938,7 +9976,7 @@
     </row>
     <row r="345" spans="13:21">
       <c r="M345" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R345" t="str">
@@ -9960,7 +9998,7 @@
     </row>
     <row r="346" spans="13:21">
       <c r="M346" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R346" t="str">
@@ -9982,7 +10020,7 @@
     </row>
     <row r="347" spans="13:21">
       <c r="M347" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R347" t="str">
@@ -10004,7 +10042,7 @@
     </row>
     <row r="348" spans="13:21">
       <c r="M348" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R348" t="str">
@@ -10026,7 +10064,7 @@
     </row>
     <row r="349" spans="13:21">
       <c r="M349" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R349" t="str">
@@ -10048,7 +10086,7 @@
     </row>
     <row r="350" spans="13:21">
       <c r="M350" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R350" t="str">
@@ -10070,7 +10108,7 @@
     </row>
     <row r="351" spans="13:21">
       <c r="M351" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R351" t="str">
@@ -10092,7 +10130,7 @@
     </row>
     <row r="352" spans="13:21">
       <c r="M352" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R352" t="str">
@@ -10114,7 +10152,7 @@
     </row>
     <row r="353" spans="13:21">
       <c r="M353" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R353" t="str">
@@ -10136,7 +10174,7 @@
     </row>
     <row r="354" spans="13:21">
       <c r="M354" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R354" t="str">
@@ -10158,7 +10196,7 @@
     </row>
     <row r="355" spans="13:21">
       <c r="M355" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R355" t="str">
@@ -10180,7 +10218,7 @@
     </row>
     <row r="356" spans="13:21">
       <c r="M356" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R356" t="str">
@@ -10202,7 +10240,7 @@
     </row>
     <row r="357" spans="13:21">
       <c r="M357" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R357" t="str">
@@ -10224,7 +10262,7 @@
     </row>
     <row r="358" spans="13:21">
       <c r="M358" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R358" t="str">
@@ -10246,7 +10284,7 @@
     </row>
     <row r="359" spans="13:21">
       <c r="M359" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R359" t="str">
@@ -10268,7 +10306,7 @@
     </row>
     <row r="360" spans="13:21">
       <c r="M360" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R360" t="str">
@@ -10290,7 +10328,7 @@
     </row>
     <row r="361" spans="13:21">
       <c r="M361" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R361" t="str">
@@ -10312,7 +10350,7 @@
     </row>
     <row r="362" spans="13:21">
       <c r="M362" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R362" t="str">
@@ -10334,7 +10372,7 @@
     </row>
     <row r="363" spans="13:21">
       <c r="M363" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R363" t="str">
@@ -10356,7 +10394,7 @@
     </row>
     <row r="364" spans="13:21">
       <c r="M364" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R364" t="str">
@@ -10378,7 +10416,7 @@
     </row>
     <row r="365" spans="13:21">
       <c r="M365" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R365" t="str">
@@ -10400,7 +10438,7 @@
     </row>
     <row r="366" spans="13:21">
       <c r="M366" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R366" t="str">
@@ -10422,7 +10460,7 @@
     </row>
     <row r="367" spans="13:21">
       <c r="M367" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R367" t="str">
@@ -10444,7 +10482,7 @@
     </row>
     <row r="368" spans="13:21">
       <c r="M368" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R368" t="str">
@@ -10466,7 +10504,7 @@
     </row>
     <row r="369" spans="13:21">
       <c r="M369" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R369" t="str">
@@ -10488,7 +10526,7 @@
     </row>
     <row r="370" spans="13:21">
       <c r="M370" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R370" t="str">
@@ -10510,7 +10548,7 @@
     </row>
     <row r="371" spans="13:21">
       <c r="M371" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R371" t="str">
@@ -10532,7 +10570,7 @@
     </row>
     <row r="372" spans="13:21">
       <c r="M372" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R372" t="str">
@@ -10554,7 +10592,7 @@
     </row>
     <row r="373" spans="13:21">
       <c r="M373" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R373" t="str">
@@ -10576,7 +10614,7 @@
     </row>
     <row r="374" spans="13:21">
       <c r="M374" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R374" t="str">
@@ -10598,7 +10636,7 @@
     </row>
     <row r="375" spans="13:21">
       <c r="M375" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R375" t="str">
@@ -10620,7 +10658,7 @@
     </row>
     <row r="376" spans="13:21">
       <c r="M376" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R376" t="str">
@@ -10642,7 +10680,7 @@
     </row>
     <row r="377" spans="13:21">
       <c r="M377" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R377" t="str">
@@ -10664,7 +10702,7 @@
     </row>
     <row r="378" spans="13:21">
       <c r="M378" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R378" t="str">
@@ -10686,7 +10724,7 @@
     </row>
     <row r="379" spans="13:21">
       <c r="M379" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R379" t="str">
@@ -10708,7 +10746,7 @@
     </row>
     <row r="380" spans="13:21">
       <c r="M380" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R380" t="str">
@@ -10730,7 +10768,7 @@
     </row>
     <row r="381" spans="13:21">
       <c r="M381" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R381" t="str">
@@ -10752,7 +10790,7 @@
     </row>
     <row r="382" spans="13:21">
       <c r="M382" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R382" t="str">
@@ -10774,7 +10812,7 @@
     </row>
     <row r="383" spans="13:21">
       <c r="M383" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R383" t="str">
@@ -10796,7 +10834,7 @@
     </row>
     <row r="384" spans="13:21">
       <c r="M384" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R384" t="str">
@@ -10818,7 +10856,7 @@
     </row>
     <row r="385" spans="13:21">
       <c r="M385" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R385" t="str">
@@ -10840,7 +10878,7 @@
     </row>
     <row r="386" spans="13:21">
       <c r="M386" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R386" t="str">
@@ -10862,7 +10900,7 @@
     </row>
     <row r="387" spans="13:21">
       <c r="M387" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R387" t="str">
@@ -10884,7 +10922,7 @@
     </row>
     <row r="388" spans="13:21">
       <c r="M388" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R388" t="str">
@@ -10906,7 +10944,7 @@
     </row>
     <row r="389" spans="13:21">
       <c r="M389" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R389" t="str">
@@ -10928,7 +10966,7 @@
     </row>
     <row r="390" spans="13:21">
       <c r="M390" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R390" t="str">
@@ -10950,7 +10988,7 @@
     </row>
     <row r="391" spans="13:21">
       <c r="M391" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R391" t="str">
@@ -10972,7 +11010,7 @@
     </row>
     <row r="392" spans="13:21">
       <c r="M392" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R392" t="str">
@@ -10994,7 +11032,7 @@
     </row>
     <row r="393" spans="13:21">
       <c r="M393" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R393" t="str">
@@ -11016,7 +11054,7 @@
     </row>
     <row r="394" spans="13:21">
       <c r="M394" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R394" t="str">
@@ -11038,7 +11076,7 @@
     </row>
     <row r="395" spans="13:21">
       <c r="M395" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R395" t="str">
@@ -11060,7 +11098,7 @@
     </row>
     <row r="396" spans="13:21">
       <c r="M396" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R396" t="str">
@@ -11082,7 +11120,7 @@
     </row>
     <row r="397" spans="13:21">
       <c r="M397" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R397" t="str">
@@ -11104,7 +11142,7 @@
     </row>
     <row r="398" spans="13:21">
       <c r="M398" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R398" t="str">
@@ -11126,7 +11164,7 @@
     </row>
     <row r="399" spans="13:21">
       <c r="M399" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R399" t="str">
@@ -11148,7 +11186,7 @@
     </row>
     <row r="400" spans="13:21">
       <c r="M400" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R400" t="str">
@@ -11170,7 +11208,7 @@
     </row>
     <row r="401" spans="13:21">
       <c r="M401" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R401" t="str">
@@ -11192,7 +11230,7 @@
     </row>
     <row r="402" spans="13:21">
       <c r="M402" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R402" t="str">
@@ -11214,7 +11252,7 @@
     </row>
     <row r="403" spans="13:21">
       <c r="M403" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R403" t="str">
@@ -11236,7 +11274,7 @@
     </row>
     <row r="404" spans="13:21">
       <c r="M404" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R404" t="str">
@@ -11258,7 +11296,7 @@
     </row>
     <row r="405" spans="13:21">
       <c r="M405" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R405" t="str">
@@ -11280,7 +11318,7 @@
     </row>
     <row r="406" spans="13:21">
       <c r="M406" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R406" t="str">
@@ -11302,7 +11340,7 @@
     </row>
     <row r="407" spans="13:21">
       <c r="M407" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R407" t="str">
@@ -11324,7 +11362,7 @@
     </row>
     <row r="408" spans="13:21">
       <c r="M408" s="22" t="str">
-        <f t="shared" ref="M408:M471" si="9">IF(F408="CJ", I408*200, "")</f>
+        <f t="shared" ref="M408:M471" si="10">IF(F408="CJ", I408*200, "")</f>
         <v/>
       </c>
       <c r="R408" t="str">
@@ -11346,7 +11384,7 @@
     </row>
     <row r="409" spans="13:21">
       <c r="M409" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R409" t="str">
@@ -11368,7 +11406,7 @@
     </row>
     <row r="410" spans="13:21">
       <c r="M410" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R410" t="str">
@@ -11390,7 +11428,7 @@
     </row>
     <row r="411" spans="13:21">
       <c r="M411" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R411" t="str">
@@ -11412,7 +11450,7 @@
     </row>
     <row r="412" spans="13:21">
       <c r="M412" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R412" t="str">
@@ -11434,7 +11472,7 @@
     </row>
     <row r="413" spans="13:21">
       <c r="M413" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R413" t="str">
@@ -11456,7 +11494,7 @@
     </row>
     <row r="414" spans="13:21">
       <c r="M414" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R414" t="str">
@@ -11478,7 +11516,7 @@
     </row>
     <row r="415" spans="13:21">
       <c r="M415" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R415" t="str">
@@ -11500,7 +11538,7 @@
     </row>
     <row r="416" spans="13:21">
       <c r="M416" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R416" t="str">
@@ -11522,7 +11560,7 @@
     </row>
     <row r="417" spans="13:21">
       <c r="M417" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R417" t="str">
@@ -11544,7 +11582,7 @@
     </row>
     <row r="418" spans="13:21">
       <c r="M418" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R418" t="str">
@@ -11566,7 +11604,7 @@
     </row>
     <row r="419" spans="13:21">
       <c r="M419" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R419" t="str">
@@ -11588,7 +11626,7 @@
     </row>
     <row r="420" spans="13:21">
       <c r="M420" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R420" t="str">
@@ -11610,7 +11648,7 @@
     </row>
     <row r="421" spans="13:21">
       <c r="M421" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R421" t="str">
@@ -11632,7 +11670,7 @@
     </row>
     <row r="422" spans="13:21">
       <c r="M422" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R422" t="str">
@@ -11654,7 +11692,7 @@
     </row>
     <row r="423" spans="13:21">
       <c r="M423" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R423" t="str">
@@ -11676,7 +11714,7 @@
     </row>
     <row r="424" spans="13:21">
       <c r="M424" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R424" t="str">
@@ -11698,7 +11736,7 @@
     </row>
     <row r="425" spans="13:21">
       <c r="M425" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R425" t="str">
@@ -11720,7 +11758,7 @@
     </row>
     <row r="426" spans="13:21">
       <c r="M426" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R426" t="str">
@@ -11742,7 +11780,7 @@
     </row>
     <row r="427" spans="13:21">
       <c r="M427" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R427" t="str">
@@ -11764,7 +11802,7 @@
     </row>
     <row r="428" spans="13:21">
       <c r="M428" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R428" t="str">
@@ -11786,7 +11824,7 @@
     </row>
     <row r="429" spans="13:21">
       <c r="M429" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R429" t="str">
@@ -11808,7 +11846,7 @@
     </row>
     <row r="430" spans="13:21">
       <c r="M430" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R430" t="str">
@@ -11830,7 +11868,7 @@
     </row>
     <row r="431" spans="13:21">
       <c r="M431" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R431" t="str">
@@ -11852,7 +11890,7 @@
     </row>
     <row r="432" spans="13:21">
       <c r="M432" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R432" t="str">
@@ -11874,7 +11912,7 @@
     </row>
     <row r="433" spans="13:21">
       <c r="M433" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R433" t="str">
@@ -11896,7 +11934,7 @@
     </row>
     <row r="434" spans="13:21">
       <c r="M434" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R434" t="str">
@@ -11918,7 +11956,7 @@
     </row>
     <row r="435" spans="13:21">
       <c r="M435" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R435" t="str">
@@ -11940,7 +11978,7 @@
     </row>
     <row r="436" spans="13:21">
       <c r="M436" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R436" t="str">
@@ -11962,7 +12000,7 @@
     </row>
     <row r="437" spans="13:21">
       <c r="M437" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R437" t="str">
@@ -11984,7 +12022,7 @@
     </row>
     <row r="438" spans="13:21">
       <c r="M438" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R438" t="str">
@@ -12006,7 +12044,7 @@
     </row>
     <row r="439" spans="13:21">
       <c r="M439" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R439" t="str">
@@ -12028,7 +12066,7 @@
     </row>
     <row r="440" spans="13:21">
       <c r="M440" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R440" t="str">
@@ -12050,7 +12088,7 @@
     </row>
     <row r="441" spans="13:21">
       <c r="M441" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R441" t="str">
@@ -12072,7 +12110,7 @@
     </row>
     <row r="442" spans="13:21">
       <c r="M442" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R442" t="str">
@@ -12094,7 +12132,7 @@
     </row>
     <row r="443" spans="13:21">
       <c r="M443" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R443" t="str">
@@ -12116,7 +12154,7 @@
     </row>
     <row r="444" spans="13:21">
       <c r="M444" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R444" t="str">
@@ -12138,7 +12176,7 @@
     </row>
     <row r="445" spans="13:21">
       <c r="M445" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R445" t="str">
@@ -12160,7 +12198,7 @@
     </row>
     <row r="446" spans="13:21">
       <c r="M446" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R446" t="str">
@@ -12182,7 +12220,7 @@
     </row>
     <row r="447" spans="13:21">
       <c r="M447" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R447" t="str">
@@ -12204,7 +12242,7 @@
     </row>
     <row r="448" spans="13:21">
       <c r="M448" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R448" t="str">
@@ -12226,7 +12264,7 @@
     </row>
     <row r="449" spans="13:21">
       <c r="M449" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R449" t="str">
@@ -12248,7 +12286,7 @@
     </row>
     <row r="450" spans="13:21">
       <c r="M450" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R450" t="str">
@@ -12270,7 +12308,7 @@
     </row>
     <row r="451" spans="13:21">
       <c r="M451" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R451" t="str">
@@ -12292,7 +12330,7 @@
     </row>
     <row r="452" spans="13:21">
       <c r="M452" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R452" t="str">
@@ -12314,7 +12352,7 @@
     </row>
     <row r="453" spans="13:21">
       <c r="M453" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R453" t="str">
@@ -12336,7 +12374,7 @@
     </row>
     <row r="454" spans="13:21">
       <c r="M454" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R454" t="str">
@@ -12358,7 +12396,7 @@
     </row>
     <row r="455" spans="13:21">
       <c r="M455" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R455" t="str">
@@ -12380,7 +12418,7 @@
     </row>
     <row r="456" spans="13:21">
       <c r="M456" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R456" t="str">
@@ -12402,7 +12440,7 @@
     </row>
     <row r="457" spans="13:21">
       <c r="M457" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R457" t="str">
@@ -12424,7 +12462,7 @@
     </row>
     <row r="458" spans="13:21">
       <c r="M458" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R458" t="str">
@@ -12446,7 +12484,7 @@
     </row>
     <row r="459" spans="13:21">
       <c r="M459" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R459" t="str">
@@ -12468,7 +12506,7 @@
     </row>
     <row r="460" spans="13:21">
       <c r="M460" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R460" t="str">
@@ -12490,7 +12528,7 @@
     </row>
     <row r="461" spans="13:21">
       <c r="M461" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R461" t="str">
@@ -12512,7 +12550,7 @@
     </row>
     <row r="462" spans="13:21">
       <c r="M462" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R462" t="str">
@@ -12534,7 +12572,7 @@
     </row>
     <row r="463" spans="13:21">
       <c r="M463" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R463" t="str">
@@ -12556,7 +12594,7 @@
     </row>
     <row r="464" spans="13:21">
       <c r="M464" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R464" t="str">
@@ -12578,7 +12616,7 @@
     </row>
     <row r="465" spans="13:21">
       <c r="M465" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R465" t="str">
@@ -12600,7 +12638,7 @@
     </row>
     <row r="466" spans="13:21">
       <c r="M466" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R466" t="str">
@@ -12622,7 +12660,7 @@
     </row>
     <row r="467" spans="13:21">
       <c r="M467" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R467" t="str">
@@ -12644,7 +12682,7 @@
     </row>
     <row r="468" spans="13:21">
       <c r="M468" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R468" t="str">
@@ -12666,7 +12704,7 @@
     </row>
     <row r="469" spans="13:21">
       <c r="M469" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R469" t="str">
@@ -12688,7 +12726,7 @@
     </row>
     <row r="470" spans="13:21">
       <c r="M470" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R470" t="str">
@@ -12710,7 +12748,7 @@
     </row>
     <row r="471" spans="13:21">
       <c r="M471" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R471" t="str">
@@ -12732,7 +12770,7 @@
     </row>
     <row r="472" spans="13:21">
       <c r="M472" s="22" t="str">
-        <f t="shared" ref="M472:M535" si="10">IF(F472="CJ", I472*200, "")</f>
+        <f t="shared" ref="M472:M535" si="11">IF(F472="CJ", I472*200, "")</f>
         <v/>
       </c>
       <c r="R472" t="str">
@@ -12754,7 +12792,7 @@
     </row>
     <row r="473" spans="13:21">
       <c r="M473" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R473" t="str">
@@ -12776,7 +12814,7 @@
     </row>
     <row r="474" spans="13:21">
       <c r="M474" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R474" t="str">
@@ -12798,7 +12836,7 @@
     </row>
     <row r="475" spans="13:21">
       <c r="M475" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R475" t="str">
@@ -12820,7 +12858,7 @@
     </row>
     <row r="476" spans="13:21">
       <c r="M476" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R476" t="str">
@@ -12842,7 +12880,7 @@
     </row>
     <row r="477" spans="13:21">
       <c r="M477" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R477" t="str">
@@ -12864,7 +12902,7 @@
     </row>
     <row r="478" spans="13:21">
       <c r="M478" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R478" t="str">
@@ -12886,7 +12924,7 @@
     </row>
     <row r="479" spans="13:21">
       <c r="M479" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R479" t="str">
@@ -12908,7 +12946,7 @@
     </row>
     <row r="480" spans="13:21">
       <c r="M480" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R480" t="str">
@@ -12930,7 +12968,7 @@
     </row>
     <row r="481" spans="13:21">
       <c r="M481" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R481" t="str">
@@ -12952,7 +12990,7 @@
     </row>
     <row r="482" spans="13:21">
       <c r="M482" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R482" t="str">
@@ -12974,7 +13012,7 @@
     </row>
     <row r="483" spans="13:21">
       <c r="M483" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R483" t="str">
@@ -12996,7 +13034,7 @@
     </row>
     <row r="484" spans="13:21">
       <c r="M484" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R484" t="str">
@@ -13018,7 +13056,7 @@
     </row>
     <row r="485" spans="13:21">
       <c r="M485" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R485" t="str">
@@ -13040,7 +13078,7 @@
     </row>
     <row r="486" spans="13:21">
       <c r="M486" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R486" t="str">
@@ -13062,7 +13100,7 @@
     </row>
     <row r="487" spans="13:21">
       <c r="M487" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R487" t="str">
@@ -13084,7 +13122,7 @@
     </row>
     <row r="488" spans="13:21">
       <c r="M488" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R488" t="str">
@@ -13106,7 +13144,7 @@
     </row>
     <row r="489" spans="13:21">
       <c r="M489" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R489" t="str">
@@ -13128,7 +13166,7 @@
     </row>
     <row r="490" spans="13:21">
       <c r="M490" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R490" t="str">
@@ -13150,7 +13188,7 @@
     </row>
     <row r="491" spans="13:21">
       <c r="M491" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R491" t="str">
@@ -13172,7 +13210,7 @@
     </row>
     <row r="492" spans="13:21">
       <c r="M492" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R492" t="str">
@@ -13194,7 +13232,7 @@
     </row>
     <row r="493" spans="13:21">
       <c r="M493" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R493" t="str">
@@ -13216,7 +13254,7 @@
     </row>
     <row r="494" spans="13:21">
       <c r="M494" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R494" t="str">
@@ -13238,7 +13276,7 @@
     </row>
     <row r="495" spans="13:21">
       <c r="M495" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R495" t="str">
@@ -13260,7 +13298,7 @@
     </row>
     <row r="496" spans="13:21">
       <c r="M496" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R496" t="str">
@@ -13282,7 +13320,7 @@
     </row>
     <row r="497" spans="13:21">
       <c r="M497" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R497" t="str">
@@ -13304,7 +13342,7 @@
     </row>
     <row r="498" spans="13:21">
       <c r="M498" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R498" t="str">
@@ -13326,7 +13364,7 @@
     </row>
     <row r="499" spans="13:21">
       <c r="M499" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R499" t="str">
@@ -13348,7 +13386,7 @@
     </row>
     <row r="500" spans="13:21">
       <c r="M500" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R500" t="str">
@@ -13370,7 +13408,7 @@
     </row>
     <row r="501" spans="13:21">
       <c r="M501" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R501" t="str">
@@ -13392,7 +13430,7 @@
     </row>
     <row r="502" spans="13:21">
       <c r="M502" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R502" t="str">
@@ -13414,7 +13452,7 @@
     </row>
     <row r="503" spans="13:21">
       <c r="M503" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R503" t="str">
@@ -13436,7 +13474,7 @@
     </row>
     <row r="504" spans="13:21">
       <c r="M504" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R504" t="str">
@@ -13458,7 +13496,7 @@
     </row>
     <row r="505" spans="13:21">
       <c r="M505" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R505" t="str">
@@ -13480,7 +13518,7 @@
     </row>
     <row r="506" spans="13:21">
       <c r="M506" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R506" t="str">
@@ -13502,7 +13540,7 @@
     </row>
     <row r="507" spans="13:21">
       <c r="M507" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R507" t="str">
@@ -13524,7 +13562,7 @@
     </row>
     <row r="508" spans="13:21">
       <c r="M508" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R508" t="str">
@@ -13546,7 +13584,7 @@
     </row>
     <row r="509" spans="13:21">
       <c r="M509" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R509" t="str">
@@ -13568,7 +13606,7 @@
     </row>
     <row r="510" spans="13:21">
       <c r="M510" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R510" t="str">
@@ -13590,7 +13628,7 @@
     </row>
     <row r="511" spans="13:21">
       <c r="M511" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R511" t="str">
@@ -13612,7 +13650,7 @@
     </row>
     <row r="512" spans="13:21">
       <c r="M512" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R512" t="str">
@@ -13634,7 +13672,7 @@
     </row>
     <row r="513" spans="13:21">
       <c r="M513" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R513" t="str">
@@ -13656,7 +13694,7 @@
     </row>
     <row r="514" spans="13:21">
       <c r="M514" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R514" t="str">
@@ -13678,7 +13716,7 @@
     </row>
     <row r="515" spans="13:21">
       <c r="M515" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R515" t="str">
@@ -13700,7 +13738,7 @@
     </row>
     <row r="516" spans="13:21">
       <c r="M516" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R516" t="str">
@@ -13722,7 +13760,7 @@
     </row>
     <row r="517" spans="13:21">
       <c r="M517" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R517" t="str">
@@ -13744,7 +13782,7 @@
     </row>
     <row r="518" spans="13:21">
       <c r="M518" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R518" t="str">
@@ -13766,7 +13804,7 @@
     </row>
     <row r="519" spans="13:21">
       <c r="M519" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R519" t="str">
@@ -13788,7 +13826,7 @@
     </row>
     <row r="520" spans="13:21">
       <c r="M520" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R520" t="str">
@@ -13810,7 +13848,7 @@
     </row>
     <row r="521" spans="13:21">
       <c r="M521" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R521" t="str">
@@ -13832,7 +13870,7 @@
     </row>
     <row r="522" spans="13:21">
       <c r="M522" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R522" t="str">
@@ -13854,7 +13892,7 @@
     </row>
     <row r="523" spans="13:21">
       <c r="M523" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R523" t="str">
@@ -13876,7 +13914,7 @@
     </row>
     <row r="524" spans="13:21">
       <c r="M524" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R524" t="str">
@@ -13898,7 +13936,7 @@
     </row>
     <row r="525" spans="13:21">
       <c r="M525" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R525" t="str">
@@ -13920,7 +13958,7 @@
     </row>
     <row r="526" spans="13:21">
       <c r="M526" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R526" t="str">
@@ -13942,7 +13980,7 @@
     </row>
     <row r="527" spans="13:21">
       <c r="M527" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R527" t="str">
@@ -13964,7 +14002,7 @@
     </row>
     <row r="528" spans="13:21">
       <c r="M528" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R528" t="str">
@@ -13986,7 +14024,7 @@
     </row>
     <row r="529" spans="13:21">
       <c r="M529" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R529" t="str">
@@ -14008,7 +14046,7 @@
     </row>
     <row r="530" spans="13:21">
       <c r="M530" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R530" t="str">
@@ -14030,7 +14068,7 @@
     </row>
     <row r="531" spans="13:21">
       <c r="M531" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R531" t="str">
@@ -14052,7 +14090,7 @@
     </row>
     <row r="532" spans="13:21">
       <c r="M532" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R532" t="str">
@@ -14074,7 +14112,7 @@
     </row>
     <row r="533" spans="13:21">
       <c r="M533" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R533" t="str">
@@ -14096,7 +14134,7 @@
     </row>
     <row r="534" spans="13:21">
       <c r="M534" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R534" t="str">
@@ -14118,7 +14156,7 @@
     </row>
     <row r="535" spans="13:21">
       <c r="M535" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R535" t="str">
@@ -14140,7 +14178,7 @@
     </row>
     <row r="536" spans="13:21">
       <c r="M536" s="22" t="str">
-        <f t="shared" ref="M536:M599" si="11">IF(F536="CJ", I536*200, "")</f>
+        <f t="shared" ref="M536:M599" si="12">IF(F536="CJ", I536*200, "")</f>
         <v/>
       </c>
       <c r="R536" t="str">
@@ -14162,7 +14200,7 @@
     </row>
     <row r="537" spans="13:21">
       <c r="M537" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R537" t="str">
@@ -14184,7 +14222,7 @@
     </row>
     <row r="538" spans="13:21">
       <c r="M538" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R538" t="str">
@@ -14206,7 +14244,7 @@
     </row>
     <row r="539" spans="13:21">
       <c r="M539" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R539" t="str">
@@ -14228,7 +14266,7 @@
     </row>
     <row r="540" spans="13:21">
       <c r="M540" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R540" t="str">
@@ -14250,7 +14288,7 @@
     </row>
     <row r="541" spans="13:21">
       <c r="M541" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R541" t="str">
@@ -14272,7 +14310,7 @@
     </row>
     <row r="542" spans="13:21">
       <c r="M542" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R542" t="str">
@@ -14294,7 +14332,7 @@
     </row>
     <row r="543" spans="13:21">
       <c r="M543" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R543" t="str">
@@ -14316,7 +14354,7 @@
     </row>
     <row r="544" spans="13:21">
       <c r="M544" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R544" t="str">
@@ -14338,7 +14376,7 @@
     </row>
     <row r="545" spans="13:21">
       <c r="M545" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R545" t="str">
@@ -14360,7 +14398,7 @@
     </row>
     <row r="546" spans="13:21">
       <c r="M546" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R546" t="str">
@@ -14382,7 +14420,7 @@
     </row>
     <row r="547" spans="13:21">
       <c r="M547" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R547" t="str">
@@ -14404,7 +14442,7 @@
     </row>
     <row r="548" spans="13:21">
       <c r="M548" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R548" t="str">
@@ -14426,7 +14464,7 @@
     </row>
     <row r="549" spans="13:21">
       <c r="M549" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R549" t="str">
@@ -14448,7 +14486,7 @@
     </row>
     <row r="550" spans="13:21">
       <c r="M550" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R550" t="str">
@@ -14470,7 +14508,7 @@
     </row>
     <row r="551" spans="13:21">
       <c r="M551" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R551" t="str">
@@ -14492,7 +14530,7 @@
     </row>
     <row r="552" spans="13:21">
       <c r="M552" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R552" t="str">
@@ -14514,7 +14552,7 @@
     </row>
     <row r="553" spans="13:21">
       <c r="M553" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R553" t="str">
@@ -14536,7 +14574,7 @@
     </row>
     <row r="554" spans="13:21">
       <c r="M554" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R554" t="str">
@@ -14558,7 +14596,7 @@
     </row>
     <row r="555" spans="13:21">
       <c r="M555" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R555" t="str">
@@ -14580,7 +14618,7 @@
     </row>
     <row r="556" spans="13:21">
       <c r="M556" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R556" t="str">
@@ -14602,7 +14640,7 @@
     </row>
     <row r="557" spans="13:21">
       <c r="M557" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R557" t="str">
@@ -14624,7 +14662,7 @@
     </row>
     <row r="558" spans="13:21">
       <c r="M558" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R558" t="str">
@@ -14646,7 +14684,7 @@
     </row>
     <row r="559" spans="13:21">
       <c r="M559" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R559" t="str">
@@ -14668,7 +14706,7 @@
     </row>
     <row r="560" spans="13:21">
       <c r="M560" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R560" t="str">
@@ -14690,7 +14728,7 @@
     </row>
     <row r="561" spans="13:21">
       <c r="M561" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R561" t="str">
@@ -14712,7 +14750,7 @@
     </row>
     <row r="562" spans="13:21">
       <c r="M562" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R562" t="str">
@@ -14734,7 +14772,7 @@
     </row>
     <row r="563" spans="13:21">
       <c r="M563" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R563" t="str">
@@ -14756,7 +14794,7 @@
     </row>
     <row r="564" spans="13:21">
       <c r="M564" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R564" t="str">
@@ -14778,7 +14816,7 @@
     </row>
     <row r="565" spans="13:21">
       <c r="M565" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R565" t="str">
@@ -14800,7 +14838,7 @@
     </row>
     <row r="566" spans="13:21">
       <c r="M566" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R566" t="str">
@@ -14822,7 +14860,7 @@
     </row>
     <row r="567" spans="13:21">
       <c r="M567" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R567" t="str">
@@ -14844,7 +14882,7 @@
     </row>
     <row r="568" spans="13:21">
       <c r="M568" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R568" t="str">
@@ -14866,7 +14904,7 @@
     </row>
     <row r="569" spans="13:21">
       <c r="M569" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R569" t="str">
@@ -14888,7 +14926,7 @@
     </row>
     <row r="570" spans="13:21">
       <c r="M570" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R570" t="str">
@@ -14910,7 +14948,7 @@
     </row>
     <row r="571" spans="13:21">
       <c r="M571" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R571" t="str">
@@ -14932,7 +14970,7 @@
     </row>
     <row r="572" spans="13:21">
       <c r="M572" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R572" t="str">
@@ -14954,7 +14992,7 @@
     </row>
     <row r="573" spans="13:21">
       <c r="M573" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R573" t="str">
@@ -14976,7 +15014,7 @@
     </row>
     <row r="574" spans="13:21">
       <c r="M574" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R574" t="str">
@@ -14998,7 +15036,7 @@
     </row>
     <row r="575" spans="13:21">
       <c r="M575" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R575" t="str">
@@ -15020,7 +15058,7 @@
     </row>
     <row r="576" spans="13:21">
       <c r="M576" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R576" t="str">
@@ -15042,7 +15080,7 @@
     </row>
     <row r="577" spans="13:21">
       <c r="M577" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R577" t="str">
@@ -15064,7 +15102,7 @@
     </row>
     <row r="578" spans="13:21">
       <c r="M578" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R578" t="str">
@@ -15086,7 +15124,7 @@
     </row>
     <row r="579" spans="13:21">
       <c r="M579" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R579" t="str">
@@ -15108,7 +15146,7 @@
     </row>
     <row r="580" spans="13:21">
       <c r="M580" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R580" t="str">
@@ -15130,7 +15168,7 @@
     </row>
     <row r="581" spans="13:21">
       <c r="M581" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R581" t="str">
@@ -15152,7 +15190,7 @@
     </row>
     <row r="582" spans="13:21">
       <c r="M582" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R582" t="str">
@@ -15174,7 +15212,7 @@
     </row>
     <row r="583" spans="13:21">
       <c r="M583" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R583" t="str">
@@ -15196,7 +15234,7 @@
     </row>
     <row r="584" spans="13:21">
       <c r="M584" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R584" t="str">
@@ -15218,7 +15256,7 @@
     </row>
     <row r="585" spans="13:21">
       <c r="M585" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R585" t="str">
@@ -15240,7 +15278,7 @@
     </row>
     <row r="586" spans="13:21">
       <c r="M586" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R586" t="str">
@@ -15262,7 +15300,7 @@
     </row>
     <row r="587" spans="13:21">
       <c r="M587" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R587" t="str">
@@ -15284,7 +15322,7 @@
     </row>
     <row r="588" spans="13:21">
       <c r="M588" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R588" t="str">
@@ -15306,7 +15344,7 @@
     </row>
     <row r="589" spans="13:21">
       <c r="M589" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R589" t="str">
@@ -15328,7 +15366,7 @@
     </row>
     <row r="590" spans="13:21">
       <c r="M590" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R590" t="str">
@@ -15350,7 +15388,7 @@
     </row>
     <row r="591" spans="13:21">
       <c r="M591" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R591" t="str">
@@ -15372,7 +15410,7 @@
     </row>
     <row r="592" spans="13:21">
       <c r="M592" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R592" t="str">
@@ -15394,7 +15432,7 @@
     </row>
     <row r="593" spans="13:21">
       <c r="M593" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R593" t="str">
@@ -15416,7 +15454,7 @@
     </row>
     <row r="594" spans="13:21">
       <c r="M594" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R594" t="str">
@@ -15438,7 +15476,7 @@
     </row>
     <row r="595" spans="13:21">
       <c r="M595" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R595" t="str">
@@ -15460,7 +15498,7 @@
     </row>
     <row r="596" spans="13:21">
       <c r="M596" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R596" t="str">
@@ -15482,7 +15520,7 @@
     </row>
     <row r="597" spans="13:21">
       <c r="M597" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R597" t="str">
@@ -15504,7 +15542,7 @@
     </row>
     <row r="598" spans="13:21">
       <c r="M598" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R598" t="str">
@@ -15526,7 +15564,7 @@
     </row>
     <row r="599" spans="13:21">
       <c r="M599" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R599" t="str">
@@ -15548,7 +15586,7 @@
     </row>
     <row r="600" spans="13:21">
       <c r="M600" s="22" t="str">
-        <f t="shared" ref="M600:M663" si="12">IF(F600="CJ", I600*200, "")</f>
+        <f t="shared" ref="M600:M663" si="13">IF(F600="CJ", I600*200, "")</f>
         <v/>
       </c>
       <c r="R600" t="str">
@@ -15570,7 +15608,7 @@
     </row>
     <row r="601" spans="13:21">
       <c r="M601" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R601" t="str">
@@ -15592,7 +15630,7 @@
     </row>
     <row r="602" spans="13:21">
       <c r="M602" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R602" t="str">
@@ -15614,7 +15652,7 @@
     </row>
     <row r="603" spans="13:21">
       <c r="M603" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R603" t="str">
@@ -15636,7 +15674,7 @@
     </row>
     <row r="604" spans="13:21">
       <c r="M604" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R604" t="str">
@@ -15658,7 +15696,7 @@
     </row>
     <row r="605" spans="13:21">
       <c r="M605" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R605" t="str">
@@ -15680,7 +15718,7 @@
     </row>
     <row r="606" spans="13:21">
       <c r="M606" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R606" t="str">
@@ -15702,7 +15740,7 @@
     </row>
     <row r="607" spans="13:21">
       <c r="M607" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R607" t="str">
@@ -15724,7 +15762,7 @@
     </row>
     <row r="608" spans="13:21">
       <c r="M608" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R608" t="str">
@@ -15746,7 +15784,7 @@
     </row>
     <row r="609" spans="13:21">
       <c r="M609" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R609" t="str">
@@ -15768,7 +15806,7 @@
     </row>
     <row r="610" spans="13:21">
       <c r="M610" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R610" t="str">
@@ -15790,7 +15828,7 @@
     </row>
     <row r="611" spans="13:21">
       <c r="M611" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R611" t="str">
@@ -15812,7 +15850,7 @@
     </row>
     <row r="612" spans="13:21">
       <c r="M612" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R612" t="str">
@@ -15834,7 +15872,7 @@
     </row>
     <row r="613" spans="13:21">
       <c r="M613" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R613" t="str">
@@ -15856,7 +15894,7 @@
     </row>
     <row r="614" spans="13:21">
       <c r="M614" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R614" t="str">
@@ -15878,7 +15916,7 @@
     </row>
     <row r="615" spans="13:21">
       <c r="M615" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R615" t="str">
@@ -15900,7 +15938,7 @@
     </row>
     <row r="616" spans="13:21">
       <c r="M616" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R616" t="str">
@@ -15922,7 +15960,7 @@
     </row>
     <row r="617" spans="13:21">
       <c r="M617" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R617" t="str">
@@ -15944,7 +15982,7 @@
     </row>
     <row r="618" spans="13:21">
       <c r="M618" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R618" t="str">
@@ -15966,7 +16004,7 @@
     </row>
     <row r="619" spans="13:21">
       <c r="M619" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R619" t="str">
@@ -15988,7 +16026,7 @@
     </row>
     <row r="620" spans="13:21">
       <c r="M620" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R620" t="str">
@@ -16010,7 +16048,7 @@
     </row>
     <row r="621" spans="13:21">
       <c r="M621" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R621" t="str">
@@ -16032,7 +16070,7 @@
     </row>
     <row r="622" spans="13:21">
       <c r="M622" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R622" t="str">
@@ -16054,7 +16092,7 @@
     </row>
     <row r="623" spans="13:21">
       <c r="M623" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R623" t="str">
@@ -16076,7 +16114,7 @@
     </row>
     <row r="624" spans="13:21">
       <c r="M624" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R624" t="str">
@@ -16098,7 +16136,7 @@
     </row>
     <row r="625" spans="13:21">
       <c r="M625" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R625" t="str">
@@ -16120,7 +16158,7 @@
     </row>
     <row r="626" spans="13:21">
       <c r="M626" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R626" t="str">
@@ -16142,7 +16180,7 @@
     </row>
     <row r="627" spans="13:21">
       <c r="M627" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R627" t="str">
@@ -16164,7 +16202,7 @@
     </row>
     <row r="628" spans="13:21">
       <c r="M628" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R628" t="str">
@@ -16186,7 +16224,7 @@
     </row>
     <row r="629" spans="13:21">
       <c r="M629" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R629" t="str">
@@ -16208,7 +16246,7 @@
     </row>
     <row r="630" spans="13:21">
       <c r="M630" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R630" t="str">
@@ -16230,7 +16268,7 @@
     </row>
     <row r="631" spans="13:21">
       <c r="M631" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R631" t="str">
@@ -16252,7 +16290,7 @@
     </row>
     <row r="632" spans="13:21">
       <c r="M632" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R632" t="str">
@@ -16274,7 +16312,7 @@
     </row>
     <row r="633" spans="13:21">
       <c r="M633" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R633" t="str">
@@ -16296,7 +16334,7 @@
     </row>
     <row r="634" spans="13:21">
       <c r="M634" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R634" t="str">
@@ -16318,7 +16356,7 @@
     </row>
     <row r="635" spans="13:21">
       <c r="M635" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R635" t="str">
@@ -16340,7 +16378,7 @@
     </row>
     <row r="636" spans="13:21">
       <c r="M636" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R636" t="str">
@@ -16362,7 +16400,7 @@
     </row>
     <row r="637" spans="13:21">
       <c r="M637" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R637" t="str">
@@ -16384,7 +16422,7 @@
     </row>
     <row r="638" spans="13:21">
       <c r="M638" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R638" t="str">
@@ -16406,7 +16444,7 @@
     </row>
     <row r="639" spans="13:21">
       <c r="M639" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R639" t="str">
@@ -16428,7 +16466,7 @@
     </row>
     <row r="640" spans="13:21">
       <c r="M640" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R640" t="str">
@@ -16450,7 +16488,7 @@
     </row>
     <row r="641" spans="13:21">
       <c r="M641" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R641" t="str">
@@ -16472,7 +16510,7 @@
     </row>
     <row r="642" spans="13:21">
       <c r="M642" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R642" t="str">
@@ -16494,7 +16532,7 @@
     </row>
     <row r="643" spans="13:21">
       <c r="M643" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R643" t="str">
@@ -16516,7 +16554,7 @@
     </row>
     <row r="644" spans="13:21">
       <c r="M644" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R644" t="str">
@@ -16538,7 +16576,7 @@
     </row>
     <row r="645" spans="13:21">
       <c r="M645" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R645" t="str">
@@ -16560,7 +16598,7 @@
     </row>
     <row r="646" spans="13:21">
       <c r="M646" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R646" t="str">
@@ -16582,7 +16620,7 @@
     </row>
     <row r="647" spans="13:21">
       <c r="M647" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R647" t="str">
@@ -16604,7 +16642,7 @@
     </row>
     <row r="648" spans="13:21">
       <c r="M648" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R648" t="str">
@@ -16626,7 +16664,7 @@
     </row>
     <row r="649" spans="13:21">
       <c r="M649" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R649" t="str">
@@ -16648,7 +16686,7 @@
     </row>
     <row r="650" spans="13:21">
       <c r="M650" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R650" t="str">
@@ -16670,7 +16708,7 @@
     </row>
     <row r="651" spans="13:21">
       <c r="M651" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R651" t="str">
@@ -16692,7 +16730,7 @@
     </row>
     <row r="652" spans="13:21">
       <c r="M652" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R652" t="str">
@@ -16714,7 +16752,7 @@
     </row>
     <row r="653" spans="13:21">
       <c r="M653" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R653" t="str">
@@ -16736,7 +16774,7 @@
     </row>
     <row r="654" spans="13:21">
       <c r="M654" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R654" t="str">
@@ -16758,7 +16796,7 @@
     </row>
     <row r="655" spans="13:21">
       <c r="M655" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R655" t="str">
@@ -16780,7 +16818,7 @@
     </row>
     <row r="656" spans="13:21">
       <c r="M656" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R656" t="str">
@@ -16802,7 +16840,7 @@
     </row>
     <row r="657" spans="13:21">
       <c r="M657" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R657" t="str">
@@ -16824,7 +16862,7 @@
     </row>
     <row r="658" spans="13:21">
       <c r="M658" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R658" t="str">
@@ -16846,7 +16884,7 @@
     </row>
     <row r="659" spans="13:21">
       <c r="M659" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R659" t="str">
@@ -16868,7 +16906,7 @@
     </row>
     <row r="660" spans="13:21">
       <c r="M660" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R660" t="str">
@@ -16890,7 +16928,7 @@
     </row>
     <row r="661" spans="13:21">
       <c r="M661" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R661" t="str">
@@ -16912,7 +16950,7 @@
     </row>
     <row r="662" spans="13:21">
       <c r="M662" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R662" t="str">
@@ -16934,7 +16972,7 @@
     </row>
     <row r="663" spans="13:21">
       <c r="M663" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R663" t="str">
@@ -16956,7 +16994,7 @@
     </row>
     <row r="664" spans="13:21">
       <c r="M664" s="22" t="str">
-        <f t="shared" ref="M664:M727" si="13">IF(F664="CJ", I664*200, "")</f>
+        <f t="shared" ref="M664:M727" si="14">IF(F664="CJ", I664*200, "")</f>
         <v/>
       </c>
       <c r="R664" t="str">
@@ -16978,7 +17016,7 @@
     </row>
     <row r="665" spans="13:21">
       <c r="M665" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R665" t="str">
@@ -17000,7 +17038,7 @@
     </row>
     <row r="666" spans="13:21">
       <c r="M666" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R666" t="str">
@@ -17022,7 +17060,7 @@
     </row>
     <row r="667" spans="13:21">
       <c r="M667" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R667" t="str">
@@ -17044,7 +17082,7 @@
     </row>
     <row r="668" spans="13:21">
       <c r="M668" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R668" t="str">
@@ -17066,7 +17104,7 @@
     </row>
     <row r="669" spans="13:21">
       <c r="M669" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R669" t="str">
@@ -17088,7 +17126,7 @@
     </row>
     <row r="670" spans="13:21">
       <c r="M670" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R670" t="str">
@@ -17110,7 +17148,7 @@
     </row>
     <row r="671" spans="13:21">
       <c r="M671" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R671" t="str">
@@ -17132,7 +17170,7 @@
     </row>
     <row r="672" spans="13:21">
       <c r="M672" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R672" t="str">
@@ -17154,7 +17192,7 @@
     </row>
     <row r="673" spans="13:21">
       <c r="M673" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R673" t="str">
@@ -17176,7 +17214,7 @@
     </row>
     <row r="674" spans="13:21">
       <c r="M674" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R674" t="str">
@@ -17198,7 +17236,7 @@
     </row>
     <row r="675" spans="13:21">
       <c r="M675" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R675" t="str">
@@ -17220,7 +17258,7 @@
     </row>
     <row r="676" spans="13:21">
       <c r="M676" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R676" t="str">
@@ -17242,7 +17280,7 @@
     </row>
     <row r="677" spans="13:21">
       <c r="M677" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R677" t="str">
@@ -17264,7 +17302,7 @@
     </row>
     <row r="678" spans="13:21">
       <c r="M678" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R678" t="str">
@@ -17286,7 +17324,7 @@
     </row>
     <row r="679" spans="13:21">
       <c r="M679" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R679" t="str">
@@ -17308,7 +17346,7 @@
     </row>
     <row r="680" spans="13:21">
       <c r="M680" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R680" t="str">
@@ -17330,7 +17368,7 @@
     </row>
     <row r="681" spans="13:21">
       <c r="M681" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R681" t="str">
@@ -17352,7 +17390,7 @@
     </row>
     <row r="682" spans="13:21">
       <c r="M682" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R682" t="str">
@@ -17374,7 +17412,7 @@
     </row>
     <row r="683" spans="13:21">
       <c r="M683" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R683" t="str">
@@ -17396,7 +17434,7 @@
     </row>
     <row r="684" spans="13:21">
       <c r="M684" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R684" t="str">
@@ -17418,7 +17456,7 @@
     </row>
     <row r="685" spans="13:21">
       <c r="M685" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R685" t="str">
@@ -17440,7 +17478,7 @@
     </row>
     <row r="686" spans="13:21">
       <c r="M686" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R686" t="str">
@@ -17462,7 +17500,7 @@
     </row>
     <row r="687" spans="13:21">
       <c r="M687" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R687" t="str">
@@ -17484,7 +17522,7 @@
     </row>
     <row r="688" spans="13:21">
       <c r="M688" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R688" t="str">
@@ -17506,7 +17544,7 @@
     </row>
     <row r="689" spans="13:21">
       <c r="M689" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R689" t="str">
@@ -17528,7 +17566,7 @@
     </row>
     <row r="690" spans="13:21">
       <c r="M690" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R690" t="str">
@@ -17550,7 +17588,7 @@
     </row>
     <row r="691" spans="13:21">
       <c r="M691" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R691" t="str">
@@ -17572,7 +17610,7 @@
     </row>
     <row r="692" spans="13:21">
       <c r="M692" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R692" t="str">
@@ -17594,7 +17632,7 @@
     </row>
     <row r="693" spans="13:21">
       <c r="M693" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R693" t="str">
@@ -17616,7 +17654,7 @@
     </row>
     <row r="694" spans="13:21">
       <c r="M694" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R694" t="str">
@@ -17638,7 +17676,7 @@
     </row>
     <row r="695" spans="13:21">
       <c r="M695" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R695" t="str">
@@ -17660,7 +17698,7 @@
     </row>
     <row r="696" spans="13:21">
       <c r="M696" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R696" t="str">
@@ -17682,7 +17720,7 @@
     </row>
     <row r="697" spans="13:21">
       <c r="M697" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R697" t="str">
@@ -17704,7 +17742,7 @@
     </row>
     <row r="698" spans="13:21">
       <c r="M698" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R698" t="str">
@@ -17726,7 +17764,7 @@
     </row>
     <row r="699" spans="13:21">
       <c r="M699" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R699" t="str">
@@ -17748,7 +17786,7 @@
     </row>
     <row r="700" spans="13:21">
       <c r="M700" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R700" t="str">
@@ -17770,7 +17808,7 @@
     </row>
     <row r="701" spans="13:21">
       <c r="M701" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R701" t="str">
@@ -17792,7 +17830,7 @@
     </row>
     <row r="702" spans="13:21">
       <c r="M702" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R702" t="str">
@@ -17814,7 +17852,7 @@
     </row>
     <row r="703" spans="13:21">
       <c r="M703" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R703" t="str">
@@ -17836,7 +17874,7 @@
     </row>
     <row r="704" spans="13:21">
       <c r="M704" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R704" t="str">
@@ -17858,7 +17896,7 @@
     </row>
     <row r="705" spans="13:21">
       <c r="M705" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R705" t="str">
@@ -17880,7 +17918,7 @@
     </row>
     <row r="706" spans="13:21">
       <c r="M706" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R706" t="str">
@@ -17902,7 +17940,7 @@
     </row>
     <row r="707" spans="13:21">
       <c r="M707" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R707" t="str">
@@ -17924,7 +17962,7 @@
     </row>
     <row r="708" spans="13:21">
       <c r="M708" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R708" t="str">
@@ -17946,7 +17984,7 @@
     </row>
     <row r="709" spans="13:21">
       <c r="M709" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R709" t="str">
@@ -17968,7 +18006,7 @@
     </row>
     <row r="710" spans="13:21">
       <c r="M710" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R710" t="str">
@@ -17990,7 +18028,7 @@
     </row>
     <row r="711" spans="13:21">
       <c r="M711" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R711" t="str">
@@ -18012,7 +18050,7 @@
     </row>
     <row r="712" spans="13:21">
       <c r="M712" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R712" t="str">
@@ -18034,7 +18072,7 @@
     </row>
     <row r="713" spans="13:21">
       <c r="M713" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R713" t="str">
@@ -18056,7 +18094,7 @@
     </row>
     <row r="714" spans="13:21">
       <c r="M714" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R714" t="str">
@@ -18078,7 +18116,7 @@
     </row>
     <row r="715" spans="13:21">
       <c r="M715" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R715" t="str">
@@ -18100,7 +18138,7 @@
     </row>
     <row r="716" spans="13:21">
       <c r="M716" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R716" t="str">
@@ -18122,7 +18160,7 @@
     </row>
     <row r="717" spans="13:21">
       <c r="M717" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R717" t="str">
@@ -18144,7 +18182,7 @@
     </row>
     <row r="718" spans="13:21">
       <c r="M718" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R718" t="str">
@@ -18166,7 +18204,7 @@
     </row>
     <row r="719" spans="13:21">
       <c r="M719" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R719" t="str">
@@ -18188,7 +18226,7 @@
     </row>
     <row r="720" spans="13:21">
       <c r="M720" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R720" t="str">
@@ -18210,7 +18248,7 @@
     </row>
     <row r="721" spans="13:21">
       <c r="M721" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R721" t="str">
@@ -18232,7 +18270,7 @@
     </row>
     <row r="722" spans="13:21">
       <c r="M722" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R722" t="str">
@@ -18254,7 +18292,7 @@
     </row>
     <row r="723" spans="13:21">
       <c r="M723" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R723" t="str">
@@ -18276,7 +18314,7 @@
     </row>
     <row r="724" spans="13:21">
       <c r="M724" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R724" t="str">
@@ -18298,7 +18336,7 @@
     </row>
     <row r="725" spans="13:21">
       <c r="M725" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R725" t="str">
@@ -18320,7 +18358,7 @@
     </row>
     <row r="726" spans="13:21">
       <c r="M726" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R726" t="str">
@@ -18342,7 +18380,7 @@
     </row>
     <row r="727" spans="13:21">
       <c r="M727" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R727" t="str">
@@ -18364,7 +18402,7 @@
     </row>
     <row r="728" spans="13:21">
       <c r="M728" s="22" t="str">
-        <f t="shared" ref="M728:M791" si="14">IF(F728="CJ", I728*200, "")</f>
+        <f t="shared" ref="M728:M791" si="15">IF(F728="CJ", I728*200, "")</f>
         <v/>
       </c>
       <c r="R728" t="str">
@@ -18386,7 +18424,7 @@
     </row>
     <row r="729" spans="13:21">
       <c r="M729" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R729" t="str">
@@ -18408,7 +18446,7 @@
     </row>
     <row r="730" spans="13:21">
       <c r="M730" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R730" t="str">
@@ -18430,7 +18468,7 @@
     </row>
     <row r="731" spans="13:21">
       <c r="M731" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R731" t="str">
@@ -18452,7 +18490,7 @@
     </row>
     <row r="732" spans="13:21">
       <c r="M732" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R732" t="str">
@@ -18474,7 +18512,7 @@
     </row>
     <row r="733" spans="13:21">
       <c r="M733" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R733" t="str">
@@ -18496,7 +18534,7 @@
     </row>
     <row r="734" spans="13:21">
       <c r="M734" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R734" t="str">
@@ -18518,7 +18556,7 @@
     </row>
     <row r="735" spans="13:21">
       <c r="M735" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R735" t="str">
@@ -18540,7 +18578,7 @@
     </row>
     <row r="736" spans="13:21">
       <c r="M736" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R736" t="str">
@@ -18562,7 +18600,7 @@
     </row>
     <row r="737" spans="13:21">
       <c r="M737" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R737" t="str">
@@ -18584,7 +18622,7 @@
     </row>
     <row r="738" spans="13:21">
       <c r="M738" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R738" t="str">
@@ -18606,7 +18644,7 @@
     </row>
     <row r="739" spans="13:21">
       <c r="M739" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R739" t="str">
@@ -18628,7 +18666,7 @@
     </row>
     <row r="740" spans="13:21">
       <c r="M740" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R740" t="str">
@@ -18650,7 +18688,7 @@
     </row>
     <row r="741" spans="13:21">
       <c r="M741" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R741" t="str">
@@ -18672,7 +18710,7 @@
     </row>
     <row r="742" spans="13:21">
       <c r="M742" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R742" t="str">
@@ -18694,7 +18732,7 @@
     </row>
     <row r="743" spans="13:21">
       <c r="M743" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R743" t="str">
@@ -18716,7 +18754,7 @@
     </row>
     <row r="744" spans="13:21">
       <c r="M744" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R744" t="str">
@@ -18738,7 +18776,7 @@
     </row>
     <row r="745" spans="13:21">
       <c r="M745" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R745" t="str">
@@ -18760,7 +18798,7 @@
     </row>
     <row r="746" spans="13:21">
       <c r="M746" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R746" t="str">
@@ -18782,7 +18820,7 @@
     </row>
     <row r="747" spans="13:21">
       <c r="M747" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R747" t="str">
@@ -18804,7 +18842,7 @@
     </row>
     <row r="748" spans="13:21">
       <c r="M748" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R748" t="str">
@@ -18826,7 +18864,7 @@
     </row>
     <row r="749" spans="13:21">
       <c r="M749" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R749" t="str">
@@ -18848,7 +18886,7 @@
     </row>
     <row r="750" spans="13:21">
       <c r="M750" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R750" t="str">
@@ -18870,7 +18908,7 @@
     </row>
     <row r="751" spans="13:21">
       <c r="M751" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R751" t="str">
@@ -18892,7 +18930,7 @@
     </row>
     <row r="752" spans="13:21">
       <c r="M752" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R752" t="str">
@@ -18914,7 +18952,7 @@
     </row>
     <row r="753" spans="13:21">
       <c r="M753" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R753" t="str">
@@ -18936,7 +18974,7 @@
     </row>
     <row r="754" spans="13:21">
       <c r="M754" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R754" t="str">
@@ -18958,7 +18996,7 @@
     </row>
     <row r="755" spans="13:21">
       <c r="M755" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R755" t="str">
@@ -18980,7 +19018,7 @@
     </row>
     <row r="756" spans="13:21">
       <c r="M756" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R756" t="str">
@@ -19002,7 +19040,7 @@
     </row>
     <row r="757" spans="13:21">
       <c r="M757" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R757" t="str">
@@ -19024,7 +19062,7 @@
     </row>
     <row r="758" spans="13:21">
       <c r="M758" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R758" t="str">
@@ -19046,7 +19084,7 @@
     </row>
     <row r="759" spans="13:21">
       <c r="M759" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R759" t="str">
@@ -19068,7 +19106,7 @@
     </row>
     <row r="760" spans="13:21">
       <c r="M760" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R760" t="str">
@@ -19090,7 +19128,7 @@
     </row>
     <row r="761" spans="13:21">
       <c r="M761" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R761" t="str">
@@ -19112,7 +19150,7 @@
     </row>
     <row r="762" spans="13:21">
       <c r="M762" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R762" t="str">
@@ -19134,7 +19172,7 @@
     </row>
     <row r="763" spans="13:21">
       <c r="M763" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R763" t="str">
@@ -19156,7 +19194,7 @@
     </row>
     <row r="764" spans="13:21">
       <c r="M764" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R764" t="str">
@@ -19178,7 +19216,7 @@
     </row>
     <row r="765" spans="13:21">
       <c r="M765" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R765" t="str">
@@ -19200,7 +19238,7 @@
     </row>
     <row r="766" spans="13:21">
       <c r="M766" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R766" t="str">
@@ -19222,7 +19260,7 @@
     </row>
     <row r="767" spans="13:21">
       <c r="M767" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R767" t="str">
@@ -19244,7 +19282,7 @@
     </row>
     <row r="768" spans="13:21">
       <c r="M768" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R768" t="str">
@@ -19266,7 +19304,7 @@
     </row>
     <row r="769" spans="13:21">
       <c r="M769" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R769" t="str">
@@ -19288,7 +19326,7 @@
     </row>
     <row r="770" spans="13:21">
       <c r="M770" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R770" t="str">
@@ -19310,7 +19348,7 @@
     </row>
     <row r="771" spans="13:21">
       <c r="M771" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R771" t="str">
@@ -19332,7 +19370,7 @@
     </row>
     <row r="772" spans="13:21">
       <c r="M772" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R772" t="str">
@@ -19354,7 +19392,7 @@
     </row>
     <row r="773" spans="13:21">
       <c r="M773" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R773" t="str">
@@ -19376,7 +19414,7 @@
     </row>
     <row r="774" spans="13:21">
       <c r="M774" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R774" t="str">
@@ -19398,7 +19436,7 @@
     </row>
     <row r="775" spans="13:21">
       <c r="M775" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R775" t="str">
@@ -19420,7 +19458,7 @@
     </row>
     <row r="776" spans="13:21">
       <c r="M776" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R776" t="str">
@@ -19442,7 +19480,7 @@
     </row>
     <row r="777" spans="13:21">
       <c r="M777" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R777" t="str">
@@ -19464,7 +19502,7 @@
     </row>
     <row r="778" spans="13:21">
       <c r="M778" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R778" t="str">
@@ -19486,7 +19524,7 @@
     </row>
     <row r="779" spans="13:21">
       <c r="M779" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R779" t="str">
@@ -19508,7 +19546,7 @@
     </row>
     <row r="780" spans="13:21">
       <c r="M780" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R780" t="str">
@@ -19530,7 +19568,7 @@
     </row>
     <row r="781" spans="13:21">
       <c r="M781" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R781" t="str">
@@ -19552,7 +19590,7 @@
     </row>
     <row r="782" spans="13:21">
       <c r="M782" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R782" t="str">
@@ -19574,7 +19612,7 @@
     </row>
     <row r="783" spans="13:21">
       <c r="M783" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R783" t="str">
@@ -19596,7 +19634,7 @@
     </row>
     <row r="784" spans="13:21">
       <c r="M784" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R784" t="str">
@@ -19618,7 +19656,7 @@
     </row>
     <row r="785" spans="13:21">
       <c r="M785" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R785" t="str">
@@ -19640,7 +19678,7 @@
     </row>
     <row r="786" spans="13:21">
       <c r="M786" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R786" t="str">
@@ -19662,7 +19700,7 @@
     </row>
     <row r="787" spans="13:21">
       <c r="M787" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R787" t="str">
@@ -19684,7 +19722,7 @@
     </row>
     <row r="788" spans="13:21">
       <c r="M788" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R788" t="str">
@@ -19706,7 +19744,7 @@
     </row>
     <row r="789" spans="13:21">
       <c r="M789" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R789" t="str">
@@ -19728,7 +19766,7 @@
     </row>
     <row r="790" spans="13:21">
       <c r="M790" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R790" t="str">
@@ -19750,7 +19788,7 @@
     </row>
     <row r="791" spans="13:21">
       <c r="M791" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R791" t="str">
@@ -19772,7 +19810,7 @@
     </row>
     <row r="792" spans="13:21">
       <c r="M792" s="22" t="str">
-        <f t="shared" ref="M792:M855" si="15">IF(F792="CJ", I792*200, "")</f>
+        <f t="shared" ref="M792:M855" si="16">IF(F792="CJ", I792*200, "")</f>
         <v/>
       </c>
       <c r="R792" t="str">
@@ -19794,7 +19832,7 @@
     </row>
     <row r="793" spans="13:21">
       <c r="M793" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R793" t="str">
@@ -19816,7 +19854,7 @@
     </row>
     <row r="794" spans="13:21">
       <c r="M794" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R794" t="str">
@@ -19838,7 +19876,7 @@
     </row>
     <row r="795" spans="13:21">
       <c r="M795" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R795" t="str">
@@ -19860,7 +19898,7 @@
     </row>
     <row r="796" spans="13:21">
       <c r="M796" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R796" t="str">
@@ -19882,7 +19920,7 @@
     </row>
     <row r="797" spans="13:21">
       <c r="M797" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R797" t="str">
@@ -19904,7 +19942,7 @@
     </row>
     <row r="798" spans="13:21">
       <c r="M798" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R798" t="str">
@@ -19926,7 +19964,7 @@
     </row>
     <row r="799" spans="13:21">
       <c r="M799" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R799" t="str">
@@ -19948,7 +19986,7 @@
     </row>
     <row r="800" spans="13:21">
       <c r="M800" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R800" t="str">
@@ -19970,7 +20008,7 @@
     </row>
     <row r="801" spans="13:21">
       <c r="M801" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R801" t="str">
@@ -19992,7 +20030,7 @@
     </row>
     <row r="802" spans="13:21">
       <c r="M802" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R802" t="str">
@@ -20014,7 +20052,7 @@
     </row>
     <row r="803" spans="13:21">
       <c r="M803" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R803" t="str">
@@ -20036,7 +20074,7 @@
     </row>
     <row r="804" spans="13:21">
       <c r="M804" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R804" t="str">
@@ -20058,7 +20096,7 @@
     </row>
     <row r="805" spans="13:21">
       <c r="M805" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R805" t="str">
@@ -20080,7 +20118,7 @@
     </row>
     <row r="806" spans="13:21">
       <c r="M806" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R806" t="str">
@@ -20102,7 +20140,7 @@
     </row>
     <row r="807" spans="13:21">
       <c r="M807" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R807" t="str">
@@ -20124,7 +20162,7 @@
     </row>
     <row r="808" spans="13:21">
       <c r="M808" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R808" t="str">
@@ -20146,7 +20184,7 @@
     </row>
     <row r="809" spans="13:21">
       <c r="M809" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R809" t="str">
@@ -20168,7 +20206,7 @@
     </row>
     <row r="810" spans="13:21">
       <c r="M810" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R810" t="str">
@@ -20190,7 +20228,7 @@
     </row>
     <row r="811" spans="13:21">
       <c r="M811" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R811" t="str">
@@ -20212,7 +20250,7 @@
     </row>
     <row r="812" spans="13:21">
       <c r="M812" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R812" t="str">
@@ -20234,7 +20272,7 @@
     </row>
     <row r="813" spans="13:21">
       <c r="M813" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R813" t="str">
@@ -20256,7 +20294,7 @@
     </row>
     <row r="814" spans="13:21">
       <c r="M814" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R814" t="str">
@@ -20278,7 +20316,7 @@
     </row>
     <row r="815" spans="13:21">
       <c r="M815" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R815" t="str">
@@ -20300,7 +20338,7 @@
     </row>
     <row r="816" spans="13:21">
       <c r="M816" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R816" t="str">
@@ -20322,7 +20360,7 @@
     </row>
     <row r="817" spans="13:21">
       <c r="M817" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R817" t="str">
@@ -20344,7 +20382,7 @@
     </row>
     <row r="818" spans="13:21">
       <c r="M818" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R818" t="str">
@@ -20366,7 +20404,7 @@
     </row>
     <row r="819" spans="13:21">
       <c r="M819" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R819" t="str">
@@ -20388,7 +20426,7 @@
     </row>
     <row r="820" spans="13:21">
       <c r="M820" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R820" t="str">
@@ -20410,7 +20448,7 @@
     </row>
     <row r="821" spans="13:21">
       <c r="M821" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R821" t="str">
@@ -20432,7 +20470,7 @@
     </row>
     <row r="822" spans="13:21">
       <c r="M822" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R822" t="str">
@@ -20454,7 +20492,7 @@
     </row>
     <row r="823" spans="13:21">
       <c r="M823" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R823" t="str">
@@ -20476,7 +20514,7 @@
     </row>
     <row r="824" spans="13:21">
       <c r="M824" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R824" t="str">
@@ -20498,7 +20536,7 @@
     </row>
     <row r="825" spans="13:21">
       <c r="M825" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R825" t="str">
@@ -20520,7 +20558,7 @@
     </row>
     <row r="826" spans="13:21">
       <c r="M826" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R826" t="str">
@@ -20542,7 +20580,7 @@
     </row>
     <row r="827" spans="13:21">
       <c r="M827" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R827" t="str">
@@ -20564,7 +20602,7 @@
     </row>
     <row r="828" spans="13:21">
       <c r="M828" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R828" t="str">
@@ -20586,7 +20624,7 @@
     </row>
     <row r="829" spans="13:21">
       <c r="M829" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R829" t="str">
@@ -20608,7 +20646,7 @@
     </row>
     <row r="830" spans="13:21">
       <c r="M830" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R830" t="str">
@@ -20630,7 +20668,7 @@
     </row>
     <row r="831" spans="13:21">
       <c r="M831" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R831" t="str">
@@ -20652,7 +20690,7 @@
     </row>
     <row r="832" spans="13:21">
       <c r="M832" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R832" t="str">
@@ -20674,7 +20712,7 @@
     </row>
     <row r="833" spans="13:21">
       <c r="M833" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R833" t="str">
@@ -20696,7 +20734,7 @@
     </row>
     <row r="834" spans="13:21">
       <c r="M834" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R834" t="str">
@@ -20718,7 +20756,7 @@
     </row>
     <row r="835" spans="13:21">
       <c r="M835" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R835" t="str">
@@ -20740,7 +20778,7 @@
     </row>
     <row r="836" spans="13:21">
       <c r="M836" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R836" t="str">
@@ -20762,7 +20800,7 @@
     </row>
     <row r="837" spans="13:21">
       <c r="M837" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R837" t="str">
@@ -20784,7 +20822,7 @@
     </row>
     <row r="838" spans="13:21">
       <c r="M838" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R838" t="str">
@@ -20806,7 +20844,7 @@
     </row>
     <row r="839" spans="13:21">
       <c r="M839" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R839" t="str">
@@ -20828,7 +20866,7 @@
     </row>
     <row r="840" spans="13:21">
       <c r="M840" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R840" t="str">
@@ -20850,7 +20888,7 @@
     </row>
     <row r="841" spans="13:21">
       <c r="M841" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R841" t="str">
@@ -20872,7 +20910,7 @@
     </row>
     <row r="842" spans="13:21">
       <c r="M842" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R842" t="str">
@@ -20894,7 +20932,7 @@
     </row>
     <row r="843" spans="13:21">
       <c r="M843" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R843" t="str">
@@ -20916,7 +20954,7 @@
     </row>
     <row r="844" spans="13:21">
       <c r="M844" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R844" t="str">
@@ -20938,7 +20976,7 @@
     </row>
     <row r="845" spans="13:21">
       <c r="M845" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R845" t="str">
@@ -20960,7 +20998,7 @@
     </row>
     <row r="846" spans="13:21">
       <c r="M846" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R846" t="str">
@@ -20982,7 +21020,7 @@
     </row>
     <row r="847" spans="13:21">
       <c r="M847" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R847" t="str">
@@ -21004,7 +21042,7 @@
     </row>
     <row r="848" spans="13:21">
       <c r="M848" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R848" t="str">
@@ -21026,7 +21064,7 @@
     </row>
     <row r="849" spans="13:21">
       <c r="M849" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R849" t="str">
@@ -21048,7 +21086,7 @@
     </row>
     <row r="850" spans="13:21">
       <c r="M850" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R850" t="str">
@@ -21070,7 +21108,7 @@
     </row>
     <row r="851" spans="13:21">
       <c r="M851" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R851" t="str">
@@ -21092,7 +21130,7 @@
     </row>
     <row r="852" spans="13:21">
       <c r="M852" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R852" t="str">
@@ -21114,7 +21152,7 @@
     </row>
     <row r="853" spans="13:21">
       <c r="M853" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R853" t="str">
@@ -21136,7 +21174,7 @@
     </row>
     <row r="854" spans="13:21">
       <c r="M854" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R854" t="str">
@@ -21158,7 +21196,7 @@
     </row>
     <row r="855" spans="13:21">
       <c r="M855" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R855" t="str">
@@ -21180,7 +21218,7 @@
     </row>
     <row r="856" spans="13:21">
       <c r="M856" s="22" t="str">
-        <f t="shared" ref="M856:M919" si="16">IF(F856="CJ", I856*200, "")</f>
+        <f t="shared" ref="M856:M919" si="17">IF(F856="CJ", I856*200, "")</f>
         <v/>
       </c>
       <c r="R856" t="str">
@@ -21202,7 +21240,7 @@
     </row>
     <row r="857" spans="13:21">
       <c r="M857" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R857" t="str">
@@ -21224,7 +21262,7 @@
     </row>
     <row r="858" spans="13:21">
       <c r="M858" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R858" t="str">
@@ -21246,7 +21284,7 @@
     </row>
     <row r="859" spans="13:21">
       <c r="M859" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R859" t="str">
@@ -21268,7 +21306,7 @@
     </row>
     <row r="860" spans="13:21">
       <c r="M860" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R860" t="str">
@@ -21290,7 +21328,7 @@
     </row>
     <row r="861" spans="13:21">
       <c r="M861" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R861" t="str">
@@ -21312,7 +21350,7 @@
     </row>
     <row r="862" spans="13:21">
       <c r="M862" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R862" t="str">
@@ -21334,7 +21372,7 @@
     </row>
     <row r="863" spans="13:21">
       <c r="M863" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R863" t="str">
@@ -21356,7 +21394,7 @@
     </row>
     <row r="864" spans="13:21">
       <c r="M864" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R864" t="str">
@@ -21378,7 +21416,7 @@
     </row>
     <row r="865" spans="13:21">
       <c r="M865" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R865" t="str">
@@ -21400,7 +21438,7 @@
     </row>
     <row r="866" spans="13:21">
       <c r="M866" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R866" t="str">
@@ -21422,7 +21460,7 @@
     </row>
     <row r="867" spans="13:21">
       <c r="M867" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R867" t="str">
@@ -21444,7 +21482,7 @@
     </row>
     <row r="868" spans="13:21">
       <c r="M868" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R868" t="str">
@@ -21466,7 +21504,7 @@
     </row>
     <row r="869" spans="13:21">
       <c r="M869" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R869" t="str">
@@ -21488,7 +21526,7 @@
     </row>
     <row r="870" spans="13:21">
       <c r="M870" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R870" t="str">
@@ -21510,7 +21548,7 @@
     </row>
     <row r="871" spans="13:21">
       <c r="M871" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R871" t="str">
@@ -21532,7 +21570,7 @@
     </row>
     <row r="872" spans="13:21">
       <c r="M872" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R872" t="str">
@@ -21554,7 +21592,7 @@
     </row>
     <row r="873" spans="13:21">
       <c r="M873" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R873" t="str">
@@ -21576,7 +21614,7 @@
     </row>
     <row r="874" spans="13:21">
       <c r="M874" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R874" t="str">
@@ -21598,7 +21636,7 @@
     </row>
     <row r="875" spans="13:21">
       <c r="M875" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R875" t="str">
@@ -21620,7 +21658,7 @@
     </row>
     <row r="876" spans="13:21">
       <c r="M876" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R876" t="str">
@@ -21642,7 +21680,7 @@
     </row>
     <row r="877" spans="13:21">
       <c r="M877" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R877" t="str">
@@ -21664,7 +21702,7 @@
     </row>
     <row r="878" spans="13:21">
       <c r="M878" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R878" t="str">
@@ -21686,7 +21724,7 @@
     </row>
     <row r="879" spans="13:21">
       <c r="M879" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R879" t="str">
@@ -21708,7 +21746,7 @@
     </row>
     <row r="880" spans="13:21">
       <c r="M880" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R880" t="str">
@@ -21730,7 +21768,7 @@
     </row>
     <row r="881" spans="13:21">
       <c r="M881" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R881" t="str">
@@ -21752,7 +21790,7 @@
     </row>
     <row r="882" spans="13:21">
       <c r="M882" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R882" t="str">
@@ -21774,7 +21812,7 @@
     </row>
     <row r="883" spans="13:21">
       <c r="M883" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R883" t="str">
@@ -21796,7 +21834,7 @@
     </row>
     <row r="884" spans="13:21">
       <c r="M884" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R884" t="str">
@@ -21818,7 +21856,7 @@
     </row>
     <row r="885" spans="13:21">
       <c r="M885" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R885" t="str">
@@ -21840,7 +21878,7 @@
     </row>
     <row r="886" spans="13:21">
       <c r="M886" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R886" t="str">
@@ -21862,7 +21900,7 @@
     </row>
     <row r="887" spans="13:21">
       <c r="M887" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R887" t="str">
@@ -21884,7 +21922,7 @@
     </row>
     <row r="888" spans="13:21">
       <c r="M888" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R888" t="str">
@@ -21906,7 +21944,7 @@
     </row>
     <row r="889" spans="13:21">
       <c r="M889" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R889" t="str">
@@ -21928,7 +21966,7 @@
     </row>
     <row r="890" spans="13:21">
       <c r="M890" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R890" t="str">
@@ -21950,7 +21988,7 @@
     </row>
     <row r="891" spans="13:21">
       <c r="M891" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R891" t="str">
@@ -21972,7 +22010,7 @@
     </row>
     <row r="892" spans="13:21">
       <c r="M892" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R892" t="str">
@@ -21994,7 +22032,7 @@
     </row>
     <row r="893" spans="13:21">
       <c r="M893" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R893" t="str">
@@ -22016,7 +22054,7 @@
     </row>
     <row r="894" spans="13:21">
       <c r="M894" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R894" t="str">
@@ -22038,7 +22076,7 @@
     </row>
     <row r="895" spans="13:21">
       <c r="M895" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R895" t="str">
@@ -22060,7 +22098,7 @@
     </row>
     <row r="896" spans="13:21">
       <c r="M896" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R896" t="str">
@@ -22082,7 +22120,7 @@
     </row>
     <row r="897" spans="13:21">
       <c r="M897" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R897" t="str">
@@ -22104,7 +22142,7 @@
     </row>
     <row r="898" spans="13:21">
       <c r="M898" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R898" t="str">
@@ -22126,7 +22164,7 @@
     </row>
     <row r="899" spans="13:21">
       <c r="M899" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R899" t="str">
@@ -22148,7 +22186,7 @@
     </row>
     <row r="900" spans="13:21">
       <c r="M900" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R900" t="str">
@@ -22170,7 +22208,7 @@
     </row>
     <row r="901" spans="13:21">
       <c r="M901" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R901" t="str">
@@ -22192,7 +22230,7 @@
     </row>
     <row r="902" spans="13:21">
       <c r="M902" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R902" t="str">
@@ -22214,7 +22252,7 @@
     </row>
     <row r="903" spans="13:21">
       <c r="M903" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R903" t="str">
@@ -22236,7 +22274,7 @@
     </row>
     <row r="904" spans="13:21">
       <c r="M904" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R904" t="str">
@@ -22258,7 +22296,7 @@
     </row>
     <row r="905" spans="13:21">
       <c r="M905" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R905" t="str">
@@ -22280,7 +22318,7 @@
     </row>
     <row r="906" spans="13:21">
       <c r="M906" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R906" t="str">
@@ -22302,7 +22340,7 @@
     </row>
     <row r="907" spans="13:21">
       <c r="M907" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R907" t="str">
@@ -22324,7 +22362,7 @@
     </row>
     <row r="908" spans="13:21">
       <c r="M908" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R908" t="str">
@@ -22346,7 +22384,7 @@
     </row>
     <row r="909" spans="13:21">
       <c r="M909" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R909" t="str">
@@ -22368,7 +22406,7 @@
     </row>
     <row r="910" spans="13:21">
       <c r="M910" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R910" t="str">
@@ -22390,7 +22428,7 @@
     </row>
     <row r="911" spans="13:21">
       <c r="M911" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R911" t="str">
@@ -22412,7 +22450,7 @@
     </row>
     <row r="912" spans="13:21">
       <c r="M912" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R912" t="str">
@@ -22434,7 +22472,7 @@
     </row>
     <row r="913" spans="13:21">
       <c r="M913" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R913" t="str">
@@ -22456,7 +22494,7 @@
     </row>
     <row r="914" spans="13:21">
       <c r="M914" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R914" t="str">
@@ -22478,7 +22516,7 @@
     </row>
     <row r="915" spans="13:21">
       <c r="M915" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R915" t="str">
@@ -22500,7 +22538,7 @@
     </row>
     <row r="916" spans="13:21">
       <c r="M916" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R916" t="str">
@@ -22522,7 +22560,7 @@
     </row>
     <row r="917" spans="13:21">
       <c r="M917" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R917" t="str">
@@ -22544,7 +22582,7 @@
     </row>
     <row r="918" spans="13:21">
       <c r="M918" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R918" t="str">
@@ -22566,7 +22604,7 @@
     </row>
     <row r="919" spans="13:21">
       <c r="M919" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R919" t="str">
@@ -22588,7 +22626,7 @@
     </row>
     <row r="920" spans="13:21">
       <c r="M920" s="22" t="str">
-        <f t="shared" ref="M920:M983" si="17">IF(F920="CJ", I920*200, "")</f>
+        <f t="shared" ref="M920:M983" si="18">IF(F920="CJ", I920*200, "")</f>
         <v/>
       </c>
       <c r="R920" t="str">
@@ -22610,7 +22648,7 @@
     </row>
     <row r="921" spans="13:21">
       <c r="M921" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R921" t="str">
@@ -22632,7 +22670,7 @@
     </row>
     <row r="922" spans="13:21">
       <c r="M922" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R922" t="str">
@@ -22654,7 +22692,7 @@
     </row>
     <row r="923" spans="13:21">
       <c r="M923" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R923" t="str">
@@ -22676,7 +22714,7 @@
     </row>
     <row r="924" spans="13:21">
       <c r="M924" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R924" t="str">
@@ -22698,7 +22736,7 @@
     </row>
     <row r="925" spans="13:21">
       <c r="M925" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R925" t="str">
@@ -22720,7 +22758,7 @@
     </row>
     <row r="926" spans="13:21">
       <c r="M926" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R926" t="str">
@@ -22742,7 +22780,7 @@
     </row>
     <row r="927" spans="13:21">
       <c r="M927" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R927" t="str">
@@ -22764,7 +22802,7 @@
     </row>
     <row r="928" spans="13:21">
       <c r="M928" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R928" t="str">
@@ -22786,7 +22824,7 @@
     </row>
     <row r="929" spans="13:21">
       <c r="M929" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R929" t="str">
@@ -22808,7 +22846,7 @@
     </row>
     <row r="930" spans="13:21">
       <c r="M930" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R930" t="str">
@@ -22830,7 +22868,7 @@
     </row>
     <row r="931" spans="13:21">
       <c r="M931" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R931" t="str">
@@ -22852,7 +22890,7 @@
     </row>
     <row r="932" spans="13:21">
       <c r="M932" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R932" t="str">
@@ -22874,7 +22912,7 @@
     </row>
     <row r="933" spans="13:21">
       <c r="M933" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R933" t="str">
@@ -22896,7 +22934,7 @@
     </row>
     <row r="934" spans="13:21">
       <c r="M934" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R934" t="str">
@@ -22918,7 +22956,7 @@
     </row>
     <row r="935" spans="13:21">
       <c r="M935" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R935" t="str">
@@ -22940,7 +22978,7 @@
     </row>
     <row r="936" spans="13:21">
       <c r="M936" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R936" t="str">
@@ -22962,7 +23000,7 @@
     </row>
     <row r="937" spans="13:21">
       <c r="M937" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R937" t="str">
@@ -22984,7 +23022,7 @@
     </row>
     <row r="938" spans="13:21">
       <c r="M938" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R938" t="str">
@@ -23006,7 +23044,7 @@
     </row>
     <row r="939" spans="13:21">
       <c r="M939" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R939" t="str">
@@ -23028,7 +23066,7 @@
     </row>
     <row r="940" spans="13:21">
       <c r="M940" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R940" t="str">
@@ -23050,7 +23088,7 @@
     </row>
     <row r="941" spans="13:21">
       <c r="M941" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R941" t="str">
@@ -23072,7 +23110,7 @@
     </row>
     <row r="942" spans="13:21">
       <c r="M942" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R942" t="str">
@@ -23094,7 +23132,7 @@
     </row>
     <row r="943" spans="13:21">
       <c r="M943" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R943" t="str">
@@ -23116,7 +23154,7 @@
     </row>
     <row r="944" spans="13:21">
       <c r="M944" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R944" t="str">
@@ -23138,7 +23176,7 @@
     </row>
     <row r="945" spans="13:21">
       <c r="M945" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R945" t="str">
@@ -23160,7 +23198,7 @@
     </row>
     <row r="946" spans="13:21">
       <c r="M946" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R946" t="str">
@@ -23182,7 +23220,7 @@
     </row>
     <row r="947" spans="13:21">
       <c r="M947" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R947" t="str">
@@ -23204,7 +23242,7 @@
     </row>
     <row r="948" spans="13:21">
       <c r="M948" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R948" t="str">
@@ -23226,7 +23264,7 @@
     </row>
     <row r="949" spans="13:21">
       <c r="M949" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R949" t="str">
@@ -23248,7 +23286,7 @@
     </row>
     <row r="950" spans="13:21">
       <c r="M950" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R950" t="str">
@@ -23270,7 +23308,7 @@
     </row>
     <row r="951" spans="13:21">
       <c r="M951" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R951" t="str">
@@ -23292,7 +23330,7 @@
     </row>
     <row r="952" spans="13:21">
       <c r="M952" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R952" t="str">
@@ -23314,7 +23352,7 @@
     </row>
     <row r="953" spans="13:21">
       <c r="M953" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R953" t="str">
@@ -23336,7 +23374,7 @@
     </row>
     <row r="954" spans="13:21">
       <c r="M954" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R954" t="str">
@@ -23358,7 +23396,7 @@
     </row>
     <row r="955" spans="13:21">
       <c r="M955" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R955" t="str">
@@ -23380,7 +23418,7 @@
     </row>
     <row r="956" spans="13:21">
       <c r="M956" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R956" t="str">
@@ -23402,7 +23440,7 @@
     </row>
     <row r="957" spans="13:21">
       <c r="M957" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R957" t="str">
@@ -23424,7 +23462,7 @@
     </row>
     <row r="958" spans="13:21">
       <c r="M958" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R958" t="str">
@@ -23446,7 +23484,7 @@
     </row>
     <row r="959" spans="13:21">
       <c r="M959" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R959" t="str">
@@ -23468,7 +23506,7 @@
     </row>
     <row r="960" spans="13:21">
       <c r="M960" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R960" t="str">
@@ -23490,7 +23528,7 @@
     </row>
     <row r="961" spans="13:21">
       <c r="M961" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R961" t="str">
@@ -23512,7 +23550,7 @@
     </row>
     <row r="962" spans="13:21">
       <c r="M962" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R962" t="str">
@@ -23534,7 +23572,7 @@
     </row>
     <row r="963" spans="13:21">
       <c r="M963" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R963" t="str">
@@ -23556,7 +23594,7 @@
     </row>
     <row r="964" spans="13:21">
       <c r="M964" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R964" t="str">
@@ -23578,7 +23616,7 @@
     </row>
     <row r="965" spans="13:21">
       <c r="M965" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R965" t="str">
@@ -23600,7 +23638,7 @@
     </row>
     <row r="966" spans="13:21">
       <c r="M966" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R966" t="str">
@@ -23622,7 +23660,7 @@
     </row>
     <row r="967" spans="13:21">
       <c r="M967" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R967" t="str">
@@ -23644,7 +23682,7 @@
     </row>
     <row r="968" spans="13:21">
       <c r="M968" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R968" t="str">
@@ -23666,7 +23704,7 @@
     </row>
     <row r="969" spans="13:21">
       <c r="M969" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R969" t="str">
@@ -23688,7 +23726,7 @@
     </row>
     <row r="970" spans="13:21">
       <c r="M970" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R970" t="str">
@@ -23710,7 +23748,7 @@
     </row>
     <row r="971" spans="13:21">
       <c r="M971" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R971" t="str">
@@ -23732,7 +23770,7 @@
     </row>
     <row r="972" spans="13:21">
       <c r="M972" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R972" t="str">
@@ -23754,7 +23792,7 @@
     </row>
     <row r="973" spans="13:21">
       <c r="M973" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R973" t="str">
@@ -23776,7 +23814,7 @@
     </row>
     <row r="974" spans="13:21">
       <c r="M974" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R974" t="str">
@@ -23798,7 +23836,7 @@
     </row>
     <row r="975" spans="13:21">
       <c r="M975" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R975" t="str">
@@ -23820,7 +23858,7 @@
     </row>
     <row r="976" spans="13:21">
       <c r="M976" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R976" t="str">
@@ -23842,7 +23880,7 @@
     </row>
     <row r="977" spans="13:21">
       <c r="M977" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R977" t="str">
@@ -23864,7 +23902,7 @@
     </row>
     <row r="978" spans="13:21">
       <c r="M978" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R978" t="str">
@@ -23886,7 +23924,7 @@
     </row>
     <row r="979" spans="13:21">
       <c r="M979" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R979" t="str">
@@ -23908,7 +23946,7 @@
     </row>
     <row r="980" spans="13:21">
       <c r="M980" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R980" t="str">
@@ -23930,7 +23968,7 @@
     </row>
     <row r="981" spans="13:21">
       <c r="M981" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R981" t="str">
@@ -23952,7 +23990,7 @@
     </row>
     <row r="982" spans="13:21">
       <c r="M982" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R982" t="str">
@@ -23974,7 +24012,7 @@
     </row>
     <row r="983" spans="13:21">
       <c r="M983" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R983" t="str">
@@ -23996,7 +24034,7 @@
     </row>
     <row r="984" spans="13:21">
       <c r="M984" s="22" t="str">
-        <f t="shared" ref="M984:M1000" si="18">IF(F984="CJ", I984*200, "")</f>
+        <f t="shared" ref="M984:M1000" si="19">IF(F984="CJ", I984*200, "")</f>
         <v/>
       </c>
       <c r="R984" t="str">
@@ -24018,7 +24056,7 @@
     </row>
     <row r="985" spans="13:21">
       <c r="M985" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R985" t="str">
@@ -24040,7 +24078,7 @@
     </row>
     <row r="986" spans="13:21">
       <c r="M986" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R986" t="str">
@@ -24062,7 +24100,7 @@
     </row>
     <row r="987" spans="13:21">
       <c r="M987" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R987" t="str">
@@ -24084,7 +24122,7 @@
     </row>
     <row r="988" spans="13:21">
       <c r="M988" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R988" t="str">
@@ -24106,7 +24144,7 @@
     </row>
     <row r="989" spans="13:21">
       <c r="M989" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R989" t="str">
@@ -24128,7 +24166,7 @@
     </row>
     <row r="990" spans="13:21">
       <c r="M990" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R990" t="str">
@@ -24150,7 +24188,7 @@
     </row>
     <row r="991" spans="13:21">
       <c r="M991" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R991" t="str">
@@ -24172,7 +24210,7 @@
     </row>
     <row r="992" spans="13:21">
       <c r="M992" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R992" t="str">
@@ -24194,7 +24232,7 @@
     </row>
     <row r="993" spans="13:21">
       <c r="M993" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R993" t="str">
@@ -24216,7 +24254,7 @@
     </row>
     <row r="994" spans="13:21">
       <c r="M994" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R994" t="str">
@@ -24238,7 +24276,7 @@
     </row>
     <row r="995" spans="13:21">
       <c r="M995" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R995" t="str">
@@ -24260,7 +24298,7 @@
     </row>
     <row r="996" spans="13:21">
       <c r="M996" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R996" t="str">
@@ -24282,7 +24320,7 @@
     </row>
     <row r="997" spans="13:21">
       <c r="M997" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R997" t="str">
@@ -24304,7 +24342,7 @@
     </row>
     <row r="998" spans="13:21">
       <c r="M998" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R998" t="str">
@@ -24326,7 +24364,7 @@
     </row>
     <row r="999" spans="13:21">
       <c r="M999" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R999" t="str">
@@ -24348,7 +24386,7 @@
     </row>
     <row r="1000" spans="13:21">
       <c r="M1000" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R1000" t="str">
@@ -24427,15 +24465,15 @@
       </c>
       <c r="C6" s="33">
         <f>SUMIFS('Detalles movimientos'!P$5:P$1000, 'Detalles movimientos'!F$5:F$1000, "ENAP carga")</f>
-        <v>46235</v>
+        <v>68985</v>
       </c>
       <c r="D6" s="33">
         <f>C6-B6</f>
-        <v>39499.199999999997</v>
+        <v>62249.2</v>
       </c>
       <c r="H6" s="41">
         <f>COUNTIFS('Detalles movimientos'!F$5:F$1000, "ENAP carga")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6" s="42"/>
     </row>
@@ -24682,41 +24720,41 @@
       </c>
     </row>
     <row r="14" spans="2:13">
-      <c r="B14" s="17" t="str">
+      <c r="B14" s="17">
         <f>IFERROR(INDEX('Detalles movimientos'!C$5:C$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>46252</v>
       </c>
       <c r="C14" s="18" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!D$5:D$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>ENAP carga</v>
       </c>
       <c r="D14" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!E$5:E$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>VJYL42</v>
       </c>
       <c r="E14" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!F$5:F$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="F14" s="18" t="str">
+        <v>ENAP carga</v>
+      </c>
+      <c r="F14" s="18">
         <f>IFERROR(INDEX('Detalles movimientos'!G$5:G$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="G14" s="20" t="str">
+        <v>0</v>
+      </c>
+      <c r="G14" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!H$5:H$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="H14" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
         <f>IFERROR(INDEX('Detalles movimientos'!I$5:I$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="I14" s="20" t="str">
+        <v>0</v>
+      </c>
+      <c r="I14" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!K$5:K$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J14" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!L$5:L$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>ENAP carga</v>
       </c>
       <c r="K14" s="20" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!M$5:M$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
@@ -24724,49 +24762,49 @@
       </c>
       <c r="L14" s="18" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!N$5:N$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="M14" s="18" t="str">
+        <v>Guía N° 2358078</v>
+      </c>
+      <c r="M14" s="18">
         <f>IFERROR(INDEX('Detalles movimientos'!Q$5:Q$1000, MATCH(5, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:13">
-      <c r="B15" s="17" t="str">
+      <c r="B15" s="17">
         <f>IFERROR(INDEX('Detalles movimientos'!C$5:C$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>46253</v>
       </c>
       <c r="C15" s="18" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!D$5:D$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>ENAP carga</v>
       </c>
       <c r="D15" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!E$5:E$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>VJYL42</v>
       </c>
       <c r="E15" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!F$5:F$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="F15" s="18" t="str">
+        <v>ENAP carga</v>
+      </c>
+      <c r="F15" s="18">
         <f>IFERROR(INDEX('Detalles movimientos'!G$5:G$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="G15" s="20" t="str">
+        <v>0</v>
+      </c>
+      <c r="G15" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!H$5:H$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
+        <v>0</v>
+      </c>
+      <c r="H15" s="21">
         <f>IFERROR(INDEX('Detalles movimientos'!I$5:I$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="I15" s="20" t="str">
+        <v>0</v>
+      </c>
+      <c r="I15" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!K$5:K$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="J15" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!L$5:L$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>ENAP carga</v>
       </c>
       <c r="K15" s="20" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!M$5:M$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
@@ -24774,11 +24812,11 @@
       </c>
       <c r="L15" s="18" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!N$5:N$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="M15" s="18" t="str">
+        <v>Guía N° 2358522</v>
+      </c>
+      <c r="M15" s="18">
         <f>IFERROR(INDEX('Detalles movimientos'!Q$5:Q$1000, MATCH(6, 'Detalles movimientos'!$U$5:$U$1000, 0)), "")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:13">
@@ -31967,7 +32005,7 @@
       </c>
       <c r="B4" s="30">
         <f>SUM('Detalles movimientos'!P:P)</f>
-        <v>46235</v>
+        <v>68985</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -31985,7 +32023,7 @@
       </c>
       <c r="B6" s="30">
         <f>B4-B5</f>
-        <v>39499.199999999997</v>
+        <v>62249.2</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -32004,7 +32042,7 @@
       </c>
       <c r="B9" s="31">
         <f>SUM('Detalles movimientos'!O:O)</f>
-        <v>15451082</v>
+        <v>23231995</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -32031,7 +32069,7 @@
       </c>
       <c r="B12" s="31">
         <f>B10-B9</f>
-        <v>-9453982</v>
+        <v>-17234895</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -32059,7 +32097,7 @@
       </c>
       <c r="B16" s="31">
         <f>IF(B4&gt;0, B9/B4, 0)</f>
-        <v>334.18583324321401</v>
+        <v>336.76879031673553</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/Ventas Granel.xlsx
+++ b/Ventas Granel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hector/Desktop/Granel Movimientos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C940D61B-68E3-BC48-B2CA-1C09FD25727D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA39D40-2574-734D-BB09-27B42BF4470C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="840" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Detalles movimientos" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="114">
   <si>
     <t>RESUMEN Y MOVIMIENTOS INDIVIDUALES: IGNACIO</t>
   </si>
@@ -359,6 +359,27 @@
   </si>
   <si>
     <t>Guía N° 2358522</t>
+  </si>
+  <si>
+    <t>El Peñón 335 Puente Alto</t>
+  </si>
+  <si>
+    <t>Transferencia dos</t>
+  </si>
+  <si>
+    <t>Bar Barrio Alto</t>
+  </si>
+  <si>
+    <t>BAR Tirua</t>
+  </si>
+  <si>
+    <t>Brasas y Sabor SpA</t>
+  </si>
+  <si>
+    <t>Pirque</t>
+  </si>
+  <si>
+    <t>Puente Alto</t>
   </si>
 </sst>
 </file>
@@ -2734,26 +2755,45 @@
       </c>
     </row>
     <row r="33" spans="3:21">
-      <c r="C33" s="7"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="5"/>
+      <c r="C33" s="7">
+        <v>46254</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I33" s="5">
+        <v>294</v>
+      </c>
       <c r="J33" s="5"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="6" t="str">
+      <c r="K33" s="6">
+        <f t="shared" ref="K33:K36" si="5">H33*I33</f>
+        <v>294000</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M33" s="6">
         <f t="shared" si="2"/>
-        <v/>
+        <v>58800</v>
       </c>
       <c r="N33" s="26"/>
       <c r="O33" s="12"/>
       <c r="P33" s="29"/>
-      <c r="R33" t="str">
+      <c r="R33">
         <f>IF(F33="CJ", COUNTIF(F$5:F33, "CJ"), "")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="S33" t="str">
         <f>IF(F33="Ignacio", COUNTIF(F$5:F33, "Ignacio"), "")</f>
@@ -2769,26 +2809,45 @@
       </c>
     </row>
     <row r="34" spans="3:21">
-      <c r="C34" s="7"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="5"/>
+      <c r="C34" s="7">
+        <v>46254</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H34" s="2">
+        <v>1100</v>
+      </c>
+      <c r="I34" s="5">
+        <v>500</v>
+      </c>
       <c r="J34" s="5"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="6" t="str">
+      <c r="K34" s="6">
+        <f t="shared" si="5"/>
+        <v>550000</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M34" s="6">
         <f t="shared" si="2"/>
-        <v/>
+        <v>100000</v>
       </c>
       <c r="N34" s="26"/>
       <c r="O34" s="12"/>
       <c r="P34" s="29"/>
-      <c r="R34" t="str">
+      <c r="R34">
         <f>IF(F34="CJ", COUNTIF(F$5:F34, "CJ"), "")</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="S34" t="str">
         <f>IF(F34="Ignacio", COUNTIF(F$5:F34, "Ignacio"), "")</f>
@@ -2804,16 +2863,35 @@
       </c>
     </row>
     <row r="35" spans="3:21">
-      <c r="C35" s="7"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="5"/>
+      <c r="C35" s="7">
+        <v>46254</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H35" s="2">
+        <v>1100</v>
+      </c>
+      <c r="I35" s="5">
+        <v>100</v>
+      </c>
       <c r="J35" s="5"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="1"/>
+      <c r="K35" s="6">
+        <f t="shared" si="5"/>
+        <v>110000</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="M35" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2829,9 +2907,9 @@
         <f>IF(F35="Ignacio", COUNTIF(F$5:F35, "Ignacio"), "")</f>
         <v/>
       </c>
-      <c r="T35" t="str">
+      <c r="T35">
         <f>IF(F35="Tripulacion", COUNTIF(F$5:F35, "Tripulacion"), "")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="U35" t="str">
         <f>IF(F35="ENAP carga", COUNTIF(F$5:F35, "ENAP carga"), "")</f>
@@ -4322,7 +4400,7 @@
     </row>
     <row r="88" spans="13:21">
       <c r="M88" s="22" t="str">
-        <f t="shared" ref="M88:M151" si="5">IF(F88="CJ", I88*200, "")</f>
+        <f t="shared" ref="M88:M151" si="6">IF(F88="CJ", I88*200, "")</f>
         <v/>
       </c>
       <c r="R88" t="str">
@@ -4344,7 +4422,7 @@
     </row>
     <row r="89" spans="13:21">
       <c r="M89" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R89" t="str">
@@ -4366,7 +4444,7 @@
     </row>
     <row r="90" spans="13:21">
       <c r="M90" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R90" t="str">
@@ -4388,7 +4466,7 @@
     </row>
     <row r="91" spans="13:21">
       <c r="M91" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R91" t="str">
@@ -4410,7 +4488,7 @@
     </row>
     <row r="92" spans="13:21">
       <c r="M92" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R92" t="str">
@@ -4432,7 +4510,7 @@
     </row>
     <row r="93" spans="13:21">
       <c r="M93" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R93" t="str">
@@ -4454,7 +4532,7 @@
     </row>
     <row r="94" spans="13:21">
       <c r="M94" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R94" t="str">
@@ -4476,7 +4554,7 @@
     </row>
     <row r="95" spans="13:21">
       <c r="M95" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R95" t="str">
@@ -4498,7 +4576,7 @@
     </row>
     <row r="96" spans="13:21">
       <c r="M96" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R96" t="str">
@@ -4520,7 +4598,7 @@
     </row>
     <row r="97" spans="13:21">
       <c r="M97" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R97" t="str">
@@ -4542,7 +4620,7 @@
     </row>
     <row r="98" spans="13:21">
       <c r="M98" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R98" t="str">
@@ -4564,7 +4642,7 @@
     </row>
     <row r="99" spans="13:21">
       <c r="M99" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R99" t="str">
@@ -4586,7 +4664,7 @@
     </row>
     <row r="100" spans="13:21">
       <c r="M100" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R100" t="str">
@@ -4608,7 +4686,7 @@
     </row>
     <row r="101" spans="13:21">
       <c r="M101" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R101" t="str">
@@ -4630,7 +4708,7 @@
     </row>
     <row r="102" spans="13:21">
       <c r="M102" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R102" t="str">
@@ -4652,7 +4730,7 @@
     </row>
     <row r="103" spans="13:21">
       <c r="M103" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R103" t="str">
@@ -4674,7 +4752,7 @@
     </row>
     <row r="104" spans="13:21">
       <c r="M104" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R104" t="str">
@@ -4696,7 +4774,7 @@
     </row>
     <row r="105" spans="13:21">
       <c r="M105" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R105" t="str">
@@ -4718,7 +4796,7 @@
     </row>
     <row r="106" spans="13:21">
       <c r="M106" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R106" t="str">
@@ -4740,7 +4818,7 @@
     </row>
     <row r="107" spans="13:21">
       <c r="M107" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R107" t="str">
@@ -4762,7 +4840,7 @@
     </row>
     <row r="108" spans="13:21">
       <c r="M108" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R108" t="str">
@@ -4784,7 +4862,7 @@
     </row>
     <row r="109" spans="13:21">
       <c r="M109" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R109" t="str">
@@ -4806,7 +4884,7 @@
     </row>
     <row r="110" spans="13:21">
       <c r="M110" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R110" t="str">
@@ -4828,7 +4906,7 @@
     </row>
     <row r="111" spans="13:21">
       <c r="M111" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R111" t="str">
@@ -4850,7 +4928,7 @@
     </row>
     <row r="112" spans="13:21">
       <c r="M112" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R112" t="str">
@@ -4872,7 +4950,7 @@
     </row>
     <row r="113" spans="13:21">
       <c r="M113" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R113" t="str">
@@ -4894,7 +4972,7 @@
     </row>
     <row r="114" spans="13:21">
       <c r="M114" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R114" t="str">
@@ -4916,7 +4994,7 @@
     </row>
     <row r="115" spans="13:21">
       <c r="M115" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R115" t="str">
@@ -4938,7 +5016,7 @@
     </row>
     <row r="116" spans="13:21">
       <c r="M116" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R116" t="str">
@@ -4960,7 +5038,7 @@
     </row>
     <row r="117" spans="13:21">
       <c r="M117" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R117" t="str">
@@ -4982,7 +5060,7 @@
     </row>
     <row r="118" spans="13:21">
       <c r="M118" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R118" t="str">
@@ -5004,7 +5082,7 @@
     </row>
     <row r="119" spans="13:21">
       <c r="M119" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R119" t="str">
@@ -5026,7 +5104,7 @@
     </row>
     <row r="120" spans="13:21">
       <c r="M120" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R120" t="str">
@@ -5048,7 +5126,7 @@
     </row>
     <row r="121" spans="13:21">
       <c r="M121" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R121" t="str">
@@ -5070,7 +5148,7 @@
     </row>
     <row r="122" spans="13:21">
       <c r="M122" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R122" t="str">
@@ -5092,7 +5170,7 @@
     </row>
     <row r="123" spans="13:21">
       <c r="M123" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R123" t="str">
@@ -5114,7 +5192,7 @@
     </row>
     <row r="124" spans="13:21">
       <c r="M124" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R124" t="str">
@@ -5136,7 +5214,7 @@
     </row>
     <row r="125" spans="13:21">
       <c r="M125" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R125" t="str">
@@ -5158,7 +5236,7 @@
     </row>
     <row r="126" spans="13:21">
       <c r="M126" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R126" t="str">
@@ -5180,7 +5258,7 @@
     </row>
     <row r="127" spans="13:21">
       <c r="M127" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R127" t="str">
@@ -5202,7 +5280,7 @@
     </row>
     <row r="128" spans="13:21">
       <c r="M128" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R128" t="str">
@@ -5224,7 +5302,7 @@
     </row>
     <row r="129" spans="13:21">
       <c r="M129" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R129" t="str">
@@ -5246,7 +5324,7 @@
     </row>
     <row r="130" spans="13:21">
       <c r="M130" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R130" t="str">
@@ -5268,7 +5346,7 @@
     </row>
     <row r="131" spans="13:21">
       <c r="M131" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R131" t="str">
@@ -5290,7 +5368,7 @@
     </row>
     <row r="132" spans="13:21">
       <c r="M132" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R132" t="str">
@@ -5312,7 +5390,7 @@
     </row>
     <row r="133" spans="13:21">
       <c r="M133" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R133" t="str">
@@ -5334,7 +5412,7 @@
     </row>
     <row r="134" spans="13:21">
       <c r="M134" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R134" t="str">
@@ -5356,7 +5434,7 @@
     </row>
     <row r="135" spans="13:21">
       <c r="M135" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R135" t="str">
@@ -5378,7 +5456,7 @@
     </row>
     <row r="136" spans="13:21">
       <c r="M136" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R136" t="str">
@@ -5400,7 +5478,7 @@
     </row>
     <row r="137" spans="13:21">
       <c r="M137" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R137" t="str">
@@ -5422,7 +5500,7 @@
     </row>
     <row r="138" spans="13:21">
       <c r="M138" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R138" t="str">
@@ -5444,7 +5522,7 @@
     </row>
     <row r="139" spans="13:21">
       <c r="M139" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R139" t="str">
@@ -5466,7 +5544,7 @@
     </row>
     <row r="140" spans="13:21">
       <c r="M140" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R140" t="str">
@@ -5488,7 +5566,7 @@
     </row>
     <row r="141" spans="13:21">
       <c r="M141" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R141" t="str">
@@ -5510,7 +5588,7 @@
     </row>
     <row r="142" spans="13:21">
       <c r="M142" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R142" t="str">
@@ -5532,7 +5610,7 @@
     </row>
     <row r="143" spans="13:21">
       <c r="M143" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R143" t="str">
@@ -5554,7 +5632,7 @@
     </row>
     <row r="144" spans="13:21">
       <c r="M144" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R144" t="str">
@@ -5576,7 +5654,7 @@
     </row>
     <row r="145" spans="13:21">
       <c r="M145" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R145" t="str">
@@ -5598,7 +5676,7 @@
     </row>
     <row r="146" spans="13:21">
       <c r="M146" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R146" t="str">
@@ -5620,7 +5698,7 @@
     </row>
     <row r="147" spans="13:21">
       <c r="M147" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R147" t="str">
@@ -5642,7 +5720,7 @@
     </row>
     <row r="148" spans="13:21">
       <c r="M148" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R148" t="str">
@@ -5664,7 +5742,7 @@
     </row>
     <row r="149" spans="13:21">
       <c r="M149" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R149" t="str">
@@ -5686,7 +5764,7 @@
     </row>
     <row r="150" spans="13:21">
       <c r="M150" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R150" t="str">
@@ -5708,7 +5786,7 @@
     </row>
     <row r="151" spans="13:21">
       <c r="M151" s="22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="R151" t="str">
@@ -5730,7 +5808,7 @@
     </row>
     <row r="152" spans="13:21">
       <c r="M152" s="22" t="str">
-        <f t="shared" ref="M152:M215" si="6">IF(F152="CJ", I152*200, "")</f>
+        <f t="shared" ref="M152:M215" si="7">IF(F152="CJ", I152*200, "")</f>
         <v/>
       </c>
       <c r="R152" t="str">
@@ -5752,7 +5830,7 @@
     </row>
     <row r="153" spans="13:21">
       <c r="M153" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R153" t="str">
@@ -5774,7 +5852,7 @@
     </row>
     <row r="154" spans="13:21">
       <c r="M154" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R154" t="str">
@@ -5796,7 +5874,7 @@
     </row>
     <row r="155" spans="13:21">
       <c r="M155" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R155" t="str">
@@ -5818,7 +5896,7 @@
     </row>
     <row r="156" spans="13:21">
       <c r="M156" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R156" t="str">
@@ -5840,7 +5918,7 @@
     </row>
     <row r="157" spans="13:21">
       <c r="M157" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R157" t="str">
@@ -5862,7 +5940,7 @@
     </row>
     <row r="158" spans="13:21">
       <c r="M158" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R158" t="str">
@@ -5884,7 +5962,7 @@
     </row>
     <row r="159" spans="13:21">
       <c r="M159" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R159" t="str">
@@ -5906,7 +5984,7 @@
     </row>
     <row r="160" spans="13:21">
       <c r="M160" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R160" t="str">
@@ -5928,7 +6006,7 @@
     </row>
     <row r="161" spans="13:21">
       <c r="M161" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R161" t="str">
@@ -5950,7 +6028,7 @@
     </row>
     <row r="162" spans="13:21">
       <c r="M162" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R162" t="str">
@@ -5972,7 +6050,7 @@
     </row>
     <row r="163" spans="13:21">
       <c r="M163" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R163" t="str">
@@ -5994,7 +6072,7 @@
     </row>
     <row r="164" spans="13:21">
       <c r="M164" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R164" t="str">
@@ -6016,7 +6094,7 @@
     </row>
     <row r="165" spans="13:21">
       <c r="M165" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R165" t="str">
@@ -6038,7 +6116,7 @@
     </row>
     <row r="166" spans="13:21">
       <c r="M166" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R166" t="str">
@@ -6060,7 +6138,7 @@
     </row>
     <row r="167" spans="13:21">
       <c r="M167" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R167" t="str">
@@ -6082,7 +6160,7 @@
     </row>
     <row r="168" spans="13:21">
       <c r="M168" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R168" t="str">
@@ -6104,7 +6182,7 @@
     </row>
     <row r="169" spans="13:21">
       <c r="M169" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R169" t="str">
@@ -6126,7 +6204,7 @@
     </row>
     <row r="170" spans="13:21">
       <c r="M170" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R170" t="str">
@@ -6148,7 +6226,7 @@
     </row>
     <row r="171" spans="13:21">
       <c r="M171" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R171" t="str">
@@ -6170,7 +6248,7 @@
     </row>
     <row r="172" spans="13:21">
       <c r="M172" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R172" t="str">
@@ -6192,7 +6270,7 @@
     </row>
     <row r="173" spans="13:21">
       <c r="M173" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R173" t="str">
@@ -6214,7 +6292,7 @@
     </row>
     <row r="174" spans="13:21">
       <c r="M174" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R174" t="str">
@@ -6236,7 +6314,7 @@
     </row>
     <row r="175" spans="13:21">
       <c r="M175" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R175" t="str">
@@ -6258,7 +6336,7 @@
     </row>
     <row r="176" spans="13:21">
       <c r="M176" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R176" t="str">
@@ -6280,7 +6358,7 @@
     </row>
     <row r="177" spans="13:21">
       <c r="M177" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R177" t="str">
@@ -6302,7 +6380,7 @@
     </row>
     <row r="178" spans="13:21">
       <c r="M178" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R178" t="str">
@@ -6324,7 +6402,7 @@
     </row>
     <row r="179" spans="13:21">
       <c r="M179" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R179" t="str">
@@ -6346,7 +6424,7 @@
     </row>
     <row r="180" spans="13:21">
       <c r="M180" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R180" t="str">
@@ -6368,7 +6446,7 @@
     </row>
     <row r="181" spans="13:21">
       <c r="M181" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R181" t="str">
@@ -6390,7 +6468,7 @@
     </row>
     <row r="182" spans="13:21">
       <c r="M182" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R182" t="str">
@@ -6412,7 +6490,7 @@
     </row>
     <row r="183" spans="13:21">
       <c r="M183" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R183" t="str">
@@ -6434,7 +6512,7 @@
     </row>
     <row r="184" spans="13:21">
       <c r="M184" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R184" t="str">
@@ -6456,7 +6534,7 @@
     </row>
     <row r="185" spans="13:21">
       <c r="M185" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R185" t="str">
@@ -6478,7 +6556,7 @@
     </row>
     <row r="186" spans="13:21">
       <c r="M186" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R186" t="str">
@@ -6500,7 +6578,7 @@
     </row>
     <row r="187" spans="13:21">
       <c r="M187" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R187" t="str">
@@ -6522,7 +6600,7 @@
     </row>
     <row r="188" spans="13:21">
       <c r="M188" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R188" t="str">
@@ -6544,7 +6622,7 @@
     </row>
     <row r="189" spans="13:21">
       <c r="M189" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R189" t="str">
@@ -6566,7 +6644,7 @@
     </row>
     <row r="190" spans="13:21">
       <c r="M190" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R190" t="str">
@@ -6588,7 +6666,7 @@
     </row>
     <row r="191" spans="13:21">
       <c r="M191" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R191" t="str">
@@ -6610,7 +6688,7 @@
     </row>
     <row r="192" spans="13:21">
       <c r="M192" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R192" t="str">
@@ -6632,7 +6710,7 @@
     </row>
     <row r="193" spans="13:21">
       <c r="M193" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R193" t="str">
@@ -6654,7 +6732,7 @@
     </row>
     <row r="194" spans="13:21">
       <c r="M194" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R194" t="str">
@@ -6676,7 +6754,7 @@
     </row>
     <row r="195" spans="13:21">
       <c r="M195" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R195" t="str">
@@ -6698,7 +6776,7 @@
     </row>
     <row r="196" spans="13:21">
       <c r="M196" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R196" t="str">
@@ -6720,7 +6798,7 @@
     </row>
     <row r="197" spans="13:21">
       <c r="M197" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R197" t="str">
@@ -6742,7 +6820,7 @@
     </row>
     <row r="198" spans="13:21">
       <c r="M198" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R198" t="str">
@@ -6764,7 +6842,7 @@
     </row>
     <row r="199" spans="13:21">
       <c r="M199" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R199" t="str">
@@ -6786,7 +6864,7 @@
     </row>
     <row r="200" spans="13:21">
       <c r="M200" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R200" t="str">
@@ -6808,7 +6886,7 @@
     </row>
     <row r="201" spans="13:21">
       <c r="M201" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R201" t="str">
@@ -6830,7 +6908,7 @@
     </row>
     <row r="202" spans="13:21">
       <c r="M202" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R202" t="str">
@@ -6852,7 +6930,7 @@
     </row>
     <row r="203" spans="13:21">
       <c r="M203" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R203" t="str">
@@ -6874,7 +6952,7 @@
     </row>
     <row r="204" spans="13:21">
       <c r="M204" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R204" t="str">
@@ -6896,7 +6974,7 @@
     </row>
     <row r="205" spans="13:21">
       <c r="M205" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R205" t="str">
@@ -6918,7 +6996,7 @@
     </row>
     <row r="206" spans="13:21">
       <c r="M206" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R206" t="str">
@@ -6940,7 +7018,7 @@
     </row>
     <row r="207" spans="13:21">
       <c r="M207" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R207" t="str">
@@ -6962,7 +7040,7 @@
     </row>
     <row r="208" spans="13:21">
       <c r="M208" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R208" t="str">
@@ -6984,7 +7062,7 @@
     </row>
     <row r="209" spans="13:21">
       <c r="M209" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R209" t="str">
@@ -7006,7 +7084,7 @@
     </row>
     <row r="210" spans="13:21">
       <c r="M210" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R210" t="str">
@@ -7028,7 +7106,7 @@
     </row>
     <row r="211" spans="13:21">
       <c r="M211" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R211" t="str">
@@ -7050,7 +7128,7 @@
     </row>
     <row r="212" spans="13:21">
       <c r="M212" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R212" t="str">
@@ -7072,7 +7150,7 @@
     </row>
     <row r="213" spans="13:21">
       <c r="M213" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R213" t="str">
@@ -7094,7 +7172,7 @@
     </row>
     <row r="214" spans="13:21">
       <c r="M214" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R214" t="str">
@@ -7116,7 +7194,7 @@
     </row>
     <row r="215" spans="13:21">
       <c r="M215" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="R215" t="str">
@@ -7138,7 +7216,7 @@
     </row>
     <row r="216" spans="13:21">
       <c r="M216" s="22" t="str">
-        <f t="shared" ref="M216:M279" si="7">IF(F216="CJ", I216*200, "")</f>
+        <f t="shared" ref="M216:M279" si="8">IF(F216="CJ", I216*200, "")</f>
         <v/>
       </c>
       <c r="R216" t="str">
@@ -7160,7 +7238,7 @@
     </row>
     <row r="217" spans="13:21">
       <c r="M217" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R217" t="str">
@@ -7182,7 +7260,7 @@
     </row>
     <row r="218" spans="13:21">
       <c r="M218" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R218" t="str">
@@ -7204,7 +7282,7 @@
     </row>
     <row r="219" spans="13:21">
       <c r="M219" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R219" t="str">
@@ -7226,7 +7304,7 @@
     </row>
     <row r="220" spans="13:21">
       <c r="M220" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R220" t="str">
@@ -7248,7 +7326,7 @@
     </row>
     <row r="221" spans="13:21">
       <c r="M221" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R221" t="str">
@@ -7270,7 +7348,7 @@
     </row>
     <row r="222" spans="13:21">
       <c r="M222" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R222" t="str">
@@ -7292,7 +7370,7 @@
     </row>
     <row r="223" spans="13:21">
       <c r="M223" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R223" t="str">
@@ -7314,7 +7392,7 @@
     </row>
     <row r="224" spans="13:21">
       <c r="M224" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R224" t="str">
@@ -7336,7 +7414,7 @@
     </row>
     <row r="225" spans="13:21">
       <c r="M225" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R225" t="str">
@@ -7358,7 +7436,7 @@
     </row>
     <row r="226" spans="13:21">
       <c r="M226" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R226" t="str">
@@ -7380,7 +7458,7 @@
     </row>
     <row r="227" spans="13:21">
       <c r="M227" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R227" t="str">
@@ -7402,7 +7480,7 @@
     </row>
     <row r="228" spans="13:21">
       <c r="M228" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R228" t="str">
@@ -7424,7 +7502,7 @@
     </row>
     <row r="229" spans="13:21">
       <c r="M229" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R229" t="str">
@@ -7446,7 +7524,7 @@
     </row>
     <row r="230" spans="13:21">
       <c r="M230" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R230" t="str">
@@ -7468,7 +7546,7 @@
     </row>
     <row r="231" spans="13:21">
       <c r="M231" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R231" t="str">
@@ -7490,7 +7568,7 @@
     </row>
     <row r="232" spans="13:21">
       <c r="M232" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R232" t="str">
@@ -7512,7 +7590,7 @@
     </row>
     <row r="233" spans="13:21">
       <c r="M233" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R233" t="str">
@@ -7534,7 +7612,7 @@
     </row>
     <row r="234" spans="13:21">
       <c r="M234" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R234" t="str">
@@ -7556,7 +7634,7 @@
     </row>
     <row r="235" spans="13:21">
       <c r="M235" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R235" t="str">
@@ -7578,7 +7656,7 @@
     </row>
     <row r="236" spans="13:21">
       <c r="M236" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R236" t="str">
@@ -7600,7 +7678,7 @@
     </row>
     <row r="237" spans="13:21">
       <c r="M237" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R237" t="str">
@@ -7622,7 +7700,7 @@
     </row>
     <row r="238" spans="13:21">
       <c r="M238" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R238" t="str">
@@ -7644,7 +7722,7 @@
     </row>
     <row r="239" spans="13:21">
       <c r="M239" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R239" t="str">
@@ -7666,7 +7744,7 @@
     </row>
     <row r="240" spans="13:21">
       <c r="M240" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R240" t="str">
@@ -7688,7 +7766,7 @@
     </row>
     <row r="241" spans="13:21">
       <c r="M241" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R241" t="str">
@@ -7710,7 +7788,7 @@
     </row>
     <row r="242" spans="13:21">
       <c r="M242" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R242" t="str">
@@ -7732,7 +7810,7 @@
     </row>
     <row r="243" spans="13:21">
       <c r="M243" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R243" t="str">
@@ -7754,7 +7832,7 @@
     </row>
     <row r="244" spans="13:21">
       <c r="M244" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R244" t="str">
@@ -7776,7 +7854,7 @@
     </row>
     <row r="245" spans="13:21">
       <c r="M245" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R245" t="str">
@@ -7798,7 +7876,7 @@
     </row>
     <row r="246" spans="13:21">
       <c r="M246" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R246" t="str">
@@ -7820,7 +7898,7 @@
     </row>
     <row r="247" spans="13:21">
       <c r="M247" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R247" t="str">
@@ -7842,7 +7920,7 @@
     </row>
     <row r="248" spans="13:21">
       <c r="M248" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R248" t="str">
@@ -7864,7 +7942,7 @@
     </row>
     <row r="249" spans="13:21">
       <c r="M249" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R249" t="str">
@@ -7886,7 +7964,7 @@
     </row>
     <row r="250" spans="13:21">
       <c r="M250" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R250" t="str">
@@ -7908,7 +7986,7 @@
     </row>
     <row r="251" spans="13:21">
       <c r="M251" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R251" t="str">
@@ -7930,7 +8008,7 @@
     </row>
     <row r="252" spans="13:21">
       <c r="M252" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R252" t="str">
@@ -7952,7 +8030,7 @@
     </row>
     <row r="253" spans="13:21">
       <c r="M253" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R253" t="str">
@@ -7974,7 +8052,7 @@
     </row>
     <row r="254" spans="13:21">
       <c r="M254" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R254" t="str">
@@ -7996,7 +8074,7 @@
     </row>
     <row r="255" spans="13:21">
       <c r="M255" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R255" t="str">
@@ -8018,7 +8096,7 @@
     </row>
     <row r="256" spans="13:21">
       <c r="M256" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R256" t="str">
@@ -8040,7 +8118,7 @@
     </row>
     <row r="257" spans="13:21">
       <c r="M257" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R257" t="str">
@@ -8062,7 +8140,7 @@
     </row>
     <row r="258" spans="13:21">
       <c r="M258" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R258" t="str">
@@ -8084,7 +8162,7 @@
     </row>
     <row r="259" spans="13:21">
       <c r="M259" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R259" t="str">
@@ -8106,7 +8184,7 @@
     </row>
     <row r="260" spans="13:21">
       <c r="M260" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R260" t="str">
@@ -8128,7 +8206,7 @@
     </row>
     <row r="261" spans="13:21">
       <c r="M261" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R261" t="str">
@@ -8150,7 +8228,7 @@
     </row>
     <row r="262" spans="13:21">
       <c r="M262" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R262" t="str">
@@ -8172,7 +8250,7 @@
     </row>
     <row r="263" spans="13:21">
       <c r="M263" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R263" t="str">
@@ -8194,7 +8272,7 @@
     </row>
     <row r="264" spans="13:21">
       <c r="M264" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R264" t="str">
@@ -8216,7 +8294,7 @@
     </row>
     <row r="265" spans="13:21">
       <c r="M265" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R265" t="str">
@@ -8238,7 +8316,7 @@
     </row>
     <row r="266" spans="13:21">
       <c r="M266" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R266" t="str">
@@ -8260,7 +8338,7 @@
     </row>
     <row r="267" spans="13:21">
       <c r="M267" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R267" t="str">
@@ -8282,7 +8360,7 @@
     </row>
     <row r="268" spans="13:21">
       <c r="M268" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R268" t="str">
@@ -8304,7 +8382,7 @@
     </row>
     <row r="269" spans="13:21">
       <c r="M269" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R269" t="str">
@@ -8326,7 +8404,7 @@
     </row>
     <row r="270" spans="13:21">
       <c r="M270" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R270" t="str">
@@ -8348,7 +8426,7 @@
     </row>
     <row r="271" spans="13:21">
       <c r="M271" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R271" t="str">
@@ -8370,7 +8448,7 @@
     </row>
     <row r="272" spans="13:21">
       <c r="M272" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R272" t="str">
@@ -8392,7 +8470,7 @@
     </row>
     <row r="273" spans="13:21">
       <c r="M273" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R273" t="str">
@@ -8414,7 +8492,7 @@
     </row>
     <row r="274" spans="13:21">
       <c r="M274" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R274" t="str">
@@ -8436,7 +8514,7 @@
     </row>
     <row r="275" spans="13:21">
       <c r="M275" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R275" t="str">
@@ -8458,7 +8536,7 @@
     </row>
     <row r="276" spans="13:21">
       <c r="M276" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R276" t="str">
@@ -8480,7 +8558,7 @@
     </row>
     <row r="277" spans="13:21">
       <c r="M277" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R277" t="str">
@@ -8502,7 +8580,7 @@
     </row>
     <row r="278" spans="13:21">
       <c r="M278" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R278" t="str">
@@ -8524,7 +8602,7 @@
     </row>
     <row r="279" spans="13:21">
       <c r="M279" s="22" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="R279" t="str">
@@ -8546,7 +8624,7 @@
     </row>
     <row r="280" spans="13:21">
       <c r="M280" s="22" t="str">
-        <f t="shared" ref="M280:M343" si="8">IF(F280="CJ", I280*200, "")</f>
+        <f t="shared" ref="M280:M343" si="9">IF(F280="CJ", I280*200, "")</f>
         <v/>
       </c>
       <c r="R280" t="str">
@@ -8568,7 +8646,7 @@
     </row>
     <row r="281" spans="13:21">
       <c r="M281" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R281" t="str">
@@ -8590,7 +8668,7 @@
     </row>
     <row r="282" spans="13:21">
       <c r="M282" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R282" t="str">
@@ -8612,7 +8690,7 @@
     </row>
     <row r="283" spans="13:21">
       <c r="M283" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R283" t="str">
@@ -8634,7 +8712,7 @@
     </row>
     <row r="284" spans="13:21">
       <c r="M284" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R284" t="str">
@@ -8656,7 +8734,7 @@
     </row>
     <row r="285" spans="13:21">
       <c r="M285" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R285" t="str">
@@ -8678,7 +8756,7 @@
     </row>
     <row r="286" spans="13:21">
       <c r="M286" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R286" t="str">
@@ -8700,7 +8778,7 @@
     </row>
     <row r="287" spans="13:21">
       <c r="M287" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R287" t="str">
@@ -8722,7 +8800,7 @@
     </row>
     <row r="288" spans="13:21">
       <c r="M288" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R288" t="str">
@@ -8744,7 +8822,7 @@
     </row>
     <row r="289" spans="13:21">
       <c r="M289" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R289" t="str">
@@ -8766,7 +8844,7 @@
     </row>
     <row r="290" spans="13:21">
       <c r="M290" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R290" t="str">
@@ -8788,7 +8866,7 @@
     </row>
     <row r="291" spans="13:21">
       <c r="M291" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R291" t="str">
@@ -8810,7 +8888,7 @@
     </row>
     <row r="292" spans="13:21">
       <c r="M292" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R292" t="str">
@@ -8832,7 +8910,7 @@
     </row>
     <row r="293" spans="13:21">
       <c r="M293" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R293" t="str">
@@ -8854,7 +8932,7 @@
     </row>
     <row r="294" spans="13:21">
       <c r="M294" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R294" t="str">
@@ -8876,7 +8954,7 @@
     </row>
     <row r="295" spans="13:21">
       <c r="M295" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R295" t="str">
@@ -8898,7 +8976,7 @@
     </row>
     <row r="296" spans="13:21">
       <c r="M296" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R296" t="str">
@@ -8920,7 +8998,7 @@
     </row>
     <row r="297" spans="13:21">
       <c r="M297" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R297" t="str">
@@ -8942,7 +9020,7 @@
     </row>
     <row r="298" spans="13:21">
       <c r="M298" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R298" t="str">
@@ -8964,7 +9042,7 @@
     </row>
     <row r="299" spans="13:21">
       <c r="M299" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R299" t="str">
@@ -8986,7 +9064,7 @@
     </row>
     <row r="300" spans="13:21">
       <c r="M300" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R300" t="str">
@@ -9008,7 +9086,7 @@
     </row>
     <row r="301" spans="13:21">
       <c r="M301" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R301" t="str">
@@ -9030,7 +9108,7 @@
     </row>
     <row r="302" spans="13:21">
       <c r="M302" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R302" t="str">
@@ -9052,7 +9130,7 @@
     </row>
     <row r="303" spans="13:21">
       <c r="M303" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R303" t="str">
@@ -9074,7 +9152,7 @@
     </row>
     <row r="304" spans="13:21">
       <c r="M304" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R304" t="str">
@@ -9096,7 +9174,7 @@
     </row>
     <row r="305" spans="13:21">
       <c r="M305" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R305" t="str">
@@ -9118,7 +9196,7 @@
     </row>
     <row r="306" spans="13:21">
       <c r="M306" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R306" t="str">
@@ -9140,7 +9218,7 @@
     </row>
     <row r="307" spans="13:21">
       <c r="M307" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R307" t="str">
@@ -9162,7 +9240,7 @@
     </row>
     <row r="308" spans="13:21">
       <c r="M308" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R308" t="str">
@@ -9184,7 +9262,7 @@
     </row>
     <row r="309" spans="13:21">
       <c r="M309" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R309" t="str">
@@ -9206,7 +9284,7 @@
     </row>
     <row r="310" spans="13:21">
       <c r="M310" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R310" t="str">
@@ -9228,7 +9306,7 @@
     </row>
     <row r="311" spans="13:21">
       <c r="M311" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R311" t="str">
@@ -9250,7 +9328,7 @@
     </row>
     <row r="312" spans="13:21">
       <c r="M312" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R312" t="str">
@@ -9272,7 +9350,7 @@
     </row>
     <row r="313" spans="13:21">
       <c r="M313" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R313" t="str">
@@ -9294,7 +9372,7 @@
     </row>
     <row r="314" spans="13:21">
       <c r="M314" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R314" t="str">
@@ -9316,7 +9394,7 @@
     </row>
     <row r="315" spans="13:21">
       <c r="M315" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R315" t="str">
@@ -9338,7 +9416,7 @@
     </row>
     <row r="316" spans="13:21">
       <c r="M316" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R316" t="str">
@@ -9360,7 +9438,7 @@
     </row>
     <row r="317" spans="13:21">
       <c r="M317" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R317" t="str">
@@ -9382,7 +9460,7 @@
     </row>
     <row r="318" spans="13:21">
       <c r="M318" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R318" t="str">
@@ -9404,7 +9482,7 @@
     </row>
     <row r="319" spans="13:21">
       <c r="M319" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R319" t="str">
@@ -9426,7 +9504,7 @@
     </row>
     <row r="320" spans="13:21">
       <c r="M320" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R320" t="str">
@@ -9448,7 +9526,7 @@
     </row>
     <row r="321" spans="13:21">
       <c r="M321" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R321" t="str">
@@ -9470,7 +9548,7 @@
     </row>
     <row r="322" spans="13:21">
       <c r="M322" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R322" t="str">
@@ -9492,7 +9570,7 @@
     </row>
     <row r="323" spans="13:21">
       <c r="M323" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R323" t="str">
@@ -9514,7 +9592,7 @@
     </row>
     <row r="324" spans="13:21">
       <c r="M324" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R324" t="str">
@@ -9536,7 +9614,7 @@
     </row>
     <row r="325" spans="13:21">
       <c r="M325" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R325" t="str">
@@ -9558,7 +9636,7 @@
     </row>
     <row r="326" spans="13:21">
       <c r="M326" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R326" t="str">
@@ -9580,7 +9658,7 @@
     </row>
     <row r="327" spans="13:21">
       <c r="M327" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R327" t="str">
@@ -9602,7 +9680,7 @@
     </row>
     <row r="328" spans="13:21">
       <c r="M328" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R328" t="str">
@@ -9624,7 +9702,7 @@
     </row>
     <row r="329" spans="13:21">
       <c r="M329" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R329" t="str">
@@ -9646,7 +9724,7 @@
     </row>
     <row r="330" spans="13:21">
       <c r="M330" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R330" t="str">
@@ -9668,7 +9746,7 @@
     </row>
     <row r="331" spans="13:21">
       <c r="M331" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R331" t="str">
@@ -9690,7 +9768,7 @@
     </row>
     <row r="332" spans="13:21">
       <c r="M332" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R332" t="str">
@@ -9712,7 +9790,7 @@
     </row>
     <row r="333" spans="13:21">
       <c r="M333" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R333" t="str">
@@ -9734,7 +9812,7 @@
     </row>
     <row r="334" spans="13:21">
       <c r="M334" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R334" t="str">
@@ -9756,7 +9834,7 @@
     </row>
     <row r="335" spans="13:21">
       <c r="M335" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R335" t="str">
@@ -9778,7 +9856,7 @@
     </row>
     <row r="336" spans="13:21">
       <c r="M336" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R336" t="str">
@@ -9800,7 +9878,7 @@
     </row>
     <row r="337" spans="13:21">
       <c r="M337" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R337" t="str">
@@ -9822,7 +9900,7 @@
     </row>
     <row r="338" spans="13:21">
       <c r="M338" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R338" t="str">
@@ -9844,7 +9922,7 @@
     </row>
     <row r="339" spans="13:21">
       <c r="M339" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R339" t="str">
@@ -9866,7 +9944,7 @@
     </row>
     <row r="340" spans="13:21">
       <c r="M340" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R340" t="str">
@@ -9888,7 +9966,7 @@
     </row>
     <row r="341" spans="13:21">
       <c r="M341" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R341" t="str">
@@ -9910,7 +9988,7 @@
     </row>
     <row r="342" spans="13:21">
       <c r="M342" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R342" t="str">
@@ -9932,7 +10010,7 @@
     </row>
     <row r="343" spans="13:21">
       <c r="M343" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="R343" t="str">
@@ -9954,7 +10032,7 @@
     </row>
     <row r="344" spans="13:21">
       <c r="M344" s="22" t="str">
-        <f t="shared" ref="M344:M407" si="9">IF(F344="CJ", I344*200, "")</f>
+        <f t="shared" ref="M344:M407" si="10">IF(F344="CJ", I344*200, "")</f>
         <v/>
       </c>
       <c r="R344" t="str">
@@ -9976,7 +10054,7 @@
     </row>
     <row r="345" spans="13:21">
       <c r="M345" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R345" t="str">
@@ -9998,7 +10076,7 @@
     </row>
     <row r="346" spans="13:21">
       <c r="M346" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R346" t="str">
@@ -10020,7 +10098,7 @@
     </row>
     <row r="347" spans="13:21">
       <c r="M347" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R347" t="str">
@@ -10042,7 +10120,7 @@
     </row>
     <row r="348" spans="13:21">
       <c r="M348" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R348" t="str">
@@ -10064,7 +10142,7 @@
     </row>
     <row r="349" spans="13:21">
       <c r="M349" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R349" t="str">
@@ -10086,7 +10164,7 @@
     </row>
     <row r="350" spans="13:21">
       <c r="M350" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R350" t="str">
@@ -10108,7 +10186,7 @@
     </row>
     <row r="351" spans="13:21">
       <c r="M351" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R351" t="str">
@@ -10130,7 +10208,7 @@
     </row>
     <row r="352" spans="13:21">
       <c r="M352" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R352" t="str">
@@ -10152,7 +10230,7 @@
     </row>
     <row r="353" spans="13:21">
       <c r="M353" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R353" t="str">
@@ -10174,7 +10252,7 @@
     </row>
     <row r="354" spans="13:21">
       <c r="M354" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R354" t="str">
@@ -10196,7 +10274,7 @@
     </row>
     <row r="355" spans="13:21">
       <c r="M355" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R355" t="str">
@@ -10218,7 +10296,7 @@
     </row>
     <row r="356" spans="13:21">
       <c r="M356" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R356" t="str">
@@ -10240,7 +10318,7 @@
     </row>
     <row r="357" spans="13:21">
       <c r="M357" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R357" t="str">
@@ -10262,7 +10340,7 @@
     </row>
     <row r="358" spans="13:21">
       <c r="M358" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R358" t="str">
@@ -10284,7 +10362,7 @@
     </row>
     <row r="359" spans="13:21">
       <c r="M359" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R359" t="str">
@@ -10306,7 +10384,7 @@
     </row>
     <row r="360" spans="13:21">
       <c r="M360" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R360" t="str">
@@ -10328,7 +10406,7 @@
     </row>
     <row r="361" spans="13:21">
       <c r="M361" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R361" t="str">
@@ -10350,7 +10428,7 @@
     </row>
     <row r="362" spans="13:21">
       <c r="M362" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R362" t="str">
@@ -10372,7 +10450,7 @@
     </row>
     <row r="363" spans="13:21">
       <c r="M363" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R363" t="str">
@@ -10394,7 +10472,7 @@
     </row>
     <row r="364" spans="13:21">
       <c r="M364" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R364" t="str">
@@ -10416,7 +10494,7 @@
     </row>
     <row r="365" spans="13:21">
       <c r="M365" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R365" t="str">
@@ -10438,7 +10516,7 @@
     </row>
     <row r="366" spans="13:21">
       <c r="M366" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R366" t="str">
@@ -10460,7 +10538,7 @@
     </row>
     <row r="367" spans="13:21">
       <c r="M367" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R367" t="str">
@@ -10482,7 +10560,7 @@
     </row>
     <row r="368" spans="13:21">
       <c r="M368" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R368" t="str">
@@ -10504,7 +10582,7 @@
     </row>
     <row r="369" spans="13:21">
       <c r="M369" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R369" t="str">
@@ -10526,7 +10604,7 @@
     </row>
     <row r="370" spans="13:21">
       <c r="M370" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R370" t="str">
@@ -10548,7 +10626,7 @@
     </row>
     <row r="371" spans="13:21">
       <c r="M371" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R371" t="str">
@@ -10570,7 +10648,7 @@
     </row>
     <row r="372" spans="13:21">
       <c r="M372" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R372" t="str">
@@ -10592,7 +10670,7 @@
     </row>
     <row r="373" spans="13:21">
       <c r="M373" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R373" t="str">
@@ -10614,7 +10692,7 @@
     </row>
     <row r="374" spans="13:21">
       <c r="M374" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R374" t="str">
@@ -10636,7 +10714,7 @@
     </row>
     <row r="375" spans="13:21">
       <c r="M375" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R375" t="str">
@@ -10658,7 +10736,7 @@
     </row>
     <row r="376" spans="13:21">
       <c r="M376" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R376" t="str">
@@ -10680,7 +10758,7 @@
     </row>
     <row r="377" spans="13:21">
       <c r="M377" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R377" t="str">
@@ -10702,7 +10780,7 @@
     </row>
     <row r="378" spans="13:21">
       <c r="M378" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R378" t="str">
@@ -10724,7 +10802,7 @@
     </row>
     <row r="379" spans="13:21">
       <c r="M379" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R379" t="str">
@@ -10746,7 +10824,7 @@
     </row>
     <row r="380" spans="13:21">
       <c r="M380" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R380" t="str">
@@ -10768,7 +10846,7 @@
     </row>
     <row r="381" spans="13:21">
       <c r="M381" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R381" t="str">
@@ -10790,7 +10868,7 @@
     </row>
     <row r="382" spans="13:21">
       <c r="M382" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R382" t="str">
@@ -10812,7 +10890,7 @@
     </row>
     <row r="383" spans="13:21">
       <c r="M383" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R383" t="str">
@@ -10834,7 +10912,7 @@
     </row>
     <row r="384" spans="13:21">
       <c r="M384" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R384" t="str">
@@ -10856,7 +10934,7 @@
     </row>
     <row r="385" spans="13:21">
       <c r="M385" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R385" t="str">
@@ -10878,7 +10956,7 @@
     </row>
     <row r="386" spans="13:21">
       <c r="M386" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R386" t="str">
@@ -10900,7 +10978,7 @@
     </row>
     <row r="387" spans="13:21">
       <c r="M387" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R387" t="str">
@@ -10922,7 +11000,7 @@
     </row>
     <row r="388" spans="13:21">
       <c r="M388" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R388" t="str">
@@ -10944,7 +11022,7 @@
     </row>
     <row r="389" spans="13:21">
       <c r="M389" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R389" t="str">
@@ -10966,7 +11044,7 @@
     </row>
     <row r="390" spans="13:21">
       <c r="M390" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R390" t="str">
@@ -10988,7 +11066,7 @@
     </row>
     <row r="391" spans="13:21">
       <c r="M391" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R391" t="str">
@@ -11010,7 +11088,7 @@
     </row>
     <row r="392" spans="13:21">
       <c r="M392" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R392" t="str">
@@ -11032,7 +11110,7 @@
     </row>
     <row r="393" spans="13:21">
       <c r="M393" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R393" t="str">
@@ -11054,7 +11132,7 @@
     </row>
     <row r="394" spans="13:21">
       <c r="M394" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R394" t="str">
@@ -11076,7 +11154,7 @@
     </row>
     <row r="395" spans="13:21">
       <c r="M395" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R395" t="str">
@@ -11098,7 +11176,7 @@
     </row>
     <row r="396" spans="13:21">
       <c r="M396" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R396" t="str">
@@ -11120,7 +11198,7 @@
     </row>
     <row r="397" spans="13:21">
       <c r="M397" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R397" t="str">
@@ -11142,7 +11220,7 @@
     </row>
     <row r="398" spans="13:21">
       <c r="M398" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R398" t="str">
@@ -11164,7 +11242,7 @@
     </row>
     <row r="399" spans="13:21">
       <c r="M399" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R399" t="str">
@@ -11186,7 +11264,7 @@
     </row>
     <row r="400" spans="13:21">
       <c r="M400" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R400" t="str">
@@ -11208,7 +11286,7 @@
     </row>
     <row r="401" spans="13:21">
       <c r="M401" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R401" t="str">
@@ -11230,7 +11308,7 @@
     </row>
     <row r="402" spans="13:21">
       <c r="M402" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R402" t="str">
@@ -11252,7 +11330,7 @@
     </row>
     <row r="403" spans="13:21">
       <c r="M403" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R403" t="str">
@@ -11274,7 +11352,7 @@
     </row>
     <row r="404" spans="13:21">
       <c r="M404" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R404" t="str">
@@ -11296,7 +11374,7 @@
     </row>
     <row r="405" spans="13:21">
       <c r="M405" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R405" t="str">
@@ -11318,7 +11396,7 @@
     </row>
     <row r="406" spans="13:21">
       <c r="M406" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R406" t="str">
@@ -11340,7 +11418,7 @@
     </row>
     <row r="407" spans="13:21">
       <c r="M407" s="22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="R407" t="str">
@@ -11362,7 +11440,7 @@
     </row>
     <row r="408" spans="13:21">
       <c r="M408" s="22" t="str">
-        <f t="shared" ref="M408:M471" si="10">IF(F408="CJ", I408*200, "")</f>
+        <f t="shared" ref="M408:M471" si="11">IF(F408="CJ", I408*200, "")</f>
         <v/>
       </c>
       <c r="R408" t="str">
@@ -11384,7 +11462,7 @@
     </row>
     <row r="409" spans="13:21">
       <c r="M409" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R409" t="str">
@@ -11406,7 +11484,7 @@
     </row>
     <row r="410" spans="13:21">
       <c r="M410" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R410" t="str">
@@ -11428,7 +11506,7 @@
     </row>
     <row r="411" spans="13:21">
       <c r="M411" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R411" t="str">
@@ -11450,7 +11528,7 @@
     </row>
     <row r="412" spans="13:21">
       <c r="M412" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R412" t="str">
@@ -11472,7 +11550,7 @@
     </row>
     <row r="413" spans="13:21">
       <c r="M413" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R413" t="str">
@@ -11494,7 +11572,7 @@
     </row>
     <row r="414" spans="13:21">
       <c r="M414" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R414" t="str">
@@ -11516,7 +11594,7 @@
     </row>
     <row r="415" spans="13:21">
       <c r="M415" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R415" t="str">
@@ -11538,7 +11616,7 @@
     </row>
     <row r="416" spans="13:21">
       <c r="M416" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R416" t="str">
@@ -11560,7 +11638,7 @@
     </row>
     <row r="417" spans="13:21">
       <c r="M417" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R417" t="str">
@@ -11582,7 +11660,7 @@
     </row>
     <row r="418" spans="13:21">
       <c r="M418" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R418" t="str">
@@ -11604,7 +11682,7 @@
     </row>
     <row r="419" spans="13:21">
       <c r="M419" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R419" t="str">
@@ -11626,7 +11704,7 @@
     </row>
     <row r="420" spans="13:21">
       <c r="M420" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R420" t="str">
@@ -11648,7 +11726,7 @@
     </row>
     <row r="421" spans="13:21">
       <c r="M421" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R421" t="str">
@@ -11670,7 +11748,7 @@
     </row>
     <row r="422" spans="13:21">
       <c r="M422" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R422" t="str">
@@ -11692,7 +11770,7 @@
     </row>
     <row r="423" spans="13:21">
       <c r="M423" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R423" t="str">
@@ -11714,7 +11792,7 @@
     </row>
     <row r="424" spans="13:21">
       <c r="M424" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R424" t="str">
@@ -11736,7 +11814,7 @@
     </row>
     <row r="425" spans="13:21">
       <c r="M425" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R425" t="str">
@@ -11758,7 +11836,7 @@
     </row>
     <row r="426" spans="13:21">
       <c r="M426" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R426" t="str">
@@ -11780,7 +11858,7 @@
     </row>
     <row r="427" spans="13:21">
       <c r="M427" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R427" t="str">
@@ -11802,7 +11880,7 @@
     </row>
     <row r="428" spans="13:21">
       <c r="M428" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R428" t="str">
@@ -11824,7 +11902,7 @@
     </row>
     <row r="429" spans="13:21">
       <c r="M429" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R429" t="str">
@@ -11846,7 +11924,7 @@
     </row>
     <row r="430" spans="13:21">
       <c r="M430" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R430" t="str">
@@ -11868,7 +11946,7 @@
     </row>
     <row r="431" spans="13:21">
       <c r="M431" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R431" t="str">
@@ -11890,7 +11968,7 @@
     </row>
     <row r="432" spans="13:21">
       <c r="M432" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R432" t="str">
@@ -11912,7 +11990,7 @@
     </row>
     <row r="433" spans="13:21">
       <c r="M433" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R433" t="str">
@@ -11934,7 +12012,7 @@
     </row>
     <row r="434" spans="13:21">
       <c r="M434" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R434" t="str">
@@ -11956,7 +12034,7 @@
     </row>
     <row r="435" spans="13:21">
       <c r="M435" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R435" t="str">
@@ -11978,7 +12056,7 @@
     </row>
     <row r="436" spans="13:21">
       <c r="M436" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R436" t="str">
@@ -12000,7 +12078,7 @@
     </row>
     <row r="437" spans="13:21">
       <c r="M437" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R437" t="str">
@@ -12022,7 +12100,7 @@
     </row>
     <row r="438" spans="13:21">
       <c r="M438" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R438" t="str">
@@ -12044,7 +12122,7 @@
     </row>
     <row r="439" spans="13:21">
       <c r="M439" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R439" t="str">
@@ -12066,7 +12144,7 @@
     </row>
     <row r="440" spans="13:21">
       <c r="M440" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R440" t="str">
@@ -12088,7 +12166,7 @@
     </row>
     <row r="441" spans="13:21">
       <c r="M441" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R441" t="str">
@@ -12110,7 +12188,7 @@
     </row>
     <row r="442" spans="13:21">
       <c r="M442" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R442" t="str">
@@ -12132,7 +12210,7 @@
     </row>
     <row r="443" spans="13:21">
       <c r="M443" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R443" t="str">
@@ -12154,7 +12232,7 @@
     </row>
     <row r="444" spans="13:21">
       <c r="M444" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R444" t="str">
@@ -12176,7 +12254,7 @@
     </row>
     <row r="445" spans="13:21">
       <c r="M445" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R445" t="str">
@@ -12198,7 +12276,7 @@
     </row>
     <row r="446" spans="13:21">
       <c r="M446" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R446" t="str">
@@ -12220,7 +12298,7 @@
     </row>
     <row r="447" spans="13:21">
       <c r="M447" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R447" t="str">
@@ -12242,7 +12320,7 @@
     </row>
     <row r="448" spans="13:21">
       <c r="M448" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R448" t="str">
@@ -12264,7 +12342,7 @@
     </row>
     <row r="449" spans="13:21">
       <c r="M449" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R449" t="str">
@@ -12286,7 +12364,7 @@
     </row>
     <row r="450" spans="13:21">
       <c r="M450" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R450" t="str">
@@ -12308,7 +12386,7 @@
     </row>
     <row r="451" spans="13:21">
       <c r="M451" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R451" t="str">
@@ -12330,7 +12408,7 @@
     </row>
     <row r="452" spans="13:21">
       <c r="M452" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R452" t="str">
@@ -12352,7 +12430,7 @@
     </row>
     <row r="453" spans="13:21">
       <c r="M453" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R453" t="str">
@@ -12374,7 +12452,7 @@
     </row>
     <row r="454" spans="13:21">
       <c r="M454" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R454" t="str">
@@ -12396,7 +12474,7 @@
     </row>
     <row r="455" spans="13:21">
       <c r="M455" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R455" t="str">
@@ -12418,7 +12496,7 @@
     </row>
     <row r="456" spans="13:21">
       <c r="M456" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R456" t="str">
@@ -12440,7 +12518,7 @@
     </row>
     <row r="457" spans="13:21">
       <c r="M457" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R457" t="str">
@@ -12462,7 +12540,7 @@
     </row>
     <row r="458" spans="13:21">
       <c r="M458" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R458" t="str">
@@ -12484,7 +12562,7 @@
     </row>
     <row r="459" spans="13:21">
       <c r="M459" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R459" t="str">
@@ -12506,7 +12584,7 @@
     </row>
     <row r="460" spans="13:21">
       <c r="M460" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R460" t="str">
@@ -12528,7 +12606,7 @@
     </row>
     <row r="461" spans="13:21">
       <c r="M461" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R461" t="str">
@@ -12550,7 +12628,7 @@
     </row>
     <row r="462" spans="13:21">
       <c r="M462" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R462" t="str">
@@ -12572,7 +12650,7 @@
     </row>
     <row r="463" spans="13:21">
       <c r="M463" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R463" t="str">
@@ -12594,7 +12672,7 @@
     </row>
     <row r="464" spans="13:21">
       <c r="M464" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R464" t="str">
@@ -12616,7 +12694,7 @@
     </row>
     <row r="465" spans="13:21">
       <c r="M465" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R465" t="str">
@@ -12638,7 +12716,7 @@
     </row>
     <row r="466" spans="13:21">
       <c r="M466" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R466" t="str">
@@ -12660,7 +12738,7 @@
     </row>
     <row r="467" spans="13:21">
       <c r="M467" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R467" t="str">
@@ -12682,7 +12760,7 @@
     </row>
     <row r="468" spans="13:21">
       <c r="M468" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R468" t="str">
@@ -12704,7 +12782,7 @@
     </row>
     <row r="469" spans="13:21">
       <c r="M469" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R469" t="str">
@@ -12726,7 +12804,7 @@
     </row>
     <row r="470" spans="13:21">
       <c r="M470" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R470" t="str">
@@ -12748,7 +12826,7 @@
     </row>
     <row r="471" spans="13:21">
       <c r="M471" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="R471" t="str">
@@ -12770,7 +12848,7 @@
     </row>
     <row r="472" spans="13:21">
       <c r="M472" s="22" t="str">
-        <f t="shared" ref="M472:M535" si="11">IF(F472="CJ", I472*200, "")</f>
+        <f t="shared" ref="M472:M535" si="12">IF(F472="CJ", I472*200, "")</f>
         <v/>
       </c>
       <c r="R472" t="str">
@@ -12792,7 +12870,7 @@
     </row>
     <row r="473" spans="13:21">
       <c r="M473" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R473" t="str">
@@ -12814,7 +12892,7 @@
     </row>
     <row r="474" spans="13:21">
       <c r="M474" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R474" t="str">
@@ -12836,7 +12914,7 @@
     </row>
     <row r="475" spans="13:21">
       <c r="M475" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R475" t="str">
@@ -12858,7 +12936,7 @@
     </row>
     <row r="476" spans="13:21">
       <c r="M476" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R476" t="str">
@@ -12880,7 +12958,7 @@
     </row>
     <row r="477" spans="13:21">
       <c r="M477" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R477" t="str">
@@ -12902,7 +12980,7 @@
     </row>
     <row r="478" spans="13:21">
       <c r="M478" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R478" t="str">
@@ -12924,7 +13002,7 @@
     </row>
     <row r="479" spans="13:21">
       <c r="M479" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R479" t="str">
@@ -12946,7 +13024,7 @@
     </row>
     <row r="480" spans="13:21">
       <c r="M480" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R480" t="str">
@@ -12968,7 +13046,7 @@
     </row>
     <row r="481" spans="13:21">
       <c r="M481" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R481" t="str">
@@ -12990,7 +13068,7 @@
     </row>
     <row r="482" spans="13:21">
       <c r="M482" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R482" t="str">
@@ -13012,7 +13090,7 @@
     </row>
     <row r="483" spans="13:21">
       <c r="M483" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R483" t="str">
@@ -13034,7 +13112,7 @@
     </row>
     <row r="484" spans="13:21">
       <c r="M484" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R484" t="str">
@@ -13056,7 +13134,7 @@
     </row>
     <row r="485" spans="13:21">
       <c r="M485" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R485" t="str">
@@ -13078,7 +13156,7 @@
     </row>
     <row r="486" spans="13:21">
       <c r="M486" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R486" t="str">
@@ -13100,7 +13178,7 @@
     </row>
     <row r="487" spans="13:21">
       <c r="M487" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R487" t="str">
@@ -13122,7 +13200,7 @@
     </row>
     <row r="488" spans="13:21">
       <c r="M488" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R488" t="str">
@@ -13144,7 +13222,7 @@
     </row>
     <row r="489" spans="13:21">
       <c r="M489" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R489" t="str">
@@ -13166,7 +13244,7 @@
     </row>
     <row r="490" spans="13:21">
       <c r="M490" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R490" t="str">
@@ -13188,7 +13266,7 @@
     </row>
     <row r="491" spans="13:21">
       <c r="M491" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R491" t="str">
@@ -13210,7 +13288,7 @@
     </row>
     <row r="492" spans="13:21">
       <c r="M492" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R492" t="str">
@@ -13232,7 +13310,7 @@
     </row>
     <row r="493" spans="13:21">
       <c r="M493" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R493" t="str">
@@ -13254,7 +13332,7 @@
     </row>
     <row r="494" spans="13:21">
       <c r="M494" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R494" t="str">
@@ -13276,7 +13354,7 @@
     </row>
     <row r="495" spans="13:21">
       <c r="M495" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R495" t="str">
@@ -13298,7 +13376,7 @@
     </row>
     <row r="496" spans="13:21">
       <c r="M496" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R496" t="str">
@@ -13320,7 +13398,7 @@
     </row>
     <row r="497" spans="13:21">
       <c r="M497" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R497" t="str">
@@ -13342,7 +13420,7 @@
     </row>
     <row r="498" spans="13:21">
       <c r="M498" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R498" t="str">
@@ -13364,7 +13442,7 @@
     </row>
     <row r="499" spans="13:21">
       <c r="M499" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R499" t="str">
@@ -13386,7 +13464,7 @@
     </row>
     <row r="500" spans="13:21">
       <c r="M500" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R500" t="str">
@@ -13408,7 +13486,7 @@
     </row>
     <row r="501" spans="13:21">
       <c r="M501" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R501" t="str">
@@ -13430,7 +13508,7 @@
     </row>
     <row r="502" spans="13:21">
       <c r="M502" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R502" t="str">
@@ -13452,7 +13530,7 @@
     </row>
     <row r="503" spans="13:21">
       <c r="M503" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R503" t="str">
@@ -13474,7 +13552,7 @@
     </row>
     <row r="504" spans="13:21">
       <c r="M504" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R504" t="str">
@@ -13496,7 +13574,7 @@
     </row>
     <row r="505" spans="13:21">
       <c r="M505" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R505" t="str">
@@ -13518,7 +13596,7 @@
     </row>
     <row r="506" spans="13:21">
       <c r="M506" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R506" t="str">
@@ -13540,7 +13618,7 @@
     </row>
     <row r="507" spans="13:21">
       <c r="M507" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R507" t="str">
@@ -13562,7 +13640,7 @@
     </row>
     <row r="508" spans="13:21">
       <c r="M508" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R508" t="str">
@@ -13584,7 +13662,7 @@
     </row>
     <row r="509" spans="13:21">
       <c r="M509" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R509" t="str">
@@ -13606,7 +13684,7 @@
     </row>
     <row r="510" spans="13:21">
       <c r="M510" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R510" t="str">
@@ -13628,7 +13706,7 @@
     </row>
     <row r="511" spans="13:21">
       <c r="M511" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R511" t="str">
@@ -13650,7 +13728,7 @@
     </row>
     <row r="512" spans="13:21">
       <c r="M512" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R512" t="str">
@@ -13672,7 +13750,7 @@
     </row>
     <row r="513" spans="13:21">
       <c r="M513" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R513" t="str">
@@ -13694,7 +13772,7 @@
     </row>
     <row r="514" spans="13:21">
       <c r="M514" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R514" t="str">
@@ -13716,7 +13794,7 @@
     </row>
     <row r="515" spans="13:21">
       <c r="M515" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R515" t="str">
@@ -13738,7 +13816,7 @@
     </row>
     <row r="516" spans="13:21">
       <c r="M516" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R516" t="str">
@@ -13760,7 +13838,7 @@
     </row>
     <row r="517" spans="13:21">
       <c r="M517" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R517" t="str">
@@ -13782,7 +13860,7 @@
     </row>
     <row r="518" spans="13:21">
       <c r="M518" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R518" t="str">
@@ -13804,7 +13882,7 @@
     </row>
     <row r="519" spans="13:21">
       <c r="M519" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R519" t="str">
@@ -13826,7 +13904,7 @@
     </row>
     <row r="520" spans="13:21">
       <c r="M520" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R520" t="str">
@@ -13848,7 +13926,7 @@
     </row>
     <row r="521" spans="13:21">
       <c r="M521" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R521" t="str">
@@ -13870,7 +13948,7 @@
     </row>
     <row r="522" spans="13:21">
       <c r="M522" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R522" t="str">
@@ -13892,7 +13970,7 @@
     </row>
     <row r="523" spans="13:21">
       <c r="M523" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R523" t="str">
@@ -13914,7 +13992,7 @@
     </row>
     <row r="524" spans="13:21">
       <c r="M524" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R524" t="str">
@@ -13936,7 +14014,7 @@
     </row>
     <row r="525" spans="13:21">
       <c r="M525" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R525" t="str">
@@ -13958,7 +14036,7 @@
     </row>
     <row r="526" spans="13:21">
       <c r="M526" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R526" t="str">
@@ -13980,7 +14058,7 @@
     </row>
     <row r="527" spans="13:21">
       <c r="M527" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R527" t="str">
@@ -14002,7 +14080,7 @@
     </row>
     <row r="528" spans="13:21">
       <c r="M528" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R528" t="str">
@@ -14024,7 +14102,7 @@
     </row>
     <row r="529" spans="13:21">
       <c r="M529" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R529" t="str">
@@ -14046,7 +14124,7 @@
     </row>
     <row r="530" spans="13:21">
       <c r="M530" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R530" t="str">
@@ -14068,7 +14146,7 @@
     </row>
     <row r="531" spans="13:21">
       <c r="M531" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R531" t="str">
@@ -14090,7 +14168,7 @@
     </row>
     <row r="532" spans="13:21">
       <c r="M532" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R532" t="str">
@@ -14112,7 +14190,7 @@
     </row>
     <row r="533" spans="13:21">
       <c r="M533" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R533" t="str">
@@ -14134,7 +14212,7 @@
     </row>
     <row r="534" spans="13:21">
       <c r="M534" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R534" t="str">
@@ -14156,7 +14234,7 @@
     </row>
     <row r="535" spans="13:21">
       <c r="M535" s="22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="R535" t="str">
@@ -14178,7 +14256,7 @@
     </row>
     <row r="536" spans="13:21">
       <c r="M536" s="22" t="str">
-        <f t="shared" ref="M536:M599" si="12">IF(F536="CJ", I536*200, "")</f>
+        <f t="shared" ref="M536:M599" si="13">IF(F536="CJ", I536*200, "")</f>
         <v/>
       </c>
       <c r="R536" t="str">
@@ -14200,7 +14278,7 @@
     </row>
     <row r="537" spans="13:21">
       <c r="M537" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R537" t="str">
@@ -14222,7 +14300,7 @@
     </row>
     <row r="538" spans="13:21">
       <c r="M538" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R538" t="str">
@@ -14244,7 +14322,7 @@
     </row>
     <row r="539" spans="13:21">
       <c r="M539" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R539" t="str">
@@ -14266,7 +14344,7 @@
     </row>
     <row r="540" spans="13:21">
       <c r="M540" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R540" t="str">
@@ -14288,7 +14366,7 @@
     </row>
     <row r="541" spans="13:21">
       <c r="M541" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R541" t="str">
@@ -14310,7 +14388,7 @@
     </row>
     <row r="542" spans="13:21">
       <c r="M542" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R542" t="str">
@@ -14332,7 +14410,7 @@
     </row>
     <row r="543" spans="13:21">
       <c r="M543" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R543" t="str">
@@ -14354,7 +14432,7 @@
     </row>
     <row r="544" spans="13:21">
       <c r="M544" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R544" t="str">
@@ -14376,7 +14454,7 @@
     </row>
     <row r="545" spans="13:21">
       <c r="M545" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R545" t="str">
@@ -14398,7 +14476,7 @@
     </row>
     <row r="546" spans="13:21">
       <c r="M546" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R546" t="str">
@@ -14420,7 +14498,7 @@
     </row>
     <row r="547" spans="13:21">
       <c r="M547" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R547" t="str">
@@ -14442,7 +14520,7 @@
     </row>
     <row r="548" spans="13:21">
       <c r="M548" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R548" t="str">
@@ -14464,7 +14542,7 @@
     </row>
     <row r="549" spans="13:21">
       <c r="M549" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R549" t="str">
@@ -14486,7 +14564,7 @@
     </row>
     <row r="550" spans="13:21">
       <c r="M550" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R550" t="str">
@@ -14508,7 +14586,7 @@
     </row>
     <row r="551" spans="13:21">
       <c r="M551" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R551" t="str">
@@ -14530,7 +14608,7 @@
     </row>
     <row r="552" spans="13:21">
       <c r="M552" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R552" t="str">
@@ -14552,7 +14630,7 @@
     </row>
     <row r="553" spans="13:21">
       <c r="M553" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R553" t="str">
@@ -14574,7 +14652,7 @@
     </row>
     <row r="554" spans="13:21">
       <c r="M554" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R554" t="str">
@@ -14596,7 +14674,7 @@
     </row>
     <row r="555" spans="13:21">
       <c r="M555" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R555" t="str">
@@ -14618,7 +14696,7 @@
     </row>
     <row r="556" spans="13:21">
       <c r="M556" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R556" t="str">
@@ -14640,7 +14718,7 @@
     </row>
     <row r="557" spans="13:21">
       <c r="M557" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R557" t="str">
@@ -14662,7 +14740,7 @@
     </row>
     <row r="558" spans="13:21">
       <c r="M558" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R558" t="str">
@@ -14684,7 +14762,7 @@
     </row>
     <row r="559" spans="13:21">
       <c r="M559" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R559" t="str">
@@ -14706,7 +14784,7 @@
     </row>
     <row r="560" spans="13:21">
       <c r="M560" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R560" t="str">
@@ -14728,7 +14806,7 @@
     </row>
     <row r="561" spans="13:21">
       <c r="M561" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R561" t="str">
@@ -14750,7 +14828,7 @@
     </row>
     <row r="562" spans="13:21">
       <c r="M562" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R562" t="str">
@@ -14772,7 +14850,7 @@
     </row>
     <row r="563" spans="13:21">
       <c r="M563" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R563" t="str">
@@ -14794,7 +14872,7 @@
     </row>
     <row r="564" spans="13:21">
       <c r="M564" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R564" t="str">
@@ -14816,7 +14894,7 @@
     </row>
     <row r="565" spans="13:21">
       <c r="M565" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R565" t="str">
@@ -14838,7 +14916,7 @@
     </row>
     <row r="566" spans="13:21">
       <c r="M566" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R566" t="str">
@@ -14860,7 +14938,7 @@
     </row>
     <row r="567" spans="13:21">
       <c r="M567" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R567" t="str">
@@ -14882,7 +14960,7 @@
     </row>
     <row r="568" spans="13:21">
       <c r="M568" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R568" t="str">
@@ -14904,7 +14982,7 @@
     </row>
     <row r="569" spans="13:21">
       <c r="M569" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R569" t="str">
@@ -14926,7 +15004,7 @@
     </row>
     <row r="570" spans="13:21">
       <c r="M570" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R570" t="str">
@@ -14948,7 +15026,7 @@
     </row>
     <row r="571" spans="13:21">
       <c r="M571" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R571" t="str">
@@ -14970,7 +15048,7 @@
     </row>
     <row r="572" spans="13:21">
       <c r="M572" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R572" t="str">
@@ -14992,7 +15070,7 @@
     </row>
     <row r="573" spans="13:21">
       <c r="M573" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R573" t="str">
@@ -15014,7 +15092,7 @@
     </row>
     <row r="574" spans="13:21">
       <c r="M574" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R574" t="str">
@@ -15036,7 +15114,7 @@
     </row>
     <row r="575" spans="13:21">
       <c r="M575" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R575" t="str">
@@ -15058,7 +15136,7 @@
     </row>
     <row r="576" spans="13:21">
       <c r="M576" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R576" t="str">
@@ -15080,7 +15158,7 @@
     </row>
     <row r="577" spans="13:21">
       <c r="M577" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R577" t="str">
@@ -15102,7 +15180,7 @@
     </row>
     <row r="578" spans="13:21">
       <c r="M578" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R578" t="str">
@@ -15124,7 +15202,7 @@
     </row>
     <row r="579" spans="13:21">
       <c r="M579" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R579" t="str">
@@ -15146,7 +15224,7 @@
     </row>
     <row r="580" spans="13:21">
       <c r="M580" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R580" t="str">
@@ -15168,7 +15246,7 @@
     </row>
     <row r="581" spans="13:21">
       <c r="M581" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R581" t="str">
@@ -15190,7 +15268,7 @@
     </row>
     <row r="582" spans="13:21">
       <c r="M582" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R582" t="str">
@@ -15212,7 +15290,7 @@
     </row>
     <row r="583" spans="13:21">
       <c r="M583" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R583" t="str">
@@ -15234,7 +15312,7 @@
     </row>
     <row r="584" spans="13:21">
       <c r="M584" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R584" t="str">
@@ -15256,7 +15334,7 @@
     </row>
     <row r="585" spans="13:21">
       <c r="M585" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R585" t="str">
@@ -15278,7 +15356,7 @@
     </row>
     <row r="586" spans="13:21">
       <c r="M586" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R586" t="str">
@@ -15300,7 +15378,7 @@
     </row>
     <row r="587" spans="13:21">
       <c r="M587" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R587" t="str">
@@ -15322,7 +15400,7 @@
     </row>
     <row r="588" spans="13:21">
       <c r="M588" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R588" t="str">
@@ -15344,7 +15422,7 @@
     </row>
     <row r="589" spans="13:21">
       <c r="M589" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R589" t="str">
@@ -15366,7 +15444,7 @@
     </row>
     <row r="590" spans="13:21">
       <c r="M590" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R590" t="str">
@@ -15388,7 +15466,7 @@
     </row>
     <row r="591" spans="13:21">
       <c r="M591" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R591" t="str">
@@ -15410,7 +15488,7 @@
     </row>
     <row r="592" spans="13:21">
       <c r="M592" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R592" t="str">
@@ -15432,7 +15510,7 @@
     </row>
     <row r="593" spans="13:21">
       <c r="M593" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R593" t="str">
@@ -15454,7 +15532,7 @@
     </row>
     <row r="594" spans="13:21">
       <c r="M594" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R594" t="str">
@@ -15476,7 +15554,7 @@
     </row>
     <row r="595" spans="13:21">
       <c r="M595" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R595" t="str">
@@ -15498,7 +15576,7 @@
     </row>
     <row r="596" spans="13:21">
       <c r="M596" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R596" t="str">
@@ -15520,7 +15598,7 @@
     </row>
     <row r="597" spans="13:21">
       <c r="M597" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R597" t="str">
@@ -15542,7 +15620,7 @@
     </row>
     <row r="598" spans="13:21">
       <c r="M598" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R598" t="str">
@@ -15564,7 +15642,7 @@
     </row>
     <row r="599" spans="13:21">
       <c r="M599" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="R599" t="str">
@@ -15586,7 +15664,7 @@
     </row>
     <row r="600" spans="13:21">
       <c r="M600" s="22" t="str">
-        <f t="shared" ref="M600:M663" si="13">IF(F600="CJ", I600*200, "")</f>
+        <f t="shared" ref="M600:M663" si="14">IF(F600="CJ", I600*200, "")</f>
         <v/>
       </c>
       <c r="R600" t="str">
@@ -15608,7 +15686,7 @@
     </row>
     <row r="601" spans="13:21">
       <c r="M601" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R601" t="str">
@@ -15630,7 +15708,7 @@
     </row>
     <row r="602" spans="13:21">
       <c r="M602" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R602" t="str">
@@ -15652,7 +15730,7 @@
     </row>
     <row r="603" spans="13:21">
       <c r="M603" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R603" t="str">
@@ -15674,7 +15752,7 @@
     </row>
     <row r="604" spans="13:21">
       <c r="M604" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R604" t="str">
@@ -15696,7 +15774,7 @@
     </row>
     <row r="605" spans="13:21">
       <c r="M605" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R605" t="str">
@@ -15718,7 +15796,7 @@
     </row>
     <row r="606" spans="13:21">
       <c r="M606" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R606" t="str">
@@ -15740,7 +15818,7 @@
     </row>
     <row r="607" spans="13:21">
       <c r="M607" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R607" t="str">
@@ -15762,7 +15840,7 @@
     </row>
     <row r="608" spans="13:21">
       <c r="M608" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R608" t="str">
@@ -15784,7 +15862,7 @@
     </row>
     <row r="609" spans="13:21">
       <c r="M609" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R609" t="str">
@@ -15806,7 +15884,7 @@
     </row>
     <row r="610" spans="13:21">
       <c r="M610" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R610" t="str">
@@ -15828,7 +15906,7 @@
     </row>
     <row r="611" spans="13:21">
       <c r="M611" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R611" t="str">
@@ -15850,7 +15928,7 @@
     </row>
     <row r="612" spans="13:21">
       <c r="M612" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R612" t="str">
@@ -15872,7 +15950,7 @@
     </row>
     <row r="613" spans="13:21">
       <c r="M613" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R613" t="str">
@@ -15894,7 +15972,7 @@
     </row>
     <row r="614" spans="13:21">
       <c r="M614" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R614" t="str">
@@ -15916,7 +15994,7 @@
     </row>
     <row r="615" spans="13:21">
       <c r="M615" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R615" t="str">
@@ -15938,7 +16016,7 @@
     </row>
     <row r="616" spans="13:21">
       <c r="M616" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R616" t="str">
@@ -15960,7 +16038,7 @@
     </row>
     <row r="617" spans="13:21">
       <c r="M617" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R617" t="str">
@@ -15982,7 +16060,7 @@
     </row>
     <row r="618" spans="13:21">
       <c r="M618" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R618" t="str">
@@ -16004,7 +16082,7 @@
     </row>
     <row r="619" spans="13:21">
       <c r="M619" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R619" t="str">
@@ -16026,7 +16104,7 @@
     </row>
     <row r="620" spans="13:21">
       <c r="M620" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R620" t="str">
@@ -16048,7 +16126,7 @@
     </row>
     <row r="621" spans="13:21">
       <c r="M621" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R621" t="str">
@@ -16070,7 +16148,7 @@
     </row>
     <row r="622" spans="13:21">
       <c r="M622" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R622" t="str">
@@ -16092,7 +16170,7 @@
     </row>
     <row r="623" spans="13:21">
       <c r="M623" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R623" t="str">
@@ -16114,7 +16192,7 @@
     </row>
     <row r="624" spans="13:21">
       <c r="M624" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R624" t="str">
@@ -16136,7 +16214,7 @@
     </row>
     <row r="625" spans="13:21">
       <c r="M625" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R625" t="str">
@@ -16158,7 +16236,7 @@
     </row>
     <row r="626" spans="13:21">
       <c r="M626" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R626" t="str">
@@ -16180,7 +16258,7 @@
     </row>
     <row r="627" spans="13:21">
       <c r="M627" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R627" t="str">
@@ -16202,7 +16280,7 @@
     </row>
     <row r="628" spans="13:21">
       <c r="M628" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R628" t="str">
@@ -16224,7 +16302,7 @@
     </row>
     <row r="629" spans="13:21">
       <c r="M629" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R629" t="str">
@@ -16246,7 +16324,7 @@
     </row>
     <row r="630" spans="13:21">
       <c r="M630" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R630" t="str">
@@ -16268,7 +16346,7 @@
     </row>
     <row r="631" spans="13:21">
       <c r="M631" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R631" t="str">
@@ -16290,7 +16368,7 @@
     </row>
     <row r="632" spans="13:21">
       <c r="M632" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R632" t="str">
@@ -16312,7 +16390,7 @@
     </row>
     <row r="633" spans="13:21">
       <c r="M633" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R633" t="str">
@@ -16334,7 +16412,7 @@
     </row>
     <row r="634" spans="13:21">
       <c r="M634" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R634" t="str">
@@ -16356,7 +16434,7 @@
     </row>
     <row r="635" spans="13:21">
       <c r="M635" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R635" t="str">
@@ -16378,7 +16456,7 @@
     </row>
     <row r="636" spans="13:21">
       <c r="M636" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R636" t="str">
@@ -16400,7 +16478,7 @@
     </row>
     <row r="637" spans="13:21">
       <c r="M637" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R637" t="str">
@@ -16422,7 +16500,7 @@
     </row>
     <row r="638" spans="13:21">
       <c r="M638" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R638" t="str">
@@ -16444,7 +16522,7 @@
     </row>
     <row r="639" spans="13:21">
       <c r="M639" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R639" t="str">
@@ -16466,7 +16544,7 @@
     </row>
     <row r="640" spans="13:21">
       <c r="M640" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R640" t="str">
@@ -16488,7 +16566,7 @@
     </row>
     <row r="641" spans="13:21">
       <c r="M641" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R641" t="str">
@@ -16510,7 +16588,7 @@
     </row>
     <row r="642" spans="13:21">
       <c r="M642" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R642" t="str">
@@ -16532,7 +16610,7 @@
     </row>
     <row r="643" spans="13:21">
       <c r="M643" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R643" t="str">
@@ -16554,7 +16632,7 @@
     </row>
     <row r="644" spans="13:21">
       <c r="M644" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R644" t="str">
@@ -16576,7 +16654,7 @@
     </row>
     <row r="645" spans="13:21">
       <c r="M645" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R645" t="str">
@@ -16598,7 +16676,7 @@
     </row>
     <row r="646" spans="13:21">
       <c r="M646" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R646" t="str">
@@ -16620,7 +16698,7 @@
     </row>
     <row r="647" spans="13:21">
       <c r="M647" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R647" t="str">
@@ -16642,7 +16720,7 @@
     </row>
     <row r="648" spans="13:21">
       <c r="M648" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R648" t="str">
@@ -16664,7 +16742,7 @@
     </row>
     <row r="649" spans="13:21">
       <c r="M649" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R649" t="str">
@@ -16686,7 +16764,7 @@
     </row>
     <row r="650" spans="13:21">
       <c r="M650" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R650" t="str">
@@ -16708,7 +16786,7 @@
     </row>
     <row r="651" spans="13:21">
       <c r="M651" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R651" t="str">
@@ -16730,7 +16808,7 @@
     </row>
     <row r="652" spans="13:21">
       <c r="M652" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R652" t="str">
@@ -16752,7 +16830,7 @@
     </row>
     <row r="653" spans="13:21">
       <c r="M653" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R653" t="str">
@@ -16774,7 +16852,7 @@
     </row>
     <row r="654" spans="13:21">
       <c r="M654" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R654" t="str">
@@ -16796,7 +16874,7 @@
     </row>
     <row r="655" spans="13:21">
       <c r="M655" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R655" t="str">
@@ -16818,7 +16896,7 @@
     </row>
     <row r="656" spans="13:21">
       <c r="M656" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R656" t="str">
@@ -16840,7 +16918,7 @@
     </row>
     <row r="657" spans="13:21">
       <c r="M657" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R657" t="str">
@@ -16862,7 +16940,7 @@
     </row>
     <row r="658" spans="13:21">
       <c r="M658" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R658" t="str">
@@ -16884,7 +16962,7 @@
     </row>
     <row r="659" spans="13:21">
       <c r="M659" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R659" t="str">
@@ -16906,7 +16984,7 @@
     </row>
     <row r="660" spans="13:21">
       <c r="M660" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R660" t="str">
@@ -16928,7 +17006,7 @@
     </row>
     <row r="661" spans="13:21">
       <c r="M661" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R661" t="str">
@@ -16950,7 +17028,7 @@
     </row>
     <row r="662" spans="13:21">
       <c r="M662" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R662" t="str">
@@ -16972,7 +17050,7 @@
     </row>
     <row r="663" spans="13:21">
       <c r="M663" s="22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="R663" t="str">
@@ -16994,7 +17072,7 @@
     </row>
     <row r="664" spans="13:21">
       <c r="M664" s="22" t="str">
-        <f t="shared" ref="M664:M727" si="14">IF(F664="CJ", I664*200, "")</f>
+        <f t="shared" ref="M664:M727" si="15">IF(F664="CJ", I664*200, "")</f>
         <v/>
       </c>
       <c r="R664" t="str">
@@ -17016,7 +17094,7 @@
     </row>
     <row r="665" spans="13:21">
       <c r="M665" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R665" t="str">
@@ -17038,7 +17116,7 @@
     </row>
     <row r="666" spans="13:21">
       <c r="M666" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R666" t="str">
@@ -17060,7 +17138,7 @@
     </row>
     <row r="667" spans="13:21">
       <c r="M667" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R667" t="str">
@@ -17082,7 +17160,7 @@
     </row>
     <row r="668" spans="13:21">
       <c r="M668" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R668" t="str">
@@ -17104,7 +17182,7 @@
     </row>
     <row r="669" spans="13:21">
       <c r="M669" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R669" t="str">
@@ -17126,7 +17204,7 @@
     </row>
     <row r="670" spans="13:21">
       <c r="M670" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R670" t="str">
@@ -17148,7 +17226,7 @@
     </row>
     <row r="671" spans="13:21">
       <c r="M671" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R671" t="str">
@@ -17170,7 +17248,7 @@
     </row>
     <row r="672" spans="13:21">
       <c r="M672" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R672" t="str">
@@ -17192,7 +17270,7 @@
     </row>
     <row r="673" spans="13:21">
       <c r="M673" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R673" t="str">
@@ -17214,7 +17292,7 @@
     </row>
     <row r="674" spans="13:21">
       <c r="M674" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R674" t="str">
@@ -17236,7 +17314,7 @@
     </row>
     <row r="675" spans="13:21">
       <c r="M675" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R675" t="str">
@@ -17258,7 +17336,7 @@
     </row>
     <row r="676" spans="13:21">
       <c r="M676" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R676" t="str">
@@ -17280,7 +17358,7 @@
     </row>
     <row r="677" spans="13:21">
       <c r="M677" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R677" t="str">
@@ -17302,7 +17380,7 @@
     </row>
     <row r="678" spans="13:21">
       <c r="M678" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R678" t="str">
@@ -17324,7 +17402,7 @@
     </row>
     <row r="679" spans="13:21">
       <c r="M679" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R679" t="str">
@@ -17346,7 +17424,7 @@
     </row>
     <row r="680" spans="13:21">
       <c r="M680" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R680" t="str">
@@ -17368,7 +17446,7 @@
     </row>
     <row r="681" spans="13:21">
       <c r="M681" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R681" t="str">
@@ -17390,7 +17468,7 @@
     </row>
     <row r="682" spans="13:21">
       <c r="M682" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R682" t="str">
@@ -17412,7 +17490,7 @@
     </row>
     <row r="683" spans="13:21">
       <c r="M683" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R683" t="str">
@@ -17434,7 +17512,7 @@
     </row>
     <row r="684" spans="13:21">
       <c r="M684" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R684" t="str">
@@ -17456,7 +17534,7 @@
     </row>
     <row r="685" spans="13:21">
       <c r="M685" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R685" t="str">
@@ -17478,7 +17556,7 @@
     </row>
     <row r="686" spans="13:21">
       <c r="M686" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R686" t="str">
@@ -17500,7 +17578,7 @@
     </row>
     <row r="687" spans="13:21">
       <c r="M687" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R687" t="str">
@@ -17522,7 +17600,7 @@
     </row>
     <row r="688" spans="13:21">
       <c r="M688" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R688" t="str">
@@ -17544,7 +17622,7 @@
     </row>
     <row r="689" spans="13:21">
       <c r="M689" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R689" t="str">
@@ -17566,7 +17644,7 @@
     </row>
     <row r="690" spans="13:21">
       <c r="M690" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R690" t="str">
@@ -17588,7 +17666,7 @@
     </row>
     <row r="691" spans="13:21">
       <c r="M691" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R691" t="str">
@@ -17610,7 +17688,7 @@
     </row>
     <row r="692" spans="13:21">
       <c r="M692" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R692" t="str">
@@ -17632,7 +17710,7 @@
     </row>
     <row r="693" spans="13:21">
       <c r="M693" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R693" t="str">
@@ -17654,7 +17732,7 @@
     </row>
     <row r="694" spans="13:21">
       <c r="M694" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R694" t="str">
@@ -17676,7 +17754,7 @@
     </row>
     <row r="695" spans="13:21">
       <c r="M695" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R695" t="str">
@@ -17698,7 +17776,7 @@
     </row>
     <row r="696" spans="13:21">
       <c r="M696" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R696" t="str">
@@ -17720,7 +17798,7 @@
     </row>
     <row r="697" spans="13:21">
       <c r="M697" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R697" t="str">
@@ -17742,7 +17820,7 @@
     </row>
     <row r="698" spans="13:21">
       <c r="M698" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R698" t="str">
@@ -17764,7 +17842,7 @@
     </row>
     <row r="699" spans="13:21">
       <c r="M699" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R699" t="str">
@@ -17786,7 +17864,7 @@
     </row>
     <row r="700" spans="13:21">
       <c r="M700" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R700" t="str">
@@ -17808,7 +17886,7 @@
     </row>
     <row r="701" spans="13:21">
       <c r="M701" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R701" t="str">
@@ -17830,7 +17908,7 @@
     </row>
     <row r="702" spans="13:21">
       <c r="M702" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R702" t="str">
@@ -17852,7 +17930,7 @@
     </row>
     <row r="703" spans="13:21">
       <c r="M703" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R703" t="str">
@@ -17874,7 +17952,7 @@
     </row>
     <row r="704" spans="13:21">
       <c r="M704" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R704" t="str">
@@ -17896,7 +17974,7 @@
     </row>
     <row r="705" spans="13:21">
       <c r="M705" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R705" t="str">
@@ -17918,7 +17996,7 @@
     </row>
     <row r="706" spans="13:21">
       <c r="M706" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R706" t="str">
@@ -17940,7 +18018,7 @@
     </row>
     <row r="707" spans="13:21">
       <c r="M707" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R707" t="str">
@@ -17962,7 +18040,7 @@
     </row>
     <row r="708" spans="13:21">
       <c r="M708" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R708" t="str">
@@ -17984,7 +18062,7 @@
     </row>
     <row r="709" spans="13:21">
       <c r="M709" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R709" t="str">
@@ -18006,7 +18084,7 @@
     </row>
     <row r="710" spans="13:21">
       <c r="M710" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R710" t="str">
@@ -18028,7 +18106,7 @@
     </row>
     <row r="711" spans="13:21">
       <c r="M711" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R711" t="str">
@@ -18050,7 +18128,7 @@
     </row>
     <row r="712" spans="13:21">
       <c r="M712" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R712" t="str">
@@ -18072,7 +18150,7 @@
     </row>
     <row r="713" spans="13:21">
       <c r="M713" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R713" t="str">
@@ -18094,7 +18172,7 @@
     </row>
     <row r="714" spans="13:21">
       <c r="M714" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R714" t="str">
@@ -18116,7 +18194,7 @@
     </row>
     <row r="715" spans="13:21">
       <c r="M715" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R715" t="str">
@@ -18138,7 +18216,7 @@
     </row>
     <row r="716" spans="13:21">
       <c r="M716" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R716" t="str">
@@ -18160,7 +18238,7 @@
     </row>
     <row r="717" spans="13:21">
       <c r="M717" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R717" t="str">
@@ -18182,7 +18260,7 @@
     </row>
     <row r="718" spans="13:21">
       <c r="M718" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R718" t="str">
@@ -18204,7 +18282,7 @@
     </row>
     <row r="719" spans="13:21">
       <c r="M719" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R719" t="str">
@@ -18226,7 +18304,7 @@
     </row>
     <row r="720" spans="13:21">
       <c r="M720" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R720" t="str">
@@ -18248,7 +18326,7 @@
     </row>
     <row r="721" spans="13:21">
       <c r="M721" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R721" t="str">
@@ -18270,7 +18348,7 @@
     </row>
     <row r="722" spans="13:21">
       <c r="M722" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R722" t="str">
@@ -18292,7 +18370,7 @@
     </row>
     <row r="723" spans="13:21">
       <c r="M723" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R723" t="str">
@@ -18314,7 +18392,7 @@
     </row>
     <row r="724" spans="13:21">
       <c r="M724" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R724" t="str">
@@ -18336,7 +18414,7 @@
     </row>
     <row r="725" spans="13:21">
       <c r="M725" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R725" t="str">
@@ -18358,7 +18436,7 @@
     </row>
     <row r="726" spans="13:21">
       <c r="M726" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R726" t="str">
@@ -18380,7 +18458,7 @@
     </row>
     <row r="727" spans="13:21">
       <c r="M727" s="22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R727" t="str">
@@ -18402,7 +18480,7 @@
     </row>
     <row r="728" spans="13:21">
       <c r="M728" s="22" t="str">
-        <f t="shared" ref="M728:M791" si="15">IF(F728="CJ", I728*200, "")</f>
+        <f t="shared" ref="M728:M791" si="16">IF(F728="CJ", I728*200, "")</f>
         <v/>
       </c>
       <c r="R728" t="str">
@@ -18424,7 +18502,7 @@
     </row>
     <row r="729" spans="13:21">
       <c r="M729" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R729" t="str">
@@ -18446,7 +18524,7 @@
     </row>
     <row r="730" spans="13:21">
       <c r="M730" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R730" t="str">
@@ -18468,7 +18546,7 @@
     </row>
     <row r="731" spans="13:21">
       <c r="M731" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R731" t="str">
@@ -18490,7 +18568,7 @@
     </row>
     <row r="732" spans="13:21">
       <c r="M732" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R732" t="str">
@@ -18512,7 +18590,7 @@
     </row>
     <row r="733" spans="13:21">
       <c r="M733" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R733" t="str">
@@ -18534,7 +18612,7 @@
     </row>
     <row r="734" spans="13:21">
       <c r="M734" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R734" t="str">
@@ -18556,7 +18634,7 @@
     </row>
     <row r="735" spans="13:21">
       <c r="M735" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R735" t="str">
@@ -18578,7 +18656,7 @@
     </row>
     <row r="736" spans="13:21">
       <c r="M736" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R736" t="str">
@@ -18600,7 +18678,7 @@
     </row>
     <row r="737" spans="13:21">
       <c r="M737" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R737" t="str">
@@ -18622,7 +18700,7 @@
     </row>
     <row r="738" spans="13:21">
       <c r="M738" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R738" t="str">
@@ -18644,7 +18722,7 @@
     </row>
     <row r="739" spans="13:21">
       <c r="M739" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R739" t="str">
@@ -18666,7 +18744,7 @@
     </row>
     <row r="740" spans="13:21">
       <c r="M740" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R740" t="str">
@@ -18688,7 +18766,7 @@
     </row>
     <row r="741" spans="13:21">
       <c r="M741" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R741" t="str">
@@ -18710,7 +18788,7 @@
     </row>
     <row r="742" spans="13:21">
       <c r="M742" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R742" t="str">
@@ -18732,7 +18810,7 @@
     </row>
     <row r="743" spans="13:21">
       <c r="M743" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R743" t="str">
@@ -18754,7 +18832,7 @@
     </row>
     <row r="744" spans="13:21">
       <c r="M744" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R744" t="str">
@@ -18776,7 +18854,7 @@
     </row>
     <row r="745" spans="13:21">
       <c r="M745" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R745" t="str">
@@ -18798,7 +18876,7 @@
     </row>
     <row r="746" spans="13:21">
       <c r="M746" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R746" t="str">
@@ -18820,7 +18898,7 @@
     </row>
     <row r="747" spans="13:21">
       <c r="M747" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R747" t="str">
@@ -18842,7 +18920,7 @@
     </row>
     <row r="748" spans="13:21">
       <c r="M748" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R748" t="str">
@@ -18864,7 +18942,7 @@
     </row>
     <row r="749" spans="13:21">
       <c r="M749" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R749" t="str">
@@ -18886,7 +18964,7 @@
     </row>
     <row r="750" spans="13:21">
       <c r="M750" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R750" t="str">
@@ -18908,7 +18986,7 @@
     </row>
     <row r="751" spans="13:21">
       <c r="M751" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R751" t="str">
@@ -18930,7 +19008,7 @@
     </row>
     <row r="752" spans="13:21">
       <c r="M752" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R752" t="str">
@@ -18952,7 +19030,7 @@
     </row>
     <row r="753" spans="13:21">
       <c r="M753" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R753" t="str">
@@ -18974,7 +19052,7 @@
     </row>
     <row r="754" spans="13:21">
       <c r="M754" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R754" t="str">
@@ -18996,7 +19074,7 @@
     </row>
     <row r="755" spans="13:21">
       <c r="M755" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R755" t="str">
@@ -19018,7 +19096,7 @@
     </row>
     <row r="756" spans="13:21">
       <c r="M756" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R756" t="str">
@@ -19040,7 +19118,7 @@
     </row>
     <row r="757" spans="13:21">
       <c r="M757" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R757" t="str">
@@ -19062,7 +19140,7 @@
     </row>
     <row r="758" spans="13:21">
       <c r="M758" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R758" t="str">
@@ -19084,7 +19162,7 @@
     </row>
     <row r="759" spans="13:21">
       <c r="M759" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R759" t="str">
@@ -19106,7 +19184,7 @@
     </row>
     <row r="760" spans="13:21">
       <c r="M760" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R760" t="str">
@@ -19128,7 +19206,7 @@
     </row>
     <row r="761" spans="13:21">
       <c r="M761" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R761" t="str">
@@ -19150,7 +19228,7 @@
     </row>
     <row r="762" spans="13:21">
       <c r="M762" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R762" t="str">
@@ -19172,7 +19250,7 @@
     </row>
     <row r="763" spans="13:21">
       <c r="M763" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R763" t="str">
@@ -19194,7 +19272,7 @@
     </row>
     <row r="764" spans="13:21">
       <c r="M764" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R764" t="str">
@@ -19216,7 +19294,7 @@
     </row>
     <row r="765" spans="13:21">
       <c r="M765" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R765" t="str">
@@ -19238,7 +19316,7 @@
     </row>
     <row r="766" spans="13:21">
       <c r="M766" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R766" t="str">
@@ -19260,7 +19338,7 @@
     </row>
     <row r="767" spans="13:21">
       <c r="M767" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R767" t="str">
@@ -19282,7 +19360,7 @@
     </row>
     <row r="768" spans="13:21">
       <c r="M768" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R768" t="str">
@@ -19304,7 +19382,7 @@
     </row>
     <row r="769" spans="13:21">
       <c r="M769" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R769" t="str">
@@ -19326,7 +19404,7 @@
     </row>
     <row r="770" spans="13:21">
       <c r="M770" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R770" t="str">
@@ -19348,7 +19426,7 @@
     </row>
     <row r="771" spans="13:21">
       <c r="M771" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R771" t="str">
@@ -19370,7 +19448,7 @@
     </row>
     <row r="772" spans="13:21">
       <c r="M772" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R772" t="str">
@@ -19392,7 +19470,7 @@
     </row>
     <row r="773" spans="13:21">
       <c r="M773" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R773" t="str">
@@ -19414,7 +19492,7 @@
     </row>
     <row r="774" spans="13:21">
       <c r="M774" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R774" t="str">
@@ -19436,7 +19514,7 @@
     </row>
     <row r="775" spans="13:21">
       <c r="M775" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R775" t="str">
@@ -19458,7 +19536,7 @@
     </row>
     <row r="776" spans="13:21">
       <c r="M776" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R776" t="str">
@@ -19480,7 +19558,7 @@
     </row>
     <row r="777" spans="13:21">
       <c r="M777" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R777" t="str">
@@ -19502,7 +19580,7 @@
     </row>
     <row r="778" spans="13:21">
       <c r="M778" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R778" t="str">
@@ -19524,7 +19602,7 @@
     </row>
     <row r="779" spans="13:21">
       <c r="M779" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R779" t="str">
@@ -19546,7 +19624,7 @@
     </row>
     <row r="780" spans="13:21">
       <c r="M780" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R780" t="str">
@@ -19568,7 +19646,7 @@
     </row>
     <row r="781" spans="13:21">
       <c r="M781" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R781" t="str">
@@ -19590,7 +19668,7 @@
     </row>
     <row r="782" spans="13:21">
       <c r="M782" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R782" t="str">
@@ -19612,7 +19690,7 @@
     </row>
     <row r="783" spans="13:21">
       <c r="M783" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R783" t="str">
@@ -19634,7 +19712,7 @@
     </row>
     <row r="784" spans="13:21">
       <c r="M784" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R784" t="str">
@@ -19656,7 +19734,7 @@
     </row>
     <row r="785" spans="13:21">
       <c r="M785" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R785" t="str">
@@ -19678,7 +19756,7 @@
     </row>
     <row r="786" spans="13:21">
       <c r="M786" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R786" t="str">
@@ -19700,7 +19778,7 @@
     </row>
     <row r="787" spans="13:21">
       <c r="M787" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R787" t="str">
@@ -19722,7 +19800,7 @@
     </row>
     <row r="788" spans="13:21">
       <c r="M788" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R788" t="str">
@@ -19744,7 +19822,7 @@
     </row>
     <row r="789" spans="13:21">
       <c r="M789" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R789" t="str">
@@ -19766,7 +19844,7 @@
     </row>
     <row r="790" spans="13:21">
       <c r="M790" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R790" t="str">
@@ -19788,7 +19866,7 @@
     </row>
     <row r="791" spans="13:21">
       <c r="M791" s="22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R791" t="str">
@@ -19810,7 +19888,7 @@
     </row>
     <row r="792" spans="13:21">
       <c r="M792" s="22" t="str">
-        <f t="shared" ref="M792:M855" si="16">IF(F792="CJ", I792*200, "")</f>
+        <f t="shared" ref="M792:M855" si="17">IF(F792="CJ", I792*200, "")</f>
         <v/>
       </c>
       <c r="R792" t="str">
@@ -19832,7 +19910,7 @@
     </row>
     <row r="793" spans="13:21">
       <c r="M793" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R793" t="str">
@@ -19854,7 +19932,7 @@
     </row>
     <row r="794" spans="13:21">
       <c r="M794" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R794" t="str">
@@ -19876,7 +19954,7 @@
     </row>
     <row r="795" spans="13:21">
       <c r="M795" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R795" t="str">
@@ -19898,7 +19976,7 @@
     </row>
     <row r="796" spans="13:21">
       <c r="M796" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R796" t="str">
@@ -19920,7 +19998,7 @@
     </row>
     <row r="797" spans="13:21">
       <c r="M797" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R797" t="str">
@@ -19942,7 +20020,7 @@
     </row>
     <row r="798" spans="13:21">
       <c r="M798" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R798" t="str">
@@ -19964,7 +20042,7 @@
     </row>
     <row r="799" spans="13:21">
       <c r="M799" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R799" t="str">
@@ -19986,7 +20064,7 @@
     </row>
     <row r="800" spans="13:21">
       <c r="M800" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R800" t="str">
@@ -20008,7 +20086,7 @@
     </row>
     <row r="801" spans="13:21">
       <c r="M801" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R801" t="str">
@@ -20030,7 +20108,7 @@
     </row>
     <row r="802" spans="13:21">
       <c r="M802" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R802" t="str">
@@ -20052,7 +20130,7 @@
     </row>
     <row r="803" spans="13:21">
       <c r="M803" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R803" t="str">
@@ -20074,7 +20152,7 @@
     </row>
     <row r="804" spans="13:21">
       <c r="M804" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R804" t="str">
@@ -20096,7 +20174,7 @@
     </row>
     <row r="805" spans="13:21">
       <c r="M805" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R805" t="str">
@@ -20118,7 +20196,7 @@
     </row>
     <row r="806" spans="13:21">
       <c r="M806" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R806" t="str">
@@ -20140,7 +20218,7 @@
     </row>
     <row r="807" spans="13:21">
       <c r="M807" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R807" t="str">
@@ -20162,7 +20240,7 @@
     </row>
     <row r="808" spans="13:21">
       <c r="M808" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R808" t="str">
@@ -20184,7 +20262,7 @@
     </row>
     <row r="809" spans="13:21">
       <c r="M809" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R809" t="str">
@@ -20206,7 +20284,7 @@
     </row>
     <row r="810" spans="13:21">
       <c r="M810" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R810" t="str">
@@ -20228,7 +20306,7 @@
     </row>
     <row r="811" spans="13:21">
       <c r="M811" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R811" t="str">
@@ -20250,7 +20328,7 @@
     </row>
     <row r="812" spans="13:21">
       <c r="M812" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R812" t="str">
@@ -20272,7 +20350,7 @@
     </row>
     <row r="813" spans="13:21">
       <c r="M813" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R813" t="str">
@@ -20294,7 +20372,7 @@
     </row>
     <row r="814" spans="13:21">
       <c r="M814" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R814" t="str">
@@ -20316,7 +20394,7 @@
     </row>
     <row r="815" spans="13:21">
       <c r="M815" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R815" t="str">
@@ -20338,7 +20416,7 @@
     </row>
     <row r="816" spans="13:21">
       <c r="M816" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R816" t="str">
@@ -20360,7 +20438,7 @@
     </row>
     <row r="817" spans="13:21">
       <c r="M817" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R817" t="str">
@@ -20382,7 +20460,7 @@
     </row>
     <row r="818" spans="13:21">
       <c r="M818" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R818" t="str">
@@ -20404,7 +20482,7 @@
     </row>
     <row r="819" spans="13:21">
       <c r="M819" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R819" t="str">
@@ -20426,7 +20504,7 @@
     </row>
     <row r="820" spans="13:21">
       <c r="M820" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R820" t="str">
@@ -20448,7 +20526,7 @@
     </row>
     <row r="821" spans="13:21">
       <c r="M821" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R821" t="str">
@@ -20470,7 +20548,7 @@
     </row>
     <row r="822" spans="13:21">
       <c r="M822" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R822" t="str">
@@ -20492,7 +20570,7 @@
     </row>
     <row r="823" spans="13:21">
       <c r="M823" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R823" t="str">
@@ -20514,7 +20592,7 @@
     </row>
     <row r="824" spans="13:21">
       <c r="M824" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R824" t="str">
@@ -20536,7 +20614,7 @@
     </row>
     <row r="825" spans="13:21">
       <c r="M825" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R825" t="str">
@@ -20558,7 +20636,7 @@
     </row>
     <row r="826" spans="13:21">
       <c r="M826" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R826" t="str">
@@ -20580,7 +20658,7 @@
     </row>
     <row r="827" spans="13:21">
       <c r="M827" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R827" t="str">
@@ -20602,7 +20680,7 @@
     </row>
     <row r="828" spans="13:21">
       <c r="M828" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R828" t="str">
@@ -20624,7 +20702,7 @@
     </row>
     <row r="829" spans="13:21">
       <c r="M829" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R829" t="str">
@@ -20646,7 +20724,7 @@
     </row>
     <row r="830" spans="13:21">
       <c r="M830" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R830" t="str">
@@ -20668,7 +20746,7 @@
     </row>
     <row r="831" spans="13:21">
       <c r="M831" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R831" t="str">
@@ -20690,7 +20768,7 @@
     </row>
     <row r="832" spans="13:21">
       <c r="M832" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R832" t="str">
@@ -20712,7 +20790,7 @@
     </row>
     <row r="833" spans="13:21">
       <c r="M833" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R833" t="str">
@@ -20734,7 +20812,7 @@
     </row>
     <row r="834" spans="13:21">
       <c r="M834" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R834" t="str">
@@ -20756,7 +20834,7 @@
     </row>
     <row r="835" spans="13:21">
       <c r="M835" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R835" t="str">
@@ -20778,7 +20856,7 @@
     </row>
     <row r="836" spans="13:21">
       <c r="M836" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R836" t="str">
@@ -20800,7 +20878,7 @@
     </row>
     <row r="837" spans="13:21">
       <c r="M837" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R837" t="str">
@@ -20822,7 +20900,7 @@
     </row>
     <row r="838" spans="13:21">
       <c r="M838" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R838" t="str">
@@ -20844,7 +20922,7 @@
     </row>
     <row r="839" spans="13:21">
       <c r="M839" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R839" t="str">
@@ -20866,7 +20944,7 @@
     </row>
     <row r="840" spans="13:21">
       <c r="M840" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R840" t="str">
@@ -20888,7 +20966,7 @@
     </row>
     <row r="841" spans="13:21">
       <c r="M841" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R841" t="str">
@@ -20910,7 +20988,7 @@
     </row>
     <row r="842" spans="13:21">
       <c r="M842" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R842" t="str">
@@ -20932,7 +21010,7 @@
     </row>
     <row r="843" spans="13:21">
       <c r="M843" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R843" t="str">
@@ -20954,7 +21032,7 @@
     </row>
     <row r="844" spans="13:21">
       <c r="M844" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R844" t="str">
@@ -20976,7 +21054,7 @@
     </row>
     <row r="845" spans="13:21">
       <c r="M845" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R845" t="str">
@@ -20998,7 +21076,7 @@
     </row>
     <row r="846" spans="13:21">
       <c r="M846" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R846" t="str">
@@ -21020,7 +21098,7 @@
     </row>
     <row r="847" spans="13:21">
       <c r="M847" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R847" t="str">
@@ -21042,7 +21120,7 @@
     </row>
     <row r="848" spans="13:21">
       <c r="M848" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R848" t="str">
@@ -21064,7 +21142,7 @@
     </row>
     <row r="849" spans="13:21">
       <c r="M849" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R849" t="str">
@@ -21086,7 +21164,7 @@
     </row>
     <row r="850" spans="13:21">
       <c r="M850" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R850" t="str">
@@ -21108,7 +21186,7 @@
     </row>
     <row r="851" spans="13:21">
       <c r="M851" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R851" t="str">
@@ -21130,7 +21208,7 @@
     </row>
     <row r="852" spans="13:21">
       <c r="M852" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R852" t="str">
@@ -21152,7 +21230,7 @@
     </row>
     <row r="853" spans="13:21">
       <c r="M853" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R853" t="str">
@@ -21174,7 +21252,7 @@
     </row>
     <row r="854" spans="13:21">
       <c r="M854" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R854" t="str">
@@ -21196,7 +21274,7 @@
     </row>
     <row r="855" spans="13:21">
       <c r="M855" s="22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R855" t="str">
@@ -21218,7 +21296,7 @@
     </row>
     <row r="856" spans="13:21">
       <c r="M856" s="22" t="str">
-        <f t="shared" ref="M856:M919" si="17">IF(F856="CJ", I856*200, "")</f>
+        <f t="shared" ref="M856:M919" si="18">IF(F856="CJ", I856*200, "")</f>
         <v/>
       </c>
       <c r="R856" t="str">
@@ -21240,7 +21318,7 @@
     </row>
     <row r="857" spans="13:21">
       <c r="M857" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R857" t="str">
@@ -21262,7 +21340,7 @@
     </row>
     <row r="858" spans="13:21">
       <c r="M858" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R858" t="str">
@@ -21284,7 +21362,7 @@
     </row>
     <row r="859" spans="13:21">
       <c r="M859" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R859" t="str">
@@ -21306,7 +21384,7 @@
     </row>
     <row r="860" spans="13:21">
       <c r="M860" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R860" t="str">
@@ -21328,7 +21406,7 @@
     </row>
     <row r="861" spans="13:21">
       <c r="M861" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R861" t="str">
@@ -21350,7 +21428,7 @@
     </row>
     <row r="862" spans="13:21">
       <c r="M862" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R862" t="str">
@@ -21372,7 +21450,7 @@
     </row>
     <row r="863" spans="13:21">
       <c r="M863" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R863" t="str">
@@ -21394,7 +21472,7 @@
     </row>
     <row r="864" spans="13:21">
       <c r="M864" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R864" t="str">
@@ -21416,7 +21494,7 @@
     </row>
     <row r="865" spans="13:21">
       <c r="M865" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R865" t="str">
@@ -21438,7 +21516,7 @@
     </row>
     <row r="866" spans="13:21">
       <c r="M866" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R866" t="str">
@@ -21460,7 +21538,7 @@
     </row>
     <row r="867" spans="13:21">
       <c r="M867" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R867" t="str">
@@ -21482,7 +21560,7 @@
     </row>
     <row r="868" spans="13:21">
       <c r="M868" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R868" t="str">
@@ -21504,7 +21582,7 @@
     </row>
     <row r="869" spans="13:21">
       <c r="M869" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R869" t="str">
@@ -21526,7 +21604,7 @@
     </row>
     <row r="870" spans="13:21">
       <c r="M870" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R870" t="str">
@@ -21548,7 +21626,7 @@
     </row>
     <row r="871" spans="13:21">
       <c r="M871" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R871" t="str">
@@ -21570,7 +21648,7 @@
     </row>
     <row r="872" spans="13:21">
       <c r="M872" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R872" t="str">
@@ -21592,7 +21670,7 @@
     </row>
     <row r="873" spans="13:21">
       <c r="M873" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R873" t="str">
@@ -21614,7 +21692,7 @@
     </row>
     <row r="874" spans="13:21">
       <c r="M874" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R874" t="str">
@@ -21636,7 +21714,7 @@
     </row>
     <row r="875" spans="13:21">
       <c r="M875" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R875" t="str">
@@ -21658,7 +21736,7 @@
     </row>
     <row r="876" spans="13:21">
       <c r="M876" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R876" t="str">
@@ -21680,7 +21758,7 @@
     </row>
     <row r="877" spans="13:21">
       <c r="M877" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R877" t="str">
@@ -21702,7 +21780,7 @@
     </row>
     <row r="878" spans="13:21">
       <c r="M878" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R878" t="str">
@@ -21724,7 +21802,7 @@
     </row>
     <row r="879" spans="13:21">
       <c r="M879" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R879" t="str">
@@ -21746,7 +21824,7 @@
     </row>
     <row r="880" spans="13:21">
       <c r="M880" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R880" t="str">
@@ -21768,7 +21846,7 @@
     </row>
     <row r="881" spans="13:21">
       <c r="M881" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R881" t="str">
@@ -21790,7 +21868,7 @@
     </row>
     <row r="882" spans="13:21">
       <c r="M882" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R882" t="str">
@@ -21812,7 +21890,7 @@
     </row>
     <row r="883" spans="13:21">
       <c r="M883" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R883" t="str">
@@ -21834,7 +21912,7 @@
     </row>
     <row r="884" spans="13:21">
       <c r="M884" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R884" t="str">
@@ -21856,7 +21934,7 @@
     </row>
     <row r="885" spans="13:21">
       <c r="M885" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R885" t="str">
@@ -21878,7 +21956,7 @@
     </row>
     <row r="886" spans="13:21">
       <c r="M886" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R886" t="str">
@@ -21900,7 +21978,7 @@
     </row>
     <row r="887" spans="13:21">
       <c r="M887" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R887" t="str">
@@ -21922,7 +22000,7 @@
     </row>
     <row r="888" spans="13:21">
       <c r="M888" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R888" t="str">
@@ -21944,7 +22022,7 @@
     </row>
     <row r="889" spans="13:21">
       <c r="M889" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R889" t="str">
@@ -21966,7 +22044,7 @@
     </row>
     <row r="890" spans="13:21">
       <c r="M890" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R890" t="str">
@@ -21988,7 +22066,7 @@
     </row>
     <row r="891" spans="13:21">
       <c r="M891" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R891" t="str">
@@ -22010,7 +22088,7 @@
     </row>
     <row r="892" spans="13:21">
       <c r="M892" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R892" t="str">
@@ -22032,7 +22110,7 @@
     </row>
     <row r="893" spans="13:21">
       <c r="M893" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R893" t="str">
@@ -22054,7 +22132,7 @@
     </row>
     <row r="894" spans="13:21">
       <c r="M894" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R894" t="str">
@@ -22076,7 +22154,7 @@
     </row>
     <row r="895" spans="13:21">
       <c r="M895" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R895" t="str">
@@ -22098,7 +22176,7 @@
     </row>
     <row r="896" spans="13:21">
       <c r="M896" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R896" t="str">
@@ -22120,7 +22198,7 @@
     </row>
     <row r="897" spans="13:21">
       <c r="M897" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R897" t="str">
@@ -22142,7 +22220,7 @@
     </row>
     <row r="898" spans="13:21">
       <c r="M898" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R898" t="str">
@@ -22164,7 +22242,7 @@
     </row>
     <row r="899" spans="13:21">
       <c r="M899" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R899" t="str">
@@ -22186,7 +22264,7 @@
     </row>
     <row r="900" spans="13:21">
       <c r="M900" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R900" t="str">
@@ -22208,7 +22286,7 @@
     </row>
     <row r="901" spans="13:21">
       <c r="M901" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R901" t="str">
@@ -22230,7 +22308,7 @@
     </row>
     <row r="902" spans="13:21">
       <c r="M902" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R902" t="str">
@@ -22252,7 +22330,7 @@
     </row>
     <row r="903" spans="13:21">
       <c r="M903" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R903" t="str">
@@ -22274,7 +22352,7 @@
     </row>
     <row r="904" spans="13:21">
       <c r="M904" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R904" t="str">
@@ -22296,7 +22374,7 @@
     </row>
     <row r="905" spans="13:21">
       <c r="M905" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R905" t="str">
@@ -22318,7 +22396,7 @@
     </row>
     <row r="906" spans="13:21">
       <c r="M906" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R906" t="str">
@@ -22340,7 +22418,7 @@
     </row>
     <row r="907" spans="13:21">
       <c r="M907" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R907" t="str">
@@ -22362,7 +22440,7 @@
     </row>
     <row r="908" spans="13:21">
       <c r="M908" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R908" t="str">
@@ -22384,7 +22462,7 @@
     </row>
     <row r="909" spans="13:21">
       <c r="M909" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R909" t="str">
@@ -22406,7 +22484,7 @@
     </row>
     <row r="910" spans="13:21">
       <c r="M910" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R910" t="str">
@@ -22428,7 +22506,7 @@
     </row>
     <row r="911" spans="13:21">
       <c r="M911" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R911" t="str">
@@ -22450,7 +22528,7 @@
     </row>
     <row r="912" spans="13:21">
       <c r="M912" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R912" t="str">
@@ -22472,7 +22550,7 @@
     </row>
     <row r="913" spans="13:21">
       <c r="M913" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R913" t="str">
@@ -22494,7 +22572,7 @@
     </row>
     <row r="914" spans="13:21">
       <c r="M914" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R914" t="str">
@@ -22516,7 +22594,7 @@
     </row>
     <row r="915" spans="13:21">
       <c r="M915" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R915" t="str">
@@ -22538,7 +22616,7 @@
     </row>
     <row r="916" spans="13:21">
       <c r="M916" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R916" t="str">
@@ -22560,7 +22638,7 @@
     </row>
     <row r="917" spans="13:21">
       <c r="M917" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R917" t="str">
@@ -22582,7 +22660,7 @@
     </row>
     <row r="918" spans="13:21">
       <c r="M918" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R918" t="str">
@@ -22604,7 +22682,7 @@
     </row>
     <row r="919" spans="13:21">
       <c r="M919" s="22" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R919" t="str">
@@ -22626,7 +22704,7 @@
     </row>
     <row r="920" spans="13:21">
       <c r="M920" s="22" t="str">
-        <f t="shared" ref="M920:M983" si="18">IF(F920="CJ", I920*200, "")</f>
+        <f t="shared" ref="M920:M983" si="19">IF(F920="CJ", I920*200, "")</f>
         <v/>
       </c>
       <c r="R920" t="str">
@@ -22648,7 +22726,7 @@
     </row>
     <row r="921" spans="13:21">
       <c r="M921" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R921" t="str">
@@ -22670,7 +22748,7 @@
     </row>
     <row r="922" spans="13:21">
       <c r="M922" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R922" t="str">
@@ -22692,7 +22770,7 @@
     </row>
     <row r="923" spans="13:21">
       <c r="M923" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R923" t="str">
@@ -22714,7 +22792,7 @@
     </row>
     <row r="924" spans="13:21">
       <c r="M924" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R924" t="str">
@@ -22736,7 +22814,7 @@
     </row>
     <row r="925" spans="13:21">
       <c r="M925" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R925" t="str">
@@ -22758,7 +22836,7 @@
     </row>
     <row r="926" spans="13:21">
       <c r="M926" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R926" t="str">
@@ -22780,7 +22858,7 @@
     </row>
     <row r="927" spans="13:21">
       <c r="M927" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R927" t="str">
@@ -22802,7 +22880,7 @@
     </row>
     <row r="928" spans="13:21">
       <c r="M928" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R928" t="str">
@@ -22824,7 +22902,7 @@
     </row>
     <row r="929" spans="13:21">
       <c r="M929" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R929" t="str">
@@ -22846,7 +22924,7 @@
     </row>
     <row r="930" spans="13:21">
       <c r="M930" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R930" t="str">
@@ -22868,7 +22946,7 @@
     </row>
     <row r="931" spans="13:21">
       <c r="M931" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R931" t="str">
@@ -22890,7 +22968,7 @@
     </row>
     <row r="932" spans="13:21">
       <c r="M932" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R932" t="str">
@@ -22912,7 +22990,7 @@
     </row>
     <row r="933" spans="13:21">
       <c r="M933" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R933" t="str">
@@ -22934,7 +23012,7 @@
     </row>
     <row r="934" spans="13:21">
       <c r="M934" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R934" t="str">
@@ -22956,7 +23034,7 @@
     </row>
     <row r="935" spans="13:21">
       <c r="M935" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R935" t="str">
@@ -22978,7 +23056,7 @@
     </row>
     <row r="936" spans="13:21">
       <c r="M936" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R936" t="str">
@@ -23000,7 +23078,7 @@
     </row>
     <row r="937" spans="13:21">
       <c r="M937" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R937" t="str">
@@ -23022,7 +23100,7 @@
     </row>
     <row r="938" spans="13:21">
       <c r="M938" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R938" t="str">
@@ -23044,7 +23122,7 @@
     </row>
     <row r="939" spans="13:21">
       <c r="M939" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R939" t="str">
@@ -23066,7 +23144,7 @@
     </row>
     <row r="940" spans="13:21">
       <c r="M940" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R940" t="str">
@@ -23088,7 +23166,7 @@
     </row>
     <row r="941" spans="13:21">
       <c r="M941" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R941" t="str">
@@ -23110,7 +23188,7 @@
     </row>
     <row r="942" spans="13:21">
       <c r="M942" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R942" t="str">
@@ -23132,7 +23210,7 @@
     </row>
     <row r="943" spans="13:21">
       <c r="M943" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R943" t="str">
@@ -23154,7 +23232,7 @@
     </row>
     <row r="944" spans="13:21">
       <c r="M944" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R944" t="str">
@@ -23176,7 +23254,7 @@
     </row>
     <row r="945" spans="13:21">
       <c r="M945" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R945" t="str">
@@ -23198,7 +23276,7 @@
     </row>
     <row r="946" spans="13:21">
       <c r="M946" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R946" t="str">
@@ -23220,7 +23298,7 @@
     </row>
     <row r="947" spans="13:21">
       <c r="M947" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R947" t="str">
@@ -23242,7 +23320,7 @@
     </row>
     <row r="948" spans="13:21">
       <c r="M948" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R948" t="str">
@@ -23264,7 +23342,7 @@
     </row>
     <row r="949" spans="13:21">
       <c r="M949" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R949" t="str">
@@ -23286,7 +23364,7 @@
     </row>
     <row r="950" spans="13:21">
       <c r="M950" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R950" t="str">
@@ -23308,7 +23386,7 @@
     </row>
     <row r="951" spans="13:21">
       <c r="M951" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R951" t="str">
@@ -23330,7 +23408,7 @@
     </row>
     <row r="952" spans="13:21">
       <c r="M952" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R952" t="str">
@@ -23352,7 +23430,7 @@
     </row>
     <row r="953" spans="13:21">
       <c r="M953" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R953" t="str">
@@ -23374,7 +23452,7 @@
     </row>
     <row r="954" spans="13:21">
       <c r="M954" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R954" t="str">
@@ -23396,7 +23474,7 @@
     </row>
     <row r="955" spans="13:21">
       <c r="M955" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R955" t="str">
@@ -23418,7 +23496,7 @@
     </row>
     <row r="956" spans="13:21">
       <c r="M956" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R956" t="str">
@@ -23440,7 +23518,7 @@
     </row>
     <row r="957" spans="13:21">
       <c r="M957" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R957" t="str">
@@ -23462,7 +23540,7 @@
     </row>
     <row r="958" spans="13:21">
       <c r="M958" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R958" t="str">
@@ -23484,7 +23562,7 @@
     </row>
     <row r="959" spans="13:21">
       <c r="M959" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R959" t="str">
@@ -23506,7 +23584,7 @@
     </row>
     <row r="960" spans="13:21">
       <c r="M960" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R960" t="str">
@@ -23528,7 +23606,7 @@
     </row>
     <row r="961" spans="13:21">
       <c r="M961" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R961" t="str">
@@ -23550,7 +23628,7 @@
     </row>
     <row r="962" spans="13:21">
       <c r="M962" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R962" t="str">
@@ -23572,7 +23650,7 @@
     </row>
     <row r="963" spans="13:21">
       <c r="M963" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R963" t="str">
@@ -23594,7 +23672,7 @@
     </row>
     <row r="964" spans="13:21">
       <c r="M964" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R964" t="str">
@@ -23616,7 +23694,7 @@
     </row>
     <row r="965" spans="13:21">
       <c r="M965" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R965" t="str">
@@ -23638,7 +23716,7 @@
     </row>
     <row r="966" spans="13:21">
       <c r="M966" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R966" t="str">
@@ -23660,7 +23738,7 @@
     </row>
     <row r="967" spans="13:21">
       <c r="M967" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R967" t="str">
@@ -23682,7 +23760,7 @@
     </row>
     <row r="968" spans="13:21">
       <c r="M968" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R968" t="str">
@@ -23704,7 +23782,7 @@
     </row>
     <row r="969" spans="13:21">
       <c r="M969" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R969" t="str">
@@ -23726,7 +23804,7 @@
     </row>
     <row r="970" spans="13:21">
       <c r="M970" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R970" t="str">
@@ -23748,7 +23826,7 @@
     </row>
     <row r="971" spans="13:21">
       <c r="M971" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R971" t="str">
@@ -23770,7 +23848,7 @@
     </row>
     <row r="972" spans="13:21">
       <c r="M972" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R972" t="str">
@@ -23792,7 +23870,7 @@
     </row>
     <row r="973" spans="13:21">
       <c r="M973" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R973" t="str">
@@ -23814,7 +23892,7 @@
     </row>
     <row r="974" spans="13:21">
       <c r="M974" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R974" t="str">
@@ -23836,7 +23914,7 @@
     </row>
     <row r="975" spans="13:21">
       <c r="M975" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R975" t="str">
@@ -23858,7 +23936,7 @@
     </row>
     <row r="976" spans="13:21">
       <c r="M976" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R976" t="str">
@@ -23880,7 +23958,7 @@
     </row>
     <row r="977" spans="13:21">
       <c r="M977" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R977" t="str">
@@ -23902,7 +23980,7 @@
     </row>
     <row r="978" spans="13:21">
       <c r="M978" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R978" t="str">
@@ -23924,7 +24002,7 @@
     </row>
     <row r="979" spans="13:21">
       <c r="M979" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R979" t="str">
@@ -23946,7 +24024,7 @@
     </row>
     <row r="980" spans="13:21">
       <c r="M980" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R980" t="str">
@@ -23968,7 +24046,7 @@
     </row>
     <row r="981" spans="13:21">
       <c r="M981" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R981" t="str">
@@ -23990,7 +24068,7 @@
     </row>
     <row r="982" spans="13:21">
       <c r="M982" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R982" t="str">
@@ -24012,7 +24090,7 @@
     </row>
     <row r="983" spans="13:21">
       <c r="M983" s="22" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R983" t="str">
@@ -24034,7 +24112,7 @@
     </row>
     <row r="984" spans="13:21">
       <c r="M984" s="22" t="str">
-        <f t="shared" ref="M984:M1000" si="19">IF(F984="CJ", I984*200, "")</f>
+        <f t="shared" ref="M984:M1000" si="20">IF(F984="CJ", I984*200, "")</f>
         <v/>
       </c>
       <c r="R984" t="str">
@@ -24056,7 +24134,7 @@
     </row>
     <row r="985" spans="13:21">
       <c r="M985" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R985" t="str">
@@ -24078,7 +24156,7 @@
     </row>
     <row r="986" spans="13:21">
       <c r="M986" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R986" t="str">
@@ -24100,7 +24178,7 @@
     </row>
     <row r="987" spans="13:21">
       <c r="M987" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R987" t="str">
@@ -24122,7 +24200,7 @@
     </row>
     <row r="988" spans="13:21">
       <c r="M988" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R988" t="str">
@@ -24144,7 +24222,7 @@
     </row>
     <row r="989" spans="13:21">
       <c r="M989" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R989" t="str">
@@ -24166,7 +24244,7 @@
     </row>
     <row r="990" spans="13:21">
       <c r="M990" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R990" t="str">
@@ -24188,7 +24266,7 @@
     </row>
     <row r="991" spans="13:21">
       <c r="M991" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R991" t="str">
@@ -24210,7 +24288,7 @@
     </row>
     <row r="992" spans="13:21">
       <c r="M992" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R992" t="str">
@@ -24232,7 +24310,7 @@
     </row>
     <row r="993" spans="13:21">
       <c r="M993" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R993" t="str">
@@ -24254,7 +24332,7 @@
     </row>
     <row r="994" spans="13:21">
       <c r="M994" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R994" t="str">
@@ -24276,7 +24354,7 @@
     </row>
     <row r="995" spans="13:21">
       <c r="M995" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R995" t="str">
@@ -24298,7 +24376,7 @@
     </row>
     <row r="996" spans="13:21">
       <c r="M996" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R996" t="str">
@@ -24320,7 +24398,7 @@
     </row>
     <row r="997" spans="13:21">
       <c r="M997" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R997" t="str">
@@ -24342,7 +24420,7 @@
     </row>
     <row r="998" spans="13:21">
       <c r="M998" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R998" t="str">
@@ -24364,7 +24442,7 @@
     </row>
     <row r="999" spans="13:21">
       <c r="M999" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R999" t="str">
@@ -24386,7 +24464,7 @@
     </row>
     <row r="1000" spans="13:21">
       <c r="M1000" s="22" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R1000" t="str">
@@ -24461,7 +24539,7 @@
     <row r="6" spans="2:13" ht="24">
       <c r="B6" s="33">
         <f>'Análisis de Negocio'!B5</f>
-        <v>6735.8</v>
+        <v>7629.8</v>
       </c>
       <c r="C6" s="33">
         <f>SUMIFS('Detalles movimientos'!P$5:P$1000, 'Detalles movimientos'!F$5:F$1000, "ENAP carga")</f>
@@ -24469,7 +24547,7 @@
       </c>
       <c r="D6" s="33">
         <f>C6-B6</f>
-        <v>62249.2</v>
+        <v>61355.199999999997</v>
       </c>
       <c r="H6" s="41">
         <f>COUNTIFS('Detalles movimientos'!F$5:F$1000, "ENAP carga")</f>
@@ -32014,7 +32092,7 @@
       </c>
       <c r="B5" s="30">
         <f>SUM('Detalles movimientos'!I:I)</f>
-        <v>6735.8</v>
+        <v>7629.8</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -32023,7 +32101,7 @@
       </c>
       <c r="B6" s="30">
         <f>B4-B5</f>
-        <v>62249.2</v>
+        <v>61355.199999999997</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -32051,7 +32129,7 @@
       </c>
       <c r="B10" s="31">
         <f>SUM('Detalles movimientos'!K:K)</f>
-        <v>5997100</v>
+        <v>6951100</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -32060,7 +32138,7 @@
       </c>
       <c r="B11" s="31">
         <f>SUM('Detalles movimientos'!M:M)</f>
-        <v>1021760</v>
+        <v>1180560</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -32069,7 +32147,7 @@
       </c>
       <c r="B12" s="31">
         <f>B10-B9</f>
-        <v>-17234895</v>
+        <v>-16280895</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -32078,7 +32156,7 @@
       </c>
       <c r="B13" s="31">
         <f>B11-B10</f>
-        <v>-4975340</v>
+        <v>-5770540</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -32106,7 +32184,7 @@
       </c>
       <c r="B17" s="31">
         <f>IF(B5&gt;0, B10/B5, 0)</f>
-        <v>890.33225452062118</v>
+        <v>911.0461611051403</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -32115,7 +32193,7 @@
       </c>
       <c r="B18" s="32">
         <f>IF(B10&gt;0, B13/B10, 0)</f>
-        <v>-0.82962431842056994</v>
+        <v>-0.83016213261210459</v>
       </c>
     </row>
   </sheetData>
@@ -32184,12 +32262,12 @@
     <row r="6" spans="2:13">
       <c r="B6" s="51">
         <f>SUMIFS('Detalles movimientos'!I$5:I$1000, 'Detalles movimientos'!F$5:F$1000, "CJ")</f>
-        <v>5108.8</v>
+        <v>5902.8</v>
       </c>
       <c r="C6" s="42"/>
       <c r="E6" s="53">
         <f>SUMIFS('Detalles movimientos'!K$5:K$1000, 'Detalles movimientos'!F$5:F$1000, "CJ")</f>
-        <v>5282100</v>
+        <v>6126100</v>
       </c>
       <c r="F6" s="42"/>
       <c r="H6" s="53">
@@ -32199,7 +32277,7 @@
       <c r="I6" s="42"/>
       <c r="K6" s="53">
         <f>SUMIFS('Detalles movimientos'!M$5:M$1000, 'Detalles movimientos'!F$5:F$1000, "CJ", 'Detalles movimientos'!N$5:N$1000, "&lt;&gt;*Comision Pagada*")</f>
-        <v>536000</v>
+        <v>694800</v>
       </c>
       <c r="L6" s="42"/>
     </row>
@@ -32230,7 +32308,7 @@
       <c r="I9" s="46"/>
       <c r="J9" s="49" t="str">
         <f>"Del " &amp; TEXT(_xlfn.MINIFS('Detalles movimientos'!C$5:C$1000, 'Detalles movimientos'!F$5:F$1000, "CJ", 'Detalles movimientos'!N$5:N$1000, "&lt;&gt;*Comision Pagada*", 'Detalles movimientos'!C$5:C$1000, "&gt;0"), "dd/mm/yyyy") &amp; " al " &amp; TEXT(_xlfn.MAXIFS('Detalles movimientos'!C$5:C$1000, 'Detalles movimientos'!F$5:F$1000, "CJ", 'Detalles movimientos'!N$5:N$1000, "&lt;&gt;*Comision Pagada*"), "dd/mm/yyyy")</f>
-        <v>Del 28/07/2026 al 11/08/2026</v>
+        <v>Del 28/07/2026 al 20/08/2026</v>
       </c>
       <c r="K9" s="50"/>
       <c r="L9" s="46"/>
@@ -32974,103 +33052,103 @@
       </c>
     </row>
     <row r="27" spans="2:13">
-      <c r="B27" s="17" t="str">
+      <c r="B27" s="17">
         <f>IFERROR(INDEX('Detalles movimientos'!C$5:C$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>46254</v>
       </c>
       <c r="C27" s="18" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!D$5:D$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>Bar Barrio Alto</v>
       </c>
       <c r="D27" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!E$5:E$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>VJYL61</v>
       </c>
       <c r="E27" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!F$5:F$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>CJ</v>
       </c>
       <c r="F27" s="18" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!G$5:G$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="G27" s="20" t="str">
+        <v>El Peñón 335 Puente Alto</v>
+      </c>
+      <c r="G27" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!H$5:H$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="H27" s="21" t="str">
+        <v>1000</v>
+      </c>
+      <c r="H27" s="21">
         <f>IFERROR(INDEX('Detalles movimientos'!I$5:I$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="I27" s="20" t="str">
+        <v>294</v>
+      </c>
+      <c r="I27" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!K$5:K$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>294000</v>
       </c>
       <c r="J27" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!L$5:L$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="K27" s="20" t="str">
+        <v>Transferencia dos</v>
+      </c>
+      <c r="K27" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!M$5:M$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="L27" s="18" t="str">
+        <v>58800</v>
+      </c>
+      <c r="L27" s="18">
         <f>IFERROR(INDEX('Detalles movimientos'!N$5:N$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="M27" s="18" t="str">
+        <v>0</v>
+      </c>
+      <c r="M27" s="18">
         <f>IFERROR(INDEX('Detalles movimientos'!Q$5:Q$1000, MATCH(15, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:13">
-      <c r="B28" s="17" t="str">
+      <c r="B28" s="17">
         <f>IFERROR(INDEX('Detalles movimientos'!C$5:C$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>46254</v>
       </c>
       <c r="C28" s="18" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!D$5:D$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>BAR Tirua</v>
       </c>
       <c r="D28" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!E$5:E$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>VJYL61</v>
       </c>
       <c r="E28" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!F$5:F$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>CJ</v>
       </c>
       <c r="F28" s="18" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!G$5:G$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="G28" s="20" t="str">
+        <v>Pirque</v>
+      </c>
+      <c r="G28" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!H$5:H$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="H28" s="21" t="str">
+        <v>1100</v>
+      </c>
+      <c r="H28" s="21">
         <f>IFERROR(INDEX('Detalles movimientos'!I$5:I$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="I28" s="20" t="str">
+        <v>500</v>
+      </c>
+      <c r="I28" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!K$5:K$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>550000</v>
       </c>
       <c r="J28" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!L$5:L$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="K28" s="20" t="str">
+        <v>Pendiente de pago</v>
+      </c>
+      <c r="K28" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!M$5:M$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="L28" s="18" t="str">
+        <v>100000</v>
+      </c>
+      <c r="L28" s="18">
         <f>IFERROR(INDEX('Detalles movimientos'!N$5:N$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="M28" s="18" t="str">
+        <v>0</v>
+      </c>
+      <c r="M28" s="18">
         <f>IFERROR(INDEX('Detalles movimientos'!Q$5:Q$1000, MATCH(16, 'Detalles movimientos'!$R$5:$R$1000, 0)), "")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:13">
@@ -47343,17 +47421,17 @@
     <row r="6" spans="2:13">
       <c r="B6" s="51">
         <f>SUMIFS('Detalles movimientos'!I$5:I$1000, 'Detalles movimientos'!F$5:F$1000, "Tripulacion")</f>
-        <v>1627</v>
+        <v>1727</v>
       </c>
       <c r="C6" s="42"/>
       <c r="E6" s="53">
         <f>SUMIFS('Detalles movimientos'!K$5:K$1000, 'Detalles movimientos'!F$5:F$1000, "Tripulacion")</f>
-        <v>715000</v>
+        <v>825000</v>
       </c>
       <c r="F6" s="42"/>
       <c r="H6" s="41">
         <f>COUNTIFS('Detalles movimientos'!F$5:F$1000, "Tripulacion")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="42"/>
     </row>
@@ -47604,53 +47682,53 @@
       </c>
     </row>
     <row r="14" spans="2:13">
-      <c r="B14" s="17" t="str">
+      <c r="B14" s="17">
         <f>IFERROR(INDEX('Detalles movimientos'!C$5:C$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
-        <v/>
+        <v>46254</v>
       </c>
       <c r="C14" s="18" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!D$5:D$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
-        <v/>
+        <v>Brasas y Sabor SpA</v>
       </c>
       <c r="D14" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!E$5:E$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
-        <v/>
+        <v>VJYL61</v>
       </c>
       <c r="E14" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!F$5:F$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
-        <v/>
+        <v>Tripulacion</v>
       </c>
       <c r="F14" s="18" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!G$5:G$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="G14" s="20" t="str">
+        <v>Puente Alto</v>
+      </c>
+      <c r="G14" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!H$5:H$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="H14" s="21" t="str">
+        <v>1100</v>
+      </c>
+      <c r="H14" s="21">
         <f>IFERROR(INDEX('Detalles movimientos'!I$5:I$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="I14" s="20" t="str">
+        <v>100</v>
+      </c>
+      <c r="I14" s="20">
         <f>IFERROR(INDEX('Detalles movimientos'!K$5:K$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
-        <v/>
+        <v>110000</v>
       </c>
       <c r="J14" s="19" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!L$5:L$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
-        <v/>
+        <v>Transferencia</v>
       </c>
       <c r="K14" s="20" t="str">
         <f>IFERROR(INDEX('Detalles movimientos'!M$5:M$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
         <v/>
       </c>
-      <c r="L14" s="18" t="str">
+      <c r="L14" s="18">
         <f>IFERROR(INDEX('Detalles movimientos'!N$5:N$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
-        <v/>
-      </c>
-      <c r="M14" s="18" t="str">
+        <v>0</v>
+      </c>
+      <c r="M14" s="18">
         <f>IFERROR(INDEX('Detalles movimientos'!Q$5:Q$1000, MATCH(5, 'Detalles movimientos'!$T$5:$T$1000, 0)), "")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:13">
